--- a/data/Portfolio_Data.xlsx
+++ b/data/Portfolio_Data.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4318272397877945</v>
+        <v>0.4318272101892018</v>
       </c>
       <c r="D2" t="n">
         <v>2.55</v>
@@ -489,7 +489,7 @@
         <v>0.001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2124301627272369</v>
+        <v>0.2124300643168826</v>
       </c>
       <c r="H2" t="n">
         <v>39443271.4940239</v>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1602014637251759</v>
+        <v>0.1602014677083552</v>
       </c>
       <c r="D4" t="n">
         <v>3.51</v>
@@ -549,7 +549,7 @@
         <v>0.0012</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1377998211066009</v>
+        <v>0.1377998458546056</v>
       </c>
       <c r="H4" t="n">
         <v>3576237.306772908</v>
@@ -627,19 +627,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.004298181662146794</v>
+        <v>-0.004298071831088435</v>
       </c>
       <c r="D7" t="n">
         <v>4.75</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07735513613143541</v>
+        <v>0.07735505685039989</v>
       </c>
       <c r="F7" t="n">
         <v>0.0007</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09273754002169089</v>
+        <v>0.09273773617454587</v>
       </c>
       <c r="H7" t="n">
         <v>32657885.20717131</v>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1403601222082391</v>
+        <v>0.1403600105958702</v>
       </c>
       <c r="D8" t="n">
         <v>3.12</v>
@@ -669,7 +669,7 @@
         <v>0.0012</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1410490660537781</v>
+        <v>0.1410490556942008</v>
       </c>
       <c r="H8" t="n">
         <v>6956048.406374502</v>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.1944658191951905</v>
+        <v>0.1944658212817616</v>
       </c>
       <c r="D10" t="n">
         <v>3.27</v>
@@ -729,7 +729,7 @@
         <v>0.0012</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1238786891579732</v>
+        <v>0.1238787037497897</v>
       </c>
       <c r="H10" t="n">
         <v>1994004.019920319</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.29134823220895</v>
+        <v>0.2913480885824562</v>
       </c>
       <c r="D11" t="n">
         <v>0.44</v>
@@ -759,7 +759,7 @@
         <v>0.001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1960776656588991</v>
+        <v>0.1960776468418581</v>
       </c>
       <c r="H11" t="n">
         <v>53327634.75697211</v>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.4738823677653698</v>
+        <v>0.4738823628988045</v>
       </c>
       <c r="D12" t="n">
         <v>0.45</v>
       </c>
       <c r="E12" t="n">
-        <v>0.159227012444634</v>
+        <v>0.1592269277443307</v>
       </c>
       <c r="F12" t="n">
         <v>0.001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2599080720598509</v>
+        <v>0.259908060475026</v>
       </c>
       <c r="H12" t="n">
         <v>15860676.42231076</v>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2392326530798412</v>
+        <v>0.2392326599641728</v>
       </c>
       <c r="D13" t="n">
         <v>1.01</v>
@@ -819,7 +819,7 @@
         <v>0.001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1289187962002901</v>
+        <v>0.1289188393896091</v>
       </c>
       <c r="H13" t="n">
         <v>71484673.19920319</v>
@@ -926,10 +926,10 @@
         <v>73.30000305175781</v>
       </c>
       <c r="G2" t="n">
-        <v>83.46841430664062</v>
+        <v>83.46840667724609</v>
       </c>
       <c r="H2" t="n">
-        <v>39.87519073486328</v>
+        <v>39.87519454956055</v>
       </c>
       <c r="I2" t="n">
         <v>21.12888526916504</v>
@@ -938,7 +938,7 @@
         <v>23.8475170135498</v>
       </c>
       <c r="K2" t="n">
-        <v>571.7960815429688</v>
+        <v>571.796142578125</v>
       </c>
       <c r="L2" t="n">
         <v>132.2658843994141</v>
@@ -952,13 +952,13 @@
         <v>45880</v>
       </c>
       <c r="B3" t="n">
-        <v>40.85206985473633</v>
+        <v>40.85207366943359</v>
       </c>
       <c r="C3" t="n">
         <v>34.18000030517578</v>
       </c>
       <c r="D3" t="n">
-        <v>85.17146301269531</v>
+        <v>85.17145538330078</v>
       </c>
       <c r="E3" t="n">
         <v>308.5499877929688</v>
@@ -967,16 +967,16 @@
         <v>73.80000305175781</v>
       </c>
       <c r="G3" t="n">
-        <v>83.56404876708984</v>
+        <v>83.56403350830078</v>
       </c>
       <c r="H3" t="n">
-        <v>39.64319229125977</v>
+        <v>39.6431884765625</v>
       </c>
       <c r="I3" t="n">
         <v>21.15790939331055</v>
       </c>
       <c r="J3" t="n">
-        <v>23.73175239562988</v>
+        <v>23.73175048828125</v>
       </c>
       <c r="K3" t="n">
         <v>570.1041870117188</v>
@@ -993,7 +993,7 @@
         <v>45881</v>
       </c>
       <c r="B4" t="n">
-        <v>41.05087280273438</v>
+        <v>41.05087661743164</v>
       </c>
       <c r="C4" t="n">
         <v>34.40999984741211</v>
@@ -1008,7 +1008,7 @@
         <v>72.94999694824219</v>
       </c>
       <c r="G4" t="n">
-        <v>83.14329528808594</v>
+        <v>83.14328002929688</v>
       </c>
       <c r="H4" t="n">
         <v>39.71086120605469</v>
@@ -1017,7 +1017,7 @@
         <v>21.07084083557129</v>
       </c>
       <c r="J4" t="n">
-        <v>23.85716438293457</v>
+        <v>23.85716247558594</v>
       </c>
       <c r="K4" t="n">
         <v>577.2697143554688</v>
@@ -1026,7 +1026,7 @@
         <v>133.4048767089844</v>
       </c>
       <c r="M4" t="n">
-        <v>635.6468505859375</v>
+        <v>635.6469116210938</v>
       </c>
     </row>
     <row r="5">
@@ -1040,7 +1040,7 @@
         <v>35</v>
       </c>
       <c r="D5" t="n">
-        <v>86.45186614990234</v>
+        <v>86.45185852050781</v>
       </c>
       <c r="E5" t="n">
         <v>309.2099914550781</v>
@@ -1058,13 +1058,13 @@
         <v>21.04181671142578</v>
       </c>
       <c r="J5" t="n">
-        <v>24.07904624938965</v>
+        <v>24.07904434204102</v>
       </c>
       <c r="K5" t="n">
-        <v>577.558349609375</v>
+        <v>577.5584106445312</v>
       </c>
       <c r="L5" t="n">
-        <v>133.4546356201172</v>
+        <v>133.4546508789062</v>
       </c>
       <c r="M5" t="n">
         <v>637.8228149414062</v>
@@ -1099,13 +1099,13 @@
         <v>21.12888526916504</v>
       </c>
       <c r="J6" t="n">
-        <v>23.91504859924316</v>
+        <v>23.91504669189453</v>
       </c>
       <c r="K6" t="n">
-        <v>577.110595703125</v>
+        <v>577.1105346679688</v>
       </c>
       <c r="L6" t="n">
-        <v>133.1661682128906</v>
+        <v>133.1661529541016</v>
       </c>
       <c r="M6" t="n">
         <v>637.882080078125</v>
@@ -1143,7 +1143,7 @@
         <v>24.01151657104492</v>
       </c>
       <c r="K7" t="n">
-        <v>574.57275390625</v>
+        <v>574.5728149414062</v>
       </c>
       <c r="L7" t="n">
         <v>132.1564483642578</v>
@@ -1157,13 +1157,13 @@
         <v>45887</v>
       </c>
       <c r="B8" t="n">
-        <v>41.23998260498047</v>
+        <v>41.23998641967773</v>
       </c>
       <c r="C8" t="n">
         <v>34.54999923706055</v>
       </c>
       <c r="D8" t="n">
-        <v>85.59505462646484</v>
+        <v>85.59504699707031</v>
       </c>
       <c r="E8" t="n">
         <v>306.9500122070312</v>
@@ -1175,7 +1175,7 @@
         <v>82.37832641601562</v>
       </c>
       <c r="H8" t="n">
-        <v>39.57552337646484</v>
+        <v>39.57552719116211</v>
       </c>
       <c r="I8" t="n">
         <v>21.08051490783691</v>
@@ -1213,16 +1213,16 @@
         <v>72.30000305175781</v>
       </c>
       <c r="G9" t="n">
-        <v>82.8564453125</v>
+        <v>82.85643768310547</v>
       </c>
       <c r="H9" t="n">
-        <v>40.28118896484375</v>
+        <v>40.28119277954102</v>
       </c>
       <c r="I9" t="n">
         <v>20.91604995727539</v>
       </c>
       <c r="J9" t="n">
-        <v>24.16586875915527</v>
+        <v>24.16586685180664</v>
       </c>
       <c r="K9" t="n">
         <v>566.5513916015625</v>
@@ -1231,7 +1231,7 @@
         <v>130.1271057128906</v>
       </c>
       <c r="M9" t="n">
-        <v>632.7984008789062</v>
+        <v>632.79833984375</v>
       </c>
     </row>
     <row r="10">
@@ -1245,7 +1245,7 @@
         <v>34.43000030517578</v>
       </c>
       <c r="D10" t="n">
-        <v>87.31829833984375</v>
+        <v>87.31830596923828</v>
       </c>
       <c r="E10" t="n">
         <v>308.3599853515625</v>
@@ -1254,7 +1254,7 @@
         <v>73.51999664306641</v>
       </c>
       <c r="G10" t="n">
-        <v>83.03810882568359</v>
+        <v>83.03810119628906</v>
       </c>
       <c r="H10" t="n">
         <v>40.43586349487305</v>
@@ -1266,13 +1266,13 @@
         <v>24.2623405456543</v>
       </c>
       <c r="K10" t="n">
-        <v>563.1876220703125</v>
+        <v>563.1875610351562</v>
       </c>
       <c r="L10" t="n">
-        <v>129.2467193603516</v>
+        <v>129.2467041015625</v>
       </c>
       <c r="M10" t="n">
-        <v>631.116943359375</v>
+        <v>631.1170043945312</v>
       </c>
     </row>
     <row r="11">
@@ -1286,7 +1286,7 @@
         <v>34.61000061035156</v>
       </c>
       <c r="D11" t="n">
-        <v>87.05837249755859</v>
+        <v>87.05838012695312</v>
       </c>
       <c r="E11" t="n">
         <v>307.2900085449219</v>
@@ -1295,7 +1295,7 @@
         <v>74.12999725341797</v>
       </c>
       <c r="G11" t="n">
-        <v>82.62694549560547</v>
+        <v>82.62693786621094</v>
       </c>
       <c r="H11" t="n">
         <v>40.29086303710938</v>
@@ -1304,16 +1304,16 @@
         <v>21.27400207519531</v>
       </c>
       <c r="J11" t="n">
-        <v>24.16586875915527</v>
+        <v>24.16586685180664</v>
       </c>
       <c r="K11" t="n">
-        <v>560.5801391601562</v>
+        <v>560.5802001953125</v>
       </c>
       <c r="L11" t="n">
-        <v>128.7791748046875</v>
+        <v>128.7791900634766</v>
       </c>
       <c r="M11" t="n">
-        <v>628.5851440429688</v>
+        <v>628.5850830078125</v>
       </c>
     </row>
     <row r="12">
@@ -1321,7 +1321,7 @@
         <v>45891</v>
       </c>
       <c r="B12" t="n">
-        <v>42.73829650878906</v>
+        <v>42.7382926940918</v>
       </c>
       <c r="C12" t="n">
         <v>35.34000015258789</v>
@@ -1336,7 +1336,7 @@
         <v>74.63999938964844</v>
       </c>
       <c r="G12" t="n">
-        <v>83.23891448974609</v>
+        <v>83.23892211914062</v>
       </c>
       <c r="H12" t="n">
         <v>40.92886734008789</v>
@@ -1377,7 +1377,7 @@
         <v>75.75</v>
       </c>
       <c r="G13" t="n">
-        <v>82.99987030029297</v>
+        <v>82.9998779296875</v>
       </c>
       <c r="H13" t="n">
         <v>40.72586441040039</v>
@@ -1386,16 +1386,16 @@
         <v>21.46749114990234</v>
       </c>
       <c r="J13" t="n">
-        <v>24.37810516357422</v>
+        <v>24.37810707092285</v>
       </c>
       <c r="K13" t="n">
-        <v>567.5863647460938</v>
+        <v>567.58642578125</v>
       </c>
       <c r="L13" t="n">
         <v>130.2315368652344</v>
       </c>
       <c r="M13" t="n">
-        <v>635.4292602539062</v>
+        <v>635.42919921875</v>
       </c>
     </row>
     <row r="14">
@@ -1409,7 +1409,7 @@
         <v>35.02000045776367</v>
       </c>
       <c r="D14" t="n">
-        <v>88.00184631347656</v>
+        <v>88.00183868408203</v>
       </c>
       <c r="E14" t="n">
         <v>312.0799865722656</v>
@@ -1459,7 +1459,7 @@
         <v>74.68000030517578</v>
       </c>
       <c r="G15" t="n">
-        <v>82.8564453125</v>
+        <v>82.85643768310547</v>
       </c>
       <c r="H15" t="n">
         <v>40.78386306762695</v>
@@ -1468,7 +1468,7 @@
         <v>21.32237434387207</v>
       </c>
       <c r="J15" t="n">
-        <v>24.5903377532959</v>
+        <v>24.59034156799316</v>
       </c>
       <c r="K15" t="n">
         <v>570.7412109375</v>
@@ -1477,7 +1477,7 @@
         <v>131.5347290039062</v>
       </c>
       <c r="M15" t="n">
-        <v>639.5436401367188</v>
+        <v>639.543701171875</v>
       </c>
     </row>
     <row r="16">
@@ -1485,7 +1485,7 @@
         <v>45897</v>
       </c>
       <c r="B16" t="n">
-        <v>43.59170532226562</v>
+        <v>43.59170150756836</v>
       </c>
       <c r="C16" t="n">
         <v>35.52000045776367</v>
@@ -1500,16 +1500,16 @@
         <v>75.23999786376953</v>
       </c>
       <c r="G16" t="n">
-        <v>83.40147399902344</v>
+        <v>83.4014892578125</v>
       </c>
       <c r="H16" t="n">
-        <v>40.67753219604492</v>
+        <v>40.67753601074219</v>
       </c>
       <c r="I16" t="n">
         <v>21.45781517028809</v>
       </c>
       <c r="J16" t="n">
-        <v>24.5613956451416</v>
+        <v>24.56139755249023</v>
       </c>
       <c r="K16" t="n">
         <v>574.31396484375</v>
@@ -1518,7 +1518,7 @@
         <v>132.5742645263672</v>
       </c>
       <c r="M16" t="n">
-        <v>641.80859375</v>
+        <v>641.8085327148438</v>
       </c>
     </row>
     <row r="17">
@@ -1532,7 +1532,7 @@
         <v>36.18999862670898</v>
       </c>
       <c r="D17" t="n">
-        <v>88.80088043212891</v>
+        <v>88.80088806152344</v>
       </c>
       <c r="E17" t="n">
         <v>318.0700073242188</v>
@@ -1541,7 +1541,7 @@
         <v>74.83999633789062</v>
       </c>
       <c r="G17" t="n">
-        <v>82.80860900878906</v>
+        <v>82.80862426757812</v>
       </c>
       <c r="H17" t="n">
         <v>40.89986801147461</v>
@@ -1550,16 +1550,16 @@
         <v>21.48683738708496</v>
       </c>
       <c r="J17" t="n">
-        <v>24.67716598510742</v>
+        <v>24.67716407775879</v>
       </c>
       <c r="K17" t="n">
-        <v>567.666015625</v>
+        <v>567.6660766601562</v>
       </c>
       <c r="L17" t="n">
         <v>130.5399475097656</v>
       </c>
       <c r="M17" t="n">
-        <v>637.98095703125</v>
+        <v>637.9810180664062</v>
       </c>
     </row>
     <row r="18">
@@ -1582,7 +1582,7 @@
         <v>76.76000213623047</v>
       </c>
       <c r="G18" t="n">
-        <v>82.19239807128906</v>
+        <v>82.19239044189453</v>
       </c>
       <c r="H18" t="n">
         <v>40.203857421875</v>
@@ -1594,10 +1594,10 @@
         <v>24.23340034484863</v>
       </c>
       <c r="K18" t="n">
-        <v>562.908935546875</v>
+        <v>562.9088745117188</v>
       </c>
       <c r="L18" t="n">
-        <v>129.2218475341797</v>
+        <v>129.2218322753906</v>
       </c>
       <c r="M18" t="n">
         <v>633.2533569335938</v>
@@ -1608,7 +1608,7 @@
         <v>45903</v>
       </c>
       <c r="B19" t="n">
-        <v>42.90800476074219</v>
+        <v>42.90800857543945</v>
       </c>
       <c r="C19" t="n">
         <v>37.34000015258789</v>
@@ -1623,7 +1623,7 @@
         <v>74.83000183105469</v>
       </c>
       <c r="G19" t="n">
-        <v>83.09466552734375</v>
+        <v>83.09465789794922</v>
       </c>
       <c r="H19" t="n">
         <v>40.0975227355957</v>
@@ -1632,13 +1632,13 @@
         <v>21.64163017272949</v>
       </c>
       <c r="J19" t="n">
-        <v>24.30093002319336</v>
+        <v>24.30092811584473</v>
       </c>
       <c r="K19" t="n">
         <v>567.3375854492188</v>
       </c>
       <c r="L19" t="n">
-        <v>129.9927978515625</v>
+        <v>129.9928131103516</v>
       </c>
       <c r="M19" t="n">
         <v>636.6853637695312</v>
@@ -1664,7 +1664,7 @@
         <v>74.18000030517578</v>
       </c>
       <c r="G20" t="n">
-        <v>83.72815704345703</v>
+        <v>83.72816467285156</v>
       </c>
       <c r="H20" t="n">
         <v>40.36819458007812</v>
@@ -1673,7 +1673,7 @@
         <v>21.48683738708496</v>
       </c>
       <c r="J20" t="n">
-        <v>24.45528221130371</v>
+        <v>24.45528030395508</v>
       </c>
       <c r="K20" t="n">
         <v>572.4728393554688</v>
@@ -1682,7 +1682,7 @@
         <v>130.6344451904297</v>
       </c>
       <c r="M20" t="n">
-        <v>642.0064086914062</v>
+        <v>642.00634765625</v>
       </c>
     </row>
     <row r="21">
@@ -1690,7 +1690,7 @@
         <v>45905</v>
       </c>
       <c r="B21" t="n">
-        <v>42.36007690429688</v>
+        <v>42.36008071899414</v>
       </c>
       <c r="C21" t="n">
         <v>37.20999908447266</v>
@@ -1705,10 +1705,10 @@
         <v>72.62999725341797</v>
       </c>
       <c r="G21" t="n">
-        <v>85.00477600097656</v>
+        <v>85.00476837158203</v>
       </c>
       <c r="H21" t="n">
-        <v>40.77420043945312</v>
+        <v>40.77419662475586</v>
       </c>
       <c r="I21" t="n">
         <v>21.31270027160645</v>
@@ -1717,10 +1717,10 @@
         <v>24.69645881652832</v>
       </c>
       <c r="K21" t="n">
-        <v>573.298828125</v>
+        <v>573.2988891601562</v>
       </c>
       <c r="L21" t="n">
-        <v>130.7438507080078</v>
+        <v>130.7438354492188</v>
       </c>
       <c r="M21" t="n">
         <v>640.14697265625</v>
@@ -1746,7 +1746,7 @@
         <v>73.04000091552734</v>
       </c>
       <c r="G22" t="n">
-        <v>86.13740539550781</v>
+        <v>86.13739013671875</v>
       </c>
       <c r="H22" t="n">
         <v>40.5035285949707</v>
@@ -1764,7 +1764,7 @@
         <v>131.7237243652344</v>
       </c>
       <c r="M22" t="n">
-        <v>641.7196044921875</v>
+        <v>641.7195434570312</v>
       </c>
     </row>
     <row r="23">
@@ -1772,7 +1772,7 @@
         <v>45909</v>
       </c>
       <c r="B23" t="n">
-        <v>42.46675491333008</v>
+        <v>42.46675872802734</v>
       </c>
       <c r="C23" t="n">
         <v>37.18000030517578</v>
@@ -1799,13 +1799,13 @@
         <v>24.60963439941406</v>
       </c>
       <c r="K23" t="n">
-        <v>577.7276000976562</v>
+        <v>577.7275390625</v>
       </c>
       <c r="L23" t="n">
         <v>131.9773864746094</v>
       </c>
       <c r="M23" t="n">
-        <v>643.2031860351562</v>
+        <v>643.203125</v>
       </c>
     </row>
     <row r="24">
@@ -1828,7 +1828,7 @@
         <v>74.70999908447266</v>
       </c>
       <c r="G24" t="n">
-        <v>86.13740539550781</v>
+        <v>86.13739013671875</v>
       </c>
       <c r="H24" t="n">
         <v>40.46486282348633</v>
@@ -1869,7 +1869,7 @@
         <v>73</v>
       </c>
       <c r="G25" t="n">
-        <v>86.71331024169922</v>
+        <v>86.71330261230469</v>
       </c>
       <c r="H25" t="n">
         <v>41.12220001220703</v>
@@ -1878,16 +1878,16 @@
         <v>21.49651145935059</v>
       </c>
       <c r="J25" t="n">
-        <v>24.99551773071289</v>
+        <v>24.99551582336426</v>
       </c>
       <c r="K25" t="n">
-        <v>581.2803955078125</v>
+        <v>581.2804565429688</v>
       </c>
       <c r="L25" t="n">
         <v>134.8224487304688</v>
       </c>
       <c r="M25" t="n">
-        <v>650.423095703125</v>
+        <v>650.4231567382812</v>
       </c>
     </row>
     <row r="26">
@@ -1901,7 +1901,7 @@
         <v>38.34000015258789</v>
       </c>
       <c r="D26" t="n">
-        <v>89.34963226318359</v>
+        <v>89.34962463378906</v>
       </c>
       <c r="E26" t="n">
         <v>335.4200134277344</v>
@@ -1910,10 +1910,10 @@
         <v>73.30999755859375</v>
       </c>
       <c r="G26" t="n">
-        <v>86.33896636962891</v>
+        <v>86.33897399902344</v>
       </c>
       <c r="H26" t="n">
-        <v>40.93853378295898</v>
+        <v>40.93852996826172</v>
       </c>
       <c r="I26" t="n">
         <v>21.62228012084961</v>
@@ -1922,10 +1922,10 @@
         <v>24.9472827911377</v>
       </c>
       <c r="K26" t="n">
-        <v>583.8479614257812</v>
+        <v>583.8480834960938</v>
       </c>
       <c r="L26" t="n">
-        <v>134.7329254150391</v>
+        <v>134.73291015625</v>
       </c>
       <c r="M26" t="n">
         <v>650.2055053710938</v>
@@ -1936,7 +1936,7 @@
         <v>45915</v>
       </c>
       <c r="B27" t="n">
-        <v>42.81587600708008</v>
+        <v>42.81587982177734</v>
       </c>
       <c r="C27" t="n">
         <v>38.7599983215332</v>
@@ -1951,10 +1951,10 @@
         <v>74.23000335693359</v>
       </c>
       <c r="G27" t="n">
-        <v>86.54054260253906</v>
+        <v>86.54053497314453</v>
       </c>
       <c r="H27" t="n">
-        <v>40.89019775390625</v>
+        <v>40.89020156860352</v>
       </c>
       <c r="I27" t="n">
         <v>21.81576728820801</v>
@@ -1963,10 +1963,10 @@
         <v>24.93763542175293</v>
       </c>
       <c r="K27" t="n">
-        <v>588.8439331054688</v>
+        <v>588.843994140625</v>
       </c>
       <c r="L27" t="n">
-        <v>135.9465484619141</v>
+        <v>135.9465789794922</v>
       </c>
       <c r="M27" t="n">
         <v>653.6671752929688</v>
@@ -1977,7 +1977,7 @@
         <v>45916</v>
       </c>
       <c r="B28" t="n">
-        <v>43.53351593017578</v>
+        <v>43.53351211547852</v>
       </c>
       <c r="C28" t="n">
         <v>38.59999847412109</v>
@@ -1992,7 +1992,7 @@
         <v>75.66999816894531</v>
       </c>
       <c r="G28" t="n">
-        <v>86.72291564941406</v>
+        <v>86.72289276123047</v>
       </c>
       <c r="H28" t="n">
         <v>40.64852905273438</v>
@@ -2001,13 +2001,13 @@
         <v>22.03828048706055</v>
       </c>
       <c r="J28" t="n">
-        <v>24.83642196655273</v>
+        <v>24.8364200592041</v>
       </c>
       <c r="K28" t="n">
         <v>588.3463745117188</v>
       </c>
       <c r="L28" t="n">
-        <v>135.4740295410156</v>
+        <v>135.4740447998047</v>
       </c>
       <c r="M28" t="n">
         <v>652.7671508789062</v>
@@ -2033,10 +2033,10 @@
         <v>74.97000122070312</v>
       </c>
       <c r="G29" t="n">
-        <v>86.50214385986328</v>
+        <v>86.50213623046875</v>
       </c>
       <c r="H29" t="n">
-        <v>40.62919616699219</v>
+        <v>40.62919235229492</v>
       </c>
       <c r="I29" t="n">
         <v>21.80609512329102</v>
@@ -2083,16 +2083,16 @@
         <v>21.7093505859375</v>
       </c>
       <c r="J30" t="n">
-        <v>24.77802658081055</v>
+        <v>24.77802467346191</v>
       </c>
       <c r="K30" t="n">
-        <v>592.4664916992188</v>
+        <v>592.4666137695312</v>
       </c>
       <c r="L30" t="n">
-        <v>137.3392639160156</v>
+        <v>137.3392486572266</v>
       </c>
       <c r="M30" t="n">
-        <v>655.00244140625</v>
+        <v>655.0023803710938</v>
       </c>
     </row>
     <row r="31">
@@ -2115,7 +2115,7 @@
         <v>73.51999664306641</v>
       </c>
       <c r="G31" t="n">
-        <v>85.4462890625</v>
+        <v>85.44631195068359</v>
       </c>
       <c r="H31" t="n">
         <v>40.45519256591797</v>
@@ -2141,7 +2141,7 @@
         <v>45922</v>
       </c>
       <c r="B32" t="n">
-        <v>42.8731575012207</v>
+        <v>42.87316131591797</v>
       </c>
       <c r="C32" t="n">
         <v>40.04000091552734</v>
@@ -2156,7 +2156,7 @@
         <v>73.44999694824219</v>
       </c>
       <c r="G32" t="n">
-        <v>85.13916015625</v>
+        <v>85.13915252685547</v>
       </c>
       <c r="H32" t="n">
         <v>40.58863830566406</v>
@@ -2171,10 +2171,10 @@
         <v>600.0083618164062</v>
       </c>
       <c r="L32" t="n">
-        <v>140.7728729248047</v>
+        <v>140.7728576660156</v>
       </c>
       <c r="M32" t="n">
-        <v>661.3607177734375</v>
+        <v>661.3606567382812</v>
       </c>
     </row>
     <row r="33">
@@ -2197,7 +2197,7 @@
         <v>75.05000305175781</v>
       </c>
       <c r="G33" t="n">
-        <v>85.7342529296875</v>
+        <v>85.73424530029297</v>
       </c>
       <c r="H33" t="n">
         <v>40.91007995605469</v>
@@ -2215,7 +2215,7 @@
         <v>139.5576629638672</v>
       </c>
       <c r="M33" t="n">
-        <v>657.7605590820312</v>
+        <v>657.7606201171875</v>
       </c>
     </row>
     <row r="34">
@@ -2223,7 +2223,7 @@
         <v>45924</v>
       </c>
       <c r="B34" t="n">
-        <v>44.17887115478516</v>
+        <v>44.17886734008789</v>
       </c>
       <c r="C34" t="n">
         <v>39.81999969482422</v>
@@ -2238,7 +2238,7 @@
         <v>76.38999938964844</v>
       </c>
       <c r="G34" t="n">
-        <v>85.40790557861328</v>
+        <v>85.40792083740234</v>
       </c>
       <c r="H34" t="n">
         <v>40.49123764038086</v>
@@ -2247,7 +2247,7 @@
         <v>21.9028377532959</v>
       </c>
       <c r="J34" t="n">
-        <v>24.57365036010742</v>
+        <v>24.57365226745605</v>
       </c>
       <c r="K34" t="n">
         <v>593.9305419921875</v>
@@ -2279,7 +2279,7 @@
         <v>76.98999786376953</v>
       </c>
       <c r="G35" t="n">
-        <v>85.40790557861328</v>
+        <v>85.40792083740234</v>
       </c>
       <c r="H35" t="n">
         <v>40.39383316040039</v>
@@ -2320,7 +2320,7 @@
         <v>77.01999664306641</v>
       </c>
       <c r="G36" t="n">
-        <v>85.33112335205078</v>
+        <v>85.33110046386719</v>
       </c>
       <c r="H36" t="n">
         <v>40.79319381713867</v>
@@ -2335,7 +2335,7 @@
         <v>593.801025390625</v>
       </c>
       <c r="L36" t="n">
-        <v>138.8704071044922</v>
+        <v>138.8703918457031</v>
       </c>
       <c r="M36" t="n">
         <v>656.3819580078125</v>
@@ -2346,7 +2346,7 @@
         <v>45929</v>
       </c>
       <c r="B37" t="n">
-        <v>44.15930938720703</v>
+        <v>44.15930557250977</v>
       </c>
       <c r="C37" t="n">
         <v>42.5</v>
@@ -2361,7 +2361,7 @@
         <v>74.58999633789062</v>
       </c>
       <c r="G37" t="n">
-        <v>86.03179931640625</v>
+        <v>86.03181457519531</v>
       </c>
       <c r="H37" t="n">
         <v>40.87111282348633</v>
@@ -2414,7 +2414,7 @@
         <v>24.87534713745117</v>
       </c>
       <c r="K38" t="n">
-        <v>598.1849975585938</v>
+        <v>598.18505859375</v>
       </c>
       <c r="L38" t="n">
         <v>140.3744354248047</v>
@@ -2443,7 +2443,7 @@
         <v>73.13999938964844</v>
       </c>
       <c r="G39" t="n">
-        <v>86.00379180908203</v>
+        <v>86.00377655029297</v>
       </c>
       <c r="H39" t="n">
         <v>41.03670501708984</v>
@@ -2458,10 +2458,10 @@
         <v>601.0545043945312</v>
       </c>
       <c r="L39" t="n">
-        <v>141.7489929199219</v>
+        <v>141.7490081787109</v>
       </c>
       <c r="M39" t="n">
-        <v>662.9574584960938</v>
+        <v>662.95751953125</v>
       </c>
     </row>
     <row r="40">
@@ -2484,7 +2484,7 @@
         <v>71.54000091552734</v>
       </c>
       <c r="G40" t="n">
-        <v>86.25423431396484</v>
+        <v>86.25421905517578</v>
       </c>
       <c r="H40" t="n">
         <v>40.82241058349609</v>
@@ -2496,7 +2496,7 @@
         <v>24.84615325927734</v>
       </c>
       <c r="K40" t="n">
-        <v>603.5255126953125</v>
+        <v>603.5254516601562</v>
       </c>
       <c r="L40" t="n">
         <v>142.5159606933594</v>
@@ -2540,7 +2540,7 @@
         <v>600.9848022460938</v>
       </c>
       <c r="L41" t="n">
-        <v>141.7987976074219</v>
+        <v>141.7988128662109</v>
       </c>
       <c r="M41" t="n">
         <v>663.7112426757812</v>
@@ -2551,7 +2551,7 @@
         <v>45936</v>
       </c>
       <c r="B42" t="n">
-        <v>43.69473266601562</v>
+        <v>43.69472885131836</v>
       </c>
       <c r="C42" t="n">
         <v>44.06000137329102</v>
@@ -2566,7 +2566,7 @@
         <v>72.87000274658203</v>
       </c>
       <c r="G42" t="n">
-        <v>85.40660095214844</v>
+        <v>85.40660858154297</v>
       </c>
       <c r="H42" t="n">
         <v>40.57889938354492</v>
@@ -2607,7 +2607,7 @@
         <v>73.19999694824219</v>
       </c>
       <c r="G43" t="n">
-        <v>85.89784240722656</v>
+        <v>85.89783477783203</v>
       </c>
       <c r="H43" t="n">
         <v>40.4522705078125</v>
@@ -2619,7 +2619,7 @@
         <v>24.69043922424316</v>
       </c>
       <c r="K43" t="n">
-        <v>602.3099975585938</v>
+        <v>602.3099365234375</v>
       </c>
       <c r="L43" t="n">
         <v>142.2769012451172</v>
@@ -2633,7 +2633,7 @@
         <v>45938</v>
       </c>
       <c r="B44" t="n">
-        <v>43.50889587402344</v>
+        <v>43.5088996887207</v>
       </c>
       <c r="C44" t="n">
         <v>44.56000137329102</v>
@@ -2648,7 +2648,7 @@
         <v>73.52999877929688</v>
       </c>
       <c r="G44" t="n">
-        <v>85.96525573730469</v>
+        <v>85.96526336669922</v>
       </c>
       <c r="H44" t="n">
         <v>40.24772262573242</v>
@@ -2657,7 +2657,7 @@
         <v>22.01893043518066</v>
       </c>
       <c r="J44" t="n">
-        <v>24.55418586730957</v>
+        <v>24.5541877746582</v>
       </c>
       <c r="K44" t="n">
         <v>609.2147216796875</v>
@@ -2689,7 +2689,7 @@
         <v>72.51000213623047</v>
       </c>
       <c r="G45" t="n">
-        <v>85.89784240722656</v>
+        <v>85.89783477783203</v>
       </c>
       <c r="H45" t="n">
         <v>40.06265640258789</v>
@@ -2698,7 +2698,7 @@
         <v>21.81576728820801</v>
       </c>
       <c r="J45" t="n">
-        <v>24.39847373962402</v>
+        <v>24.39847183227539</v>
       </c>
       <c r="K45" t="n">
         <v>608.4774169921875</v>
@@ -2730,7 +2730,7 @@
         <v>69.38999938964844</v>
       </c>
       <c r="G46" t="n">
-        <v>87.28482818603516</v>
+        <v>87.28484344482422</v>
       </c>
       <c r="H46" t="n">
         <v>39.62433242797852</v>
@@ -2742,10 +2742,10 @@
         <v>24.13570594787598</v>
       </c>
       <c r="K46" t="n">
-        <v>587.3545532226562</v>
+        <v>587.3546142578125</v>
       </c>
       <c r="L46" t="n">
-        <v>138.6462860107422</v>
+        <v>138.6463012695312</v>
       </c>
       <c r="M46" t="n">
         <v>647.6542358398438</v>
@@ -2771,7 +2771,7 @@
         <v>70.27999877929688</v>
       </c>
       <c r="G47" t="n">
-        <v>87.23667907714844</v>
+        <v>87.23666381835938</v>
       </c>
       <c r="H47" t="n">
         <v>39.84836578369141</v>
@@ -2797,7 +2797,7 @@
         <v>45944</v>
       </c>
       <c r="B48" t="n">
-        <v>42.23742294311523</v>
+        <v>42.2374267578125</v>
       </c>
       <c r="C48" t="n">
         <v>46.79999923706055</v>
@@ -2838,7 +2838,7 @@
         <v>45945</v>
       </c>
       <c r="B49" t="n">
-        <v>42.21297073364258</v>
+        <v>42.21297454833984</v>
       </c>
       <c r="C49" t="n">
         <v>48.33000183105469</v>
@@ -2868,7 +2868,7 @@
         <v>600.0282592773438</v>
       </c>
       <c r="L49" t="n">
-        <v>141.5896148681641</v>
+        <v>141.5896301269531</v>
       </c>
       <c r="M49" t="n">
         <v>659.7044067382812</v>
@@ -2879,7 +2879,7 @@
         <v>45946</v>
       </c>
       <c r="B50" t="n">
-        <v>41.70438003540039</v>
+        <v>41.70438385009766</v>
       </c>
       <c r="C50" t="n">
         <v>49.16999816894531</v>
@@ -2903,13 +2903,13 @@
         <v>21.41911697387695</v>
       </c>
       <c r="J50" t="n">
-        <v>24.79749298095703</v>
+        <v>24.7974910736084</v>
       </c>
       <c r="K50" t="n">
         <v>597.806396484375</v>
       </c>
       <c r="L50" t="n">
-        <v>141.6942291259766</v>
+        <v>141.6942138671875</v>
       </c>
       <c r="M50" t="n">
         <v>655.2117309570312</v>
@@ -2935,7 +2935,7 @@
         <v>67.98000335693359</v>
       </c>
       <c r="G51" t="n">
-        <v>87.84349822998047</v>
+        <v>87.84349060058594</v>
       </c>
       <c r="H51" t="n">
         <v>40.94903945922852</v>
@@ -2961,7 +2961,7 @@
         <v>45950</v>
       </c>
       <c r="B52" t="n">
-        <v>42.49171447753906</v>
+        <v>42.49171829223633</v>
       </c>
       <c r="C52" t="n">
         <v>47.72000122070312</v>
@@ -2976,7 +2976,7 @@
         <v>67.83000183105469</v>
       </c>
       <c r="G52" t="n">
-        <v>88.18061065673828</v>
+        <v>88.18060302734375</v>
       </c>
       <c r="H52" t="n">
         <v>41.37762069702148</v>
@@ -2988,7 +2988,7 @@
         <v>25.14784812927246</v>
       </c>
       <c r="K52" t="n">
-        <v>609.3142700195312</v>
+        <v>609.3143310546875</v>
       </c>
       <c r="L52" t="n">
         <v>143.5269622802734</v>
@@ -3002,7 +3002,7 @@
         <v>45951</v>
       </c>
       <c r="B53" t="n">
-        <v>42.39391326904297</v>
+        <v>42.39391708374023</v>
       </c>
       <c r="C53" t="n">
         <v>43.79000091552734</v>
@@ -3017,7 +3017,7 @@
         <v>68.26999664306641</v>
       </c>
       <c r="G53" t="n">
-        <v>88.61405181884766</v>
+        <v>88.61404418945312</v>
       </c>
       <c r="H53" t="n">
         <v>41.25099182128906</v>
@@ -3026,13 +3026,13 @@
         <v>21.39009475708008</v>
       </c>
       <c r="J53" t="n">
-        <v>25.01160049438477</v>
+        <v>25.01159858703613</v>
       </c>
       <c r="K53" t="n">
         <v>609.1549682617188</v>
       </c>
       <c r="L53" t="n">
-        <v>143.6016540527344</v>
+        <v>143.6016693115234</v>
       </c>
       <c r="M53" t="n">
         <v>665.7741088867188</v>
@@ -3043,7 +3043,7 @@
         <v>45952</v>
       </c>
       <c r="B54" t="n">
-        <v>42.93673324584961</v>
+        <v>42.93673706054688</v>
       </c>
       <c r="C54" t="n">
         <v>43.88000106811523</v>
@@ -3058,7 +3058,7 @@
         <v>70.62999725341797</v>
       </c>
       <c r="G54" t="n">
-        <v>88.67182922363281</v>
+        <v>88.67183685302734</v>
       </c>
       <c r="H54" t="n">
         <v>41.43606567382812</v>
@@ -3073,7 +3073,7 @@
         <v>603.286376953125</v>
       </c>
       <c r="L54" t="n">
-        <v>142.1822662353516</v>
+        <v>142.1822814941406</v>
       </c>
       <c r="M54" t="n">
         <v>662.3128051757812</v>
@@ -3084,7 +3084,7 @@
         <v>45953</v>
       </c>
       <c r="B55" t="n">
-        <v>43.50889587402344</v>
+        <v>43.5088996887207</v>
       </c>
       <c r="C55" t="n">
         <v>44.18000030517578</v>
@@ -3099,7 +3099,7 @@
         <v>73.29000091552734</v>
       </c>
       <c r="G55" t="n">
-        <v>88.06504058837891</v>
+        <v>88.06503295898438</v>
       </c>
       <c r="H55" t="n">
         <v>41.39710235595703</v>
@@ -3111,10 +3111,10 @@
         <v>25.18677520751953</v>
       </c>
       <c r="K55" t="n">
-        <v>608.35791015625</v>
+        <v>608.3578491210938</v>
       </c>
       <c r="L55" t="n">
-        <v>143.9751892089844</v>
+        <v>143.9751739501953</v>
       </c>
       <c r="M55" t="n">
         <v>666.2402954101562</v>
@@ -3125,7 +3125,7 @@
         <v>45954</v>
       </c>
       <c r="B56" t="n">
-        <v>43.06877136230469</v>
+        <v>43.06877517700195</v>
       </c>
       <c r="C56" t="n">
         <v>43.9900016784668</v>
@@ -3140,7 +3140,7 @@
         <v>73.18000030517578</v>
       </c>
       <c r="G56" t="n">
-        <v>88.10356140136719</v>
+        <v>88.10355377197266</v>
       </c>
       <c r="H56" t="n">
         <v>41.543212890625</v>
@@ -3152,7 +3152,7 @@
         <v>25.23543739318848</v>
       </c>
       <c r="K56" t="n">
-        <v>614.8541259765625</v>
+        <v>614.8540649414062</v>
       </c>
       <c r="L56" t="n">
         <v>146.2113342285156</v>
@@ -3181,7 +3181,7 @@
         <v>73.12000274658203</v>
       </c>
       <c r="G57" t="n">
-        <v>88.40215301513672</v>
+        <v>88.40214538574219</v>
       </c>
       <c r="H57" t="n">
         <v>41.63087844848633</v>
@@ -3193,10 +3193,10 @@
         <v>25.32302665710449</v>
       </c>
       <c r="K57" t="n">
-        <v>625.80419921875</v>
+        <v>625.8041381835938</v>
       </c>
       <c r="L57" t="n">
-        <v>148.9106597900391</v>
+        <v>148.91064453125</v>
       </c>
       <c r="M57" t="n">
         <v>679.6094970703125</v>
@@ -3234,13 +3234,13 @@
         <v>24.93374252319336</v>
       </c>
       <c r="K58" t="n">
-        <v>630.6165161132812</v>
+        <v>630.6165771484375</v>
       </c>
       <c r="L58" t="n">
-        <v>150.3848266601562</v>
+        <v>150.3848114013672</v>
       </c>
       <c r="M58" t="n">
-        <v>681.4144897460938</v>
+        <v>681.41455078125</v>
       </c>
     </row>
     <row r="59">
@@ -3263,7 +3263,7 @@
         <v>71.80000305175781</v>
       </c>
       <c r="G59" t="n">
-        <v>87.737548828125</v>
+        <v>87.73753356933594</v>
       </c>
       <c r="H59" t="n">
         <v>39.59511184692383</v>
@@ -3278,7 +3278,7 @@
         <v>633.4562377929688</v>
       </c>
       <c r="L59" t="n">
-        <v>151.4655609130859</v>
+        <v>151.4655456542969</v>
       </c>
       <c r="M59" t="n">
         <v>681.7418823242188</v>
@@ -3316,13 +3316,13 @@
         <v>24.49579429626465</v>
       </c>
       <c r="K60" t="n">
-        <v>623.7716064453125</v>
+        <v>623.7715454101562</v>
       </c>
       <c r="L60" t="n">
-        <v>149.6029357910156</v>
+        <v>149.6029205322266</v>
       </c>
       <c r="M60" t="n">
-        <v>674.2440185546875</v>
+        <v>674.2439575195312</v>
       </c>
     </row>
     <row r="61">
@@ -3345,7 +3345,7 @@
         <v>72.55999755859375</v>
       </c>
       <c r="G61" t="n">
-        <v>86.96697998046875</v>
+        <v>86.96698760986328</v>
       </c>
       <c r="H61" t="n">
         <v>39.83862686157227</v>
@@ -3357,10 +3357,10 @@
         <v>24.53472328186035</v>
       </c>
       <c r="K61" t="n">
-        <v>626.7805786132812</v>
+        <v>626.7806396484375</v>
       </c>
       <c r="L61" t="n">
-        <v>149.7473297119141</v>
+        <v>149.7473449707031</v>
       </c>
       <c r="M61" t="n">
         <v>676.4556274414062</v>
@@ -3386,7 +3386,7 @@
         <v>72.73999786376953</v>
       </c>
       <c r="G62" t="n">
-        <v>86.74948883056641</v>
+        <v>86.74948120117188</v>
       </c>
       <c r="H62" t="n">
         <v>39.77044296264648</v>
@@ -3395,10 +3395,10 @@
         <v>22.29948806762695</v>
       </c>
       <c r="J62" t="n">
-        <v>24.55418586730957</v>
+        <v>24.5541877746582</v>
       </c>
       <c r="K62" t="n">
-        <v>629.779541015625</v>
+        <v>629.7796020507812</v>
       </c>
       <c r="L62" t="n">
         <v>150.3599243164062</v>
@@ -3436,13 +3436,13 @@
         <v>22.14469718933105</v>
       </c>
       <c r="J63" t="n">
-        <v>24.50552749633789</v>
+        <v>24.50552558898926</v>
       </c>
       <c r="K63" t="n">
-        <v>616.996337890625</v>
+        <v>616.9962768554688</v>
       </c>
       <c r="L63" t="n">
-        <v>146.390625</v>
+        <v>146.3906402587891</v>
       </c>
       <c r="M63" t="n">
         <v>669.6917114257812</v>
@@ -3468,7 +3468,7 @@
         <v>71.02999877929688</v>
       </c>
       <c r="G64" t="n">
-        <v>85.99547576904297</v>
+        <v>85.99546051025391</v>
       </c>
       <c r="H64" t="n">
         <v>39.86784362792969</v>
@@ -3483,10 +3483,10 @@
         <v>621.01171875</v>
       </c>
       <c r="L64" t="n">
-        <v>146.9633483886719</v>
+        <v>146.9633636474609</v>
       </c>
       <c r="M64" t="n">
-        <v>672.012451171875</v>
+        <v>672.0125122070312</v>
       </c>
     </row>
     <row r="65">
@@ -3518,13 +3518,13 @@
         <v>22.10600090026855</v>
       </c>
       <c r="J65" t="n">
-        <v>24.50552749633789</v>
+        <v>24.50552558898926</v>
       </c>
       <c r="K65" t="n">
         <v>609.4439086914062</v>
       </c>
       <c r="L65" t="n">
-        <v>144.0100555419922</v>
+        <v>144.0100402832031</v>
       </c>
       <c r="M65" t="n">
         <v>664.8021850585938</v>
@@ -3550,7 +3550,7 @@
         <v>71.26000213623047</v>
       </c>
       <c r="G66" t="n">
-        <v>86.58515930175781</v>
+        <v>86.58515167236328</v>
       </c>
       <c r="H66" t="n">
         <v>40.19902038574219</v>
@@ -3559,13 +3559,13 @@
         <v>22.15437126159668</v>
       </c>
       <c r="J66" t="n">
-        <v>24.83642196655273</v>
+        <v>24.8364200592041</v>
       </c>
       <c r="K66" t="n">
-        <v>607.5208740234375</v>
+        <v>607.5209350585938</v>
       </c>
       <c r="L66" t="n">
-        <v>143.5120086669922</v>
+        <v>143.5120239257812</v>
       </c>
       <c r="M66" t="n">
         <v>665.4567260742188</v>
@@ -3591,7 +3591,7 @@
         <v>71.68000030517578</v>
       </c>
       <c r="G67" t="n">
-        <v>86.56581878662109</v>
+        <v>86.56580352783203</v>
       </c>
       <c r="H67" t="n">
         <v>40.1697998046875</v>
@@ -3603,10 +3603,10 @@
         <v>24.78775978088379</v>
       </c>
       <c r="K67" t="n">
-        <v>620.9617919921875</v>
+        <v>620.9618530273438</v>
       </c>
       <c r="L67" t="n">
-        <v>147.1824798583984</v>
+        <v>147.1824951171875</v>
       </c>
       <c r="M67" t="n">
         <v>675.8407592773438</v>
@@ -3632,7 +3632,7 @@
         <v>72.72000122070312</v>
       </c>
       <c r="G68" t="n">
-        <v>86.96214294433594</v>
+        <v>86.96215057373047</v>
       </c>
       <c r="H68" t="n">
         <v>40.61786270141602</v>
@@ -3673,7 +3673,7 @@
         <v>69.79000091552734</v>
       </c>
       <c r="G69" t="n">
-        <v>87.11682891845703</v>
+        <v>87.11681365966797</v>
       </c>
       <c r="H69" t="n">
         <v>40.29642486572266</v>
@@ -3714,7 +3714,7 @@
         <v>69.84999847412109</v>
       </c>
       <c r="G70" t="n">
-        <v>86.4014892578125</v>
+        <v>86.40148162841797</v>
       </c>
       <c r="H70" t="n">
         <v>39.77044296264648</v>
@@ -3732,7 +3732,7 @@
         <v>142.7301177978516</v>
       </c>
       <c r="M70" t="n">
-        <v>666.5180053710938</v>
+        <v>666.5179443359375</v>
       </c>
     </row>
     <row r="71">
@@ -3770,10 +3770,10 @@
         <v>606.6441040039062</v>
       </c>
       <c r="L71" t="n">
-        <v>143.5070495605469</v>
+        <v>143.5070343017578</v>
       </c>
       <c r="M71" t="n">
-        <v>666.4088745117188</v>
+        <v>666.408935546875</v>
       </c>
     </row>
     <row r="72">
@@ -3781,7 +3781,7 @@
         <v>45978</v>
       </c>
       <c r="B72" t="n">
-        <v>44.17887115478516</v>
+        <v>44.17886734008789</v>
       </c>
       <c r="C72" t="n">
         <v>45.47000122070312</v>
@@ -3796,7 +3796,7 @@
         <v>71.30000305175781</v>
       </c>
       <c r="G72" t="n">
-        <v>86.12114715576172</v>
+        <v>86.12113952636719</v>
       </c>
       <c r="H72" t="n">
         <v>39.62433242797852</v>
@@ -3808,7 +3808,7 @@
         <v>24.40820503234863</v>
       </c>
       <c r="K72" t="n">
-        <v>601.4630126953125</v>
+        <v>601.4630737304688</v>
       </c>
       <c r="L72" t="n">
         <v>141.2609405517578</v>
@@ -3846,16 +3846,16 @@
         <v>22.37688255310059</v>
       </c>
       <c r="J73" t="n">
-        <v>24.44713401794434</v>
+        <v>24.44713592529297</v>
       </c>
       <c r="K73" t="n">
-        <v>594.1398315429688</v>
+        <v>594.1397094726562</v>
       </c>
       <c r="L73" t="n">
-        <v>138.9650115966797</v>
+        <v>138.9650268554688</v>
       </c>
       <c r="M73" t="n">
-        <v>654.6561889648438</v>
+        <v>654.65625</v>
       </c>
     </row>
     <row r="74">
@@ -3878,7 +3878,7 @@
         <v>70.87999725341797</v>
       </c>
       <c r="G74" t="n">
-        <v>85.91813659667969</v>
+        <v>85.91812896728516</v>
       </c>
       <c r="H74" t="n">
         <v>39.45874404907227</v>
@@ -3919,7 +3919,7 @@
         <v>70.15000152587891</v>
       </c>
       <c r="G75" t="n">
-        <v>86.25648498535156</v>
+        <v>86.25647735595703</v>
       </c>
       <c r="H75" t="n">
         <v>39.3223762512207</v>
@@ -3928,10 +3928,10 @@
         <v>21.94153594970703</v>
       </c>
       <c r="J75" t="n">
-        <v>24.16490364074707</v>
+        <v>24.16490173339844</v>
       </c>
       <c r="K75" t="n">
-        <v>583.5385131835938</v>
+        <v>583.5384521484375</v>
       </c>
       <c r="L75" t="n">
         <v>135.53857421875</v>
@@ -3945,7 +3945,7 @@
         <v>45982</v>
       </c>
       <c r="B76" t="n">
-        <v>43.72896194458008</v>
+        <v>43.72895812988281</v>
       </c>
       <c r="C76" t="n">
         <v>45.29999923706055</v>
@@ -3960,7 +3960,7 @@
         <v>69.30000305175781</v>
       </c>
       <c r="G76" t="n">
-        <v>86.51747131347656</v>
+        <v>86.51747894287109</v>
       </c>
       <c r="H76" t="n">
         <v>39.83862686157227</v>
@@ -3975,7 +3975,7 @@
         <v>587.9224853515625</v>
       </c>
       <c r="L76" t="n">
-        <v>136.0615234375</v>
+        <v>136.0615081787109</v>
       </c>
       <c r="M76" t="n">
         <v>653.6148681640625</v>
@@ -3986,7 +3986,7 @@
         <v>45985</v>
       </c>
       <c r="B77" t="n">
-        <v>43.60670852661133</v>
+        <v>43.60670471191406</v>
       </c>
       <c r="C77" t="n">
         <v>46.63000106811523</v>
@@ -4001,7 +4001,7 @@
         <v>70.41999816894531</v>
       </c>
       <c r="G77" t="n">
-        <v>87.010498046875</v>
+        <v>87.01048278808594</v>
       </c>
       <c r="H77" t="n">
         <v>39.89706420898438</v>
@@ -4010,13 +4010,13 @@
         <v>21.9028377532959</v>
       </c>
       <c r="J77" t="n">
-        <v>24.44713401794434</v>
+        <v>24.44713592529297</v>
       </c>
       <c r="K77" t="n">
         <v>602.9575805664062</v>
       </c>
       <c r="L77" t="n">
-        <v>139.3036804199219</v>
+        <v>139.3036651611328</v>
       </c>
       <c r="M77" t="n">
         <v>663.2351684570312</v>
@@ -4027,7 +4027,7 @@
         <v>45986</v>
       </c>
       <c r="B78" t="n">
-        <v>43.33284759521484</v>
+        <v>43.33285140991211</v>
       </c>
       <c r="C78" t="n">
         <v>46.66999816894531</v>
@@ -4042,7 +4042,7 @@
         <v>69.25</v>
       </c>
       <c r="G78" t="n">
-        <v>87.23281097412109</v>
+        <v>87.23281860351562</v>
       </c>
       <c r="H78" t="n">
         <v>40.21850204467773</v>
@@ -4051,10 +4051,10 @@
         <v>21.78674507141113</v>
       </c>
       <c r="J78" t="n">
-        <v>24.70989990234375</v>
+        <v>24.70990180969238</v>
       </c>
       <c r="K78" t="n">
-        <v>606.6740112304688</v>
+        <v>606.674072265625</v>
       </c>
       <c r="L78" t="n">
         <v>139.6772003173828</v>
@@ -4083,7 +4083,7 @@
         <v>70.04000091552734</v>
       </c>
       <c r="G79" t="n">
-        <v>87.61949157714844</v>
+        <v>87.61948394775391</v>
       </c>
       <c r="H79" t="n">
         <v>40.39383316040039</v>
@@ -4136,10 +4136,10 @@
         <v>24.97266960144043</v>
       </c>
       <c r="K80" t="n">
-        <v>616.996337890625</v>
+        <v>616.9962768554688</v>
       </c>
       <c r="L80" t="n">
-        <v>142.5458374023438</v>
+        <v>142.5458526611328</v>
       </c>
       <c r="M80" t="n">
         <v>677.7747192382812</v>
@@ -4150,7 +4150,7 @@
         <v>45992</v>
       </c>
       <c r="B81" t="n">
-        <v>44.65811920166016</v>
+        <v>44.65811538696289</v>
       </c>
       <c r="C81" t="n">
         <v>52.52000045776367</v>
@@ -4165,7 +4165,7 @@
         <v>71.05999755859375</v>
       </c>
       <c r="G81" t="n">
-        <v>86.11824035644531</v>
+        <v>86.11823272705078</v>
       </c>
       <c r="H81" t="n">
         <v>40.0236930847168</v>
@@ -4183,7 +4183,7 @@
         <v>142.610595703125</v>
       </c>
       <c r="M81" t="n">
-        <v>674.6802978515625</v>
+        <v>674.6803588867188</v>
       </c>
     </row>
     <row r="82">
@@ -4206,7 +4206,7 @@
         <v>70.19999694824219</v>
       </c>
       <c r="G82" t="n">
-        <v>86.15704345703125</v>
+        <v>86.15703582763672</v>
       </c>
       <c r="H82" t="n">
         <v>39.92628860473633</v>
@@ -4215,10 +4215,10 @@
         <v>22.27046585083008</v>
       </c>
       <c r="J82" t="n">
-        <v>24.70989990234375</v>
+        <v>24.70990180969238</v>
       </c>
       <c r="K82" t="n">
-        <v>619.736328125</v>
+        <v>619.7362670898438</v>
       </c>
       <c r="L82" t="n">
         <v>144.0797729492188</v>
@@ -4247,7 +4247,7 @@
         <v>70.66000366210938</v>
       </c>
       <c r="G83" t="n">
-        <v>86.39958190917969</v>
+        <v>86.39958953857422</v>
       </c>
       <c r="H83" t="n">
         <v>40.00421142578125</v>
@@ -4259,7 +4259,7 @@
         <v>24.73909759521484</v>
       </c>
       <c r="K83" t="n">
-        <v>621.2507934570312</v>
+        <v>621.250732421875</v>
       </c>
       <c r="L83" t="n">
         <v>144.4234161376953</v>
@@ -4288,7 +4288,7 @@
         <v>71.38999938964844</v>
       </c>
       <c r="G84" t="n">
-        <v>85.93392181396484</v>
+        <v>85.93391418457031</v>
       </c>
       <c r="H84" t="n">
         <v>39.93602752685547</v>
@@ -4314,7 +4314,7 @@
         <v>45996</v>
       </c>
       <c r="B85" t="n">
-        <v>44.91241073608398</v>
+        <v>44.91240692138672</v>
       </c>
       <c r="C85" t="n">
         <v>52.95000076293945</v>
@@ -4344,7 +4344,7 @@
         <v>623.20361328125</v>
       </c>
       <c r="L85" t="n">
-        <v>146.0220947265625</v>
+        <v>146.0221099853516</v>
       </c>
       <c r="M85" t="n">
         <v>680.0557861328125</v>
@@ -4382,7 +4382,7 @@
         <v>24.3692798614502</v>
       </c>
       <c r="K86" t="n">
-        <v>622.008056640625</v>
+        <v>622.0079956054688</v>
       </c>
       <c r="L86" t="n">
         <v>147.0480346679688</v>
@@ -4411,7 +4411,7 @@
         <v>69.86000061035156</v>
       </c>
       <c r="G87" t="n">
-        <v>85.3421630859375</v>
+        <v>85.34214019775391</v>
       </c>
       <c r="H87" t="n">
         <v>39.44900512695312</v>
@@ -4423,13 +4423,13 @@
         <v>24.28168869018555</v>
       </c>
       <c r="K87" t="n">
-        <v>622.7752075195312</v>
+        <v>622.775146484375</v>
       </c>
       <c r="L87" t="n">
         <v>147.4364929199219</v>
       </c>
       <c r="M87" t="n">
-        <v>677.4276123046875</v>
+        <v>677.4275512695312</v>
       </c>
     </row>
     <row r="88">
@@ -4437,7 +4437,7 @@
         <v>46001</v>
       </c>
       <c r="B88" t="n">
-        <v>45.16670989990234</v>
+        <v>45.16670608520508</v>
       </c>
       <c r="C88" t="n">
         <v>56.06999969482422</v>
@@ -4452,7 +4452,7 @@
         <v>70.54000091552734</v>
       </c>
       <c r="G88" t="n">
-        <v>85.67198944091797</v>
+        <v>85.67198181152344</v>
       </c>
       <c r="H88" t="n">
         <v>39.52692794799805</v>
@@ -4461,13 +4461,13 @@
         <v>22.37688255310059</v>
       </c>
       <c r="J88" t="n">
-        <v>24.37900924682617</v>
+        <v>24.37900733947754</v>
       </c>
       <c r="K88" t="n">
         <v>625.3258666992188</v>
       </c>
       <c r="L88" t="n">
-        <v>148.1436920166016</v>
+        <v>148.1437072753906</v>
       </c>
       <c r="M88" t="n">
         <v>681.92041015625</v>
@@ -4493,7 +4493,7 @@
         <v>69.25</v>
       </c>
       <c r="G89" t="n">
-        <v>85.55557250976562</v>
+        <v>85.55558013916016</v>
       </c>
       <c r="H89" t="n">
         <v>39.74121475219727</v>
@@ -4502,7 +4502,7 @@
         <v>22.35753440856934</v>
       </c>
       <c r="J89" t="n">
-        <v>24.44713401794434</v>
+        <v>24.44713592529297</v>
       </c>
       <c r="K89" t="n">
         <v>623.3032836914062</v>
@@ -4511,7 +4511,7 @@
         <v>147.3866882324219</v>
       </c>
       <c r="M89" t="n">
-        <v>683.5072631835938</v>
+        <v>683.5072021484375</v>
       </c>
     </row>
     <row r="90">
@@ -4552,7 +4552,7 @@
         <v>143.1235656738281</v>
       </c>
       <c r="M90" t="n">
-        <v>676.1581420898438</v>
+        <v>676.1580810546875</v>
       </c>
     </row>
     <row r="91">
@@ -4628,10 +4628,10 @@
         <v>24.42554473876953</v>
       </c>
       <c r="K92" t="n">
-        <v>609.5236206054688</v>
+        <v>609.5235595703125</v>
       </c>
       <c r="L92" t="n">
-        <v>141.9980163574219</v>
+        <v>141.9980010986328</v>
       </c>
       <c r="M92" t="n">
         <v>673.2918701171875</v>
@@ -4642,7 +4642,7 @@
         <v>46008</v>
       </c>
       <c r="B93" t="n">
-        <v>43.79742813110352</v>
+        <v>43.79742431640625</v>
       </c>
       <c r="C93" t="n">
         <v>60.2599983215332</v>
@@ -4657,7 +4657,7 @@
         <v>67.98000335693359</v>
       </c>
       <c r="G93" t="n">
-        <v>85.17723846435547</v>
+        <v>85.17723083496094</v>
       </c>
       <c r="H93" t="n">
         <v>39.67303466796875</v>
@@ -4669,7 +4669,7 @@
         <v>24.49471092224121</v>
       </c>
       <c r="K93" t="n">
-        <v>598.2247924804688</v>
+        <v>598.224853515625</v>
       </c>
       <c r="L93" t="n">
         <v>138.8405151367188</v>
@@ -4739,7 +4739,7 @@
         <v>68.02999877929688</v>
       </c>
       <c r="G95" t="n">
-        <v>85.26524353027344</v>
+        <v>85.26523590087891</v>
       </c>
       <c r="H95" t="n">
         <v>39.28341674804688</v>
@@ -4751,7 +4751,7 @@
         <v>24.41566276550293</v>
       </c>
       <c r="K95" t="n">
-        <v>614.8042602539062</v>
+        <v>614.8043212890625</v>
       </c>
       <c r="L95" t="n">
         <v>144.0299835205078</v>
@@ -4780,7 +4780,7 @@
         <v>69.73000335693359</v>
       </c>
       <c r="G96" t="n">
-        <v>85.0802001953125</v>
+        <v>85.08018493652344</v>
       </c>
       <c r="H96" t="n">
         <v>39.57487869262695</v>
@@ -4795,7 +4795,7 @@
         <v>617.7513427734375</v>
       </c>
       <c r="L96" t="n">
-        <v>144.8070678710938</v>
+        <v>144.8070831298828</v>
       </c>
       <c r="M96" t="n">
         <v>681.2098388671875</v>
@@ -4836,7 +4836,7 @@
         <v>620.6444702148438</v>
       </c>
       <c r="L97" t="n">
-        <v>145.5951538085938</v>
+        <v>145.5951385498047</v>
       </c>
       <c r="M97" t="n">
         <v>684.3233032226562</v>
@@ -4862,7 +4862,7 @@
         <v>70.19999694824219</v>
       </c>
       <c r="G98" t="n">
-        <v>85.73271179199219</v>
+        <v>85.73270416259766</v>
       </c>
       <c r="H98" t="n">
         <v>39.8210563659668</v>
@@ -4874,7 +4874,7 @@
         <v>24.70220947265625</v>
       </c>
       <c r="K98" t="n">
-        <v>622.460205078125</v>
+        <v>622.4602661132812</v>
       </c>
       <c r="L98" t="n">
         <v>145.9443054199219</v>
@@ -4903,7 +4903,7 @@
         <v>68.48000335693359</v>
       </c>
       <c r="G99" t="n">
-        <v>85.45027923583984</v>
+        <v>85.45028686523438</v>
       </c>
       <c r="H99" t="n">
         <v>39.89983367919922</v>
@@ -4915,7 +4915,7 @@
         <v>24.74173545837402</v>
       </c>
       <c r="K99" t="n">
-        <v>622.4203491210938</v>
+        <v>622.4202880859375</v>
       </c>
       <c r="L99" t="n">
         <v>146.1737365722656</v>
@@ -5067,7 +5067,7 @@
         <v>68.95999908447266</v>
       </c>
       <c r="G103" t="n">
-        <v>84.75879669189453</v>
+        <v>84.75880432128906</v>
       </c>
       <c r="H103" t="n">
         <v>39.76197814941406</v>
@@ -5079,7 +5079,7 @@
         <v>24.72197151184082</v>
       </c>
       <c r="K103" t="n">
-        <v>611.6756591796875</v>
+        <v>611.6757202148438</v>
       </c>
       <c r="L103" t="n">
         <v>143.9491577148438</v>
@@ -5190,7 +5190,7 @@
         <v>67.79000091552734</v>
       </c>
       <c r="G106" t="n">
-        <v>85.49896240234375</v>
+        <v>85.49897003173828</v>
       </c>
       <c r="H106" t="n">
         <v>39.5256462097168</v>
@@ -5272,7 +5272,7 @@
         <v>70.77999877929688</v>
       </c>
       <c r="G108" t="n">
-        <v>85.63532257080078</v>
+        <v>85.63533020019531</v>
       </c>
       <c r="H108" t="n">
         <v>39.88014221191406</v>
@@ -5313,7 +5313,7 @@
         <v>71.65000152587891</v>
       </c>
       <c r="G109" t="n">
-        <v>85.38210296630859</v>
+        <v>85.38211059570312</v>
       </c>
       <c r="H109" t="n">
         <v>39.99829864501953</v>
@@ -5354,7 +5354,7 @@
         <v>73.48000335693359</v>
       </c>
       <c r="G110" t="n">
-        <v>85.5281982421875</v>
+        <v>85.52819061279297</v>
       </c>
       <c r="H110" t="n">
         <v>40.30355453491211</v>
@@ -5436,7 +5436,7 @@
         <v>71.12999725341797</v>
       </c>
       <c r="G112" t="n">
-        <v>86.00540161132812</v>
+        <v>86.00538635253906</v>
       </c>
       <c r="H112" t="n">
         <v>41.06177520751953</v>
@@ -5477,7 +5477,7 @@
         <v>71.65000152587891</v>
       </c>
       <c r="G113" t="n">
-        <v>85.50872039794922</v>
+        <v>85.50871276855469</v>
       </c>
       <c r="H113" t="n">
         <v>41.56396865844727</v>
@@ -5518,7 +5518,7 @@
         <v>71.86000061035156</v>
       </c>
       <c r="G114" t="n">
-        <v>84.38872528076172</v>
+        <v>84.38871765136719</v>
       </c>
       <c r="H114" t="n">
         <v>40.76636505126953</v>
@@ -5533,7 +5533,7 @@
         <v>606.6276245117188</v>
       </c>
       <c r="L114" t="n">
-        <v>141.4951477050781</v>
+        <v>141.4951324462891</v>
       </c>
       <c r="M114" t="n">
         <v>673.9981689453125</v>
@@ -5574,7 +5574,7 @@
         <v>614.8282470703125</v>
       </c>
       <c r="L115" t="n">
-        <v>143.4603424072266</v>
+        <v>143.4603576660156</v>
       </c>
       <c r="M115" t="n">
         <v>681.77685546875</v>
@@ -5600,7 +5600,7 @@
         <v>71.81999969482422</v>
       </c>
       <c r="G116" t="n">
-        <v>85.40158081054688</v>
+        <v>85.40158843994141</v>
       </c>
       <c r="H116" t="n">
         <v>40.51034164428711</v>
@@ -5641,7 +5641,7 @@
         <v>73.94999694824219</v>
       </c>
       <c r="G117" t="n">
-        <v>85.63532257080078</v>
+        <v>85.63533020019531</v>
       </c>
       <c r="H117" t="n">
         <v>40.61865997314453</v>
@@ -5682,7 +5682,7 @@
         <v>73.48000335693359</v>
       </c>
       <c r="G118" t="n">
-        <v>86.04436492919922</v>
+        <v>86.04435729980469</v>
       </c>
       <c r="H118" t="n">
         <v>40.58911895751953</v>
@@ -5723,7 +5723,7 @@
         <v>75.66000366210938</v>
       </c>
       <c r="G119" t="n">
-        <v>85.50872039794922</v>
+        <v>85.50871276855469</v>
       </c>
       <c r="H119" t="n">
         <v>40.61865997314453</v>
@@ -5738,7 +5738,7 @@
         <v>629.6432495117188</v>
       </c>
       <c r="L119" t="n">
-        <v>147.6900482177734</v>
+        <v>147.6900634765625</v>
       </c>
       <c r="M119" t="n">
         <v>691.8134765625</v>
@@ -5776,7 +5776,7 @@
         <v>25.07768249511719</v>
       </c>
       <c r="K120" t="n">
-        <v>631.728271484375</v>
+        <v>631.7283325195312</v>
       </c>
       <c r="L120" t="n">
         <v>148.8671722412109</v>
@@ -5817,10 +5817,10 @@
         <v>25.41363143920898</v>
       </c>
       <c r="K121" t="n">
-        <v>627.9472045898438</v>
+        <v>627.947265625</v>
       </c>
       <c r="L121" t="n">
-        <v>146.5129089355469</v>
+        <v>146.5129241943359</v>
       </c>
       <c r="M121" t="n">
         <v>690.3711547851562</v>
@@ -5846,7 +5846,7 @@
         <v>79.51999664306641</v>
       </c>
       <c r="G122" t="n">
-        <v>84.85618591308594</v>
+        <v>84.85619354248047</v>
       </c>
       <c r="H122" t="n">
         <v>40.79590606689453</v>
@@ -5858,7 +5858,7 @@
         <v>25.36422729492188</v>
       </c>
       <c r="K122" t="n">
-        <v>620.405029296875</v>
+        <v>620.4050903320312</v>
       </c>
       <c r="L122" t="n">
         <v>143.5301971435547</v>
@@ -5887,7 +5887,7 @@
         <v>75.33000183105469</v>
       </c>
       <c r="G123" t="n">
-        <v>84.61375427246094</v>
+        <v>84.61374664306641</v>
       </c>
       <c r="H123" t="n">
         <v>40.33309555053711</v>
@@ -5928,7 +5928,7 @@
         <v>77.47000122070312</v>
       </c>
       <c r="G124" t="n">
-        <v>84.81904602050781</v>
+        <v>84.81905364990234</v>
       </c>
       <c r="H124" t="n">
         <v>40.18539810180664</v>
@@ -5943,7 +5943,7 @@
         <v>615.0676879882812</v>
       </c>
       <c r="L124" t="n">
-        <v>141.7345581054688</v>
+        <v>141.7345733642578</v>
       </c>
       <c r="M124" t="n">
         <v>685.885009765625</v>
@@ -5981,10 +5981,10 @@
         <v>25.61124992370605</v>
       </c>
       <c r="K125" t="n">
-        <v>604.322998046875</v>
+        <v>604.3230590820312</v>
       </c>
       <c r="L125" t="n">
-        <v>137.7841796875</v>
+        <v>137.7841949462891</v>
       </c>
       <c r="M125" t="n">
         <v>682.5626831054688</v>
@@ -6022,7 +6022,7 @@
         <v>25.61124992370605</v>
       </c>
       <c r="K126" t="n">
-        <v>595.6235961914062</v>
+        <v>595.6236572265625</v>
       </c>
       <c r="L126" t="n">
         <v>135.3002471923828</v>
@@ -6051,7 +6051,7 @@
         <v>76.98999786376953</v>
       </c>
       <c r="G127" t="n">
-        <v>85.58158874511719</v>
+        <v>85.58159637451172</v>
       </c>
       <c r="H127" t="n">
         <v>41.34733581542969</v>
@@ -6066,7 +6066,7 @@
         <v>608.2138671875</v>
       </c>
       <c r="L127" t="n">
-        <v>140.786865234375</v>
+        <v>140.7868804931641</v>
       </c>
       <c r="M127" t="n">
         <v>686.96923828125</v>
@@ -6092,7 +6092,7 @@
         <v>78.01999664306641</v>
       </c>
       <c r="G128" t="n">
-        <v>85.56204223632812</v>
+        <v>85.56203460693359</v>
       </c>
       <c r="H128" t="n">
         <v>41.60335159301758</v>
@@ -6256,7 +6256,7 @@
         <v>76.22000122070312</v>
       </c>
       <c r="G132" t="n">
-        <v>87.71283721923828</v>
+        <v>87.71282958984375</v>
       </c>
       <c r="H132" t="n">
         <v>42.83422470092773</v>
@@ -6268,7 +6268,7 @@
         <v>26.65862464904785</v>
       </c>
       <c r="K132" t="n">
-        <v>600.5020141601562</v>
+        <v>600.5020751953125</v>
       </c>
       <c r="L132" t="n">
         <v>139.2206878662109</v>
@@ -6297,7 +6297,7 @@
         <v>75.73000335693359</v>
       </c>
       <c r="G133" t="n">
-        <v>87.85946655273438</v>
+        <v>87.85947418212891</v>
       </c>
       <c r="H133" t="n">
         <v>43.26748657226562</v>
@@ -6312,7 +6312,7 @@
         <v>599.8834838867188</v>
       </c>
       <c r="L133" t="n">
-        <v>139.1408843994141</v>
+        <v>139.140869140625</v>
       </c>
       <c r="M133" t="n">
         <v>679.2402954101562</v>
@@ -6350,7 +6350,7 @@
         <v>26.57957649230957</v>
       </c>
       <c r="K134" t="n">
-        <v>604.3629760742188</v>
+        <v>604.3629150390625</v>
       </c>
       <c r="L134" t="n">
         <v>140.5674133300781</v>
@@ -6379,7 +6379,7 @@
         <v>81.19000244140625</v>
       </c>
       <c r="G135" t="n">
-        <v>87.61505889892578</v>
+        <v>87.61507415771484</v>
       </c>
       <c r="H135" t="n">
         <v>42.53881454467773</v>
@@ -6391,7 +6391,7 @@
         <v>26.54005432128906</v>
       </c>
       <c r="K135" t="n">
-        <v>602.04833984375</v>
+        <v>602.0484008789062</v>
       </c>
       <c r="L135" t="n">
         <v>139.8691101074219</v>
@@ -6420,7 +6420,7 @@
         <v>80.84999847412109</v>
       </c>
       <c r="G136" t="n">
-        <v>87.40975952148438</v>
+        <v>87.40976715087891</v>
       </c>
       <c r="H136" t="n">
         <v>42.89330291748047</v>
@@ -6432,10 +6432,10 @@
         <v>26.7376708984375</v>
       </c>
       <c r="K136" t="n">
-        <v>607.3757934570312</v>
+        <v>607.3758544921875</v>
       </c>
       <c r="L136" t="n">
-        <v>140.5374908447266</v>
+        <v>140.5374755859375</v>
       </c>
       <c r="M136" t="n">
         <v>685.7855834960938</v>
@@ -6461,7 +6461,7 @@
         <v>80.90000152587891</v>
       </c>
       <c r="G137" t="n">
-        <v>87.73238372802734</v>
+        <v>87.73237609863281</v>
       </c>
       <c r="H137" t="n">
         <v>42.94254302978516</v>
@@ -6476,7 +6476,7 @@
         <v>599.9932250976562</v>
       </c>
       <c r="L137" t="n">
-        <v>138.1832275390625</v>
+        <v>138.1832122802734</v>
       </c>
       <c r="M137" t="n">
         <v>678.7827758789062</v>
@@ -6502,7 +6502,7 @@
         <v>80.76000213623047</v>
       </c>
       <c r="G138" t="n">
-        <v>87.88881683349609</v>
+        <v>87.88880157470703</v>
       </c>
       <c r="H138" t="n">
         <v>43.06069946289062</v>
@@ -6543,7 +6543,7 @@
         <v>79.73000335693359</v>
       </c>
       <c r="G139" t="n">
-        <v>87.89857482910156</v>
+        <v>87.89858245849609</v>
       </c>
       <c r="H139" t="n">
         <v>42.77514266967773</v>
@@ -6584,7 +6584,7 @@
         <v>79.76999664306641</v>
       </c>
       <c r="G140" t="n">
-        <v>88.25052642822266</v>
+        <v>88.25051879882812</v>
       </c>
       <c r="H140" t="n">
         <v>42.96223449707031</v>
@@ -6625,7 +6625,7 @@
         <v>81.94999694824219</v>
       </c>
       <c r="G141" t="n">
-        <v>88.78822326660156</v>
+        <v>88.78821563720703</v>
       </c>
       <c r="H141" t="n">
         <v>43.16902160644531</v>
@@ -6637,10 +6637,10 @@
         <v>26.9254093170166</v>
       </c>
       <c r="K141" t="n">
-        <v>605.8594360351562</v>
+        <v>605.859375</v>
       </c>
       <c r="L141" t="n">
-        <v>138.4226226806641</v>
+        <v>138.4226379394531</v>
       </c>
       <c r="M141" t="n">
         <v>682.3637084960938</v>
@@ -6707,7 +6707,7 @@
         <v>90.19999694824219</v>
       </c>
       <c r="G143" t="n">
-        <v>87.72003936767578</v>
+        <v>87.72004699707031</v>
       </c>
       <c r="H143" t="n">
         <v>43.03116607666016</v>
@@ -6719,7 +6719,7 @@
         <v>26.5696964263916</v>
       </c>
       <c r="K143" t="n">
-        <v>600.162841796875</v>
+        <v>600.1629028320312</v>
       </c>
       <c r="L143" t="n">
         <v>137.1656951904297</v>
@@ -6748,7 +6748,7 @@
         <v>91.55999755859375</v>
       </c>
       <c r="G144" t="n">
-        <v>87.44539642333984</v>
+        <v>87.44538879394531</v>
       </c>
       <c r="H144" t="n">
         <v>43.09024047851562</v>
@@ -6760,7 +6760,7 @@
         <v>26.59934043884277</v>
       </c>
       <c r="K144" t="n">
-        <v>609.3112182617188</v>
+        <v>609.311279296875</v>
       </c>
       <c r="L144" t="n">
         <v>139.5</v>
@@ -6801,7 +6801,7 @@
         <v>26.35231781005859</v>
       </c>
       <c r="K145" t="n">
-        <v>607.4755859375</v>
+        <v>607.4755249023438</v>
       </c>
       <c r="L145" t="n">
         <v>139.8391723632812</v>
@@ -6830,7 +6830,7 @@
         <v>108.7699966430664</v>
       </c>
       <c r="G146" t="n">
-        <v>86.76857757568359</v>
+        <v>86.76859283447266</v>
       </c>
       <c r="H146" t="n">
         <v>42.23355865478516</v>
@@ -6845,7 +6845,7 @@
         <v>598.337158203125</v>
       </c>
       <c r="L146" t="n">
-        <v>136.9562072753906</v>
+        <v>136.9561920166016</v>
       </c>
       <c r="M146" t="n">
         <v>668.8256225585938</v>
@@ -6871,7 +6871,7 @@
         <v>104.3300018310547</v>
       </c>
       <c r="G147" t="n">
-        <v>87.52387237548828</v>
+        <v>87.52386474609375</v>
       </c>
       <c r="H147" t="n">
         <v>42.32218170166016</v>
@@ -6912,7 +6912,7 @@
         <v>105.8600006103516</v>
       </c>
       <c r="G148" t="n">
-        <v>86.59202575683594</v>
+        <v>86.59203338623047</v>
       </c>
       <c r="H148" t="n">
         <v>42.26309967041016</v>
@@ -6965,7 +6965,7 @@
         <v>25.86815452575684</v>
       </c>
       <c r="K149" t="n">
-        <v>606.2584228515625</v>
+        <v>606.2584838867188</v>
       </c>
       <c r="L149" t="n">
         <v>140.0885620117188</v>
@@ -6994,7 +6994,7 @@
         <v>118.3899993896484</v>
       </c>
       <c r="G150" t="n">
-        <v>85.30707550048828</v>
+        <v>85.30708312988281</v>
       </c>
       <c r="H150" t="n">
         <v>41.49503707885742</v>
@@ -7006,7 +7006,7 @@
         <v>25.68041610717773</v>
       </c>
       <c r="K150" t="n">
-        <v>595.85302734375</v>
+        <v>595.8530883789062</v>
       </c>
       <c r="L150" t="n">
         <v>137.5048675537109</v>
@@ -7076,7 +7076,7 @@
         <v>115.0299987792969</v>
       </c>
       <c r="G152" t="n">
-        <v>85.54249572753906</v>
+        <v>85.54248809814453</v>
       </c>
       <c r="H152" t="n">
         <v>41.92830657958984</v>
@@ -7091,7 +7091,7 @@
         <v>598.9656982421875</v>
       </c>
       <c r="L152" t="n">
-        <v>138.4425964355469</v>
+        <v>138.4425811767578</v>
       </c>
       <c r="M152" t="n">
         <v>665.493408203125</v>
@@ -7173,7 +7173,7 @@
         <v>593.4986572265625</v>
       </c>
       <c r="L154" t="n">
-        <v>137.6245727539062</v>
+        <v>137.6245880126953</v>
       </c>
       <c r="M154" t="n">
         <v>657.9335327148438</v>
@@ -7199,7 +7199,7 @@
         <v>117.3600006103516</v>
       </c>
       <c r="G155" t="n">
-        <v>85.81713104248047</v>
+        <v>85.817138671875</v>
       </c>
       <c r="H155" t="n">
         <v>41.27840423583984</v>
@@ -7240,7 +7240,7 @@
         <v>121.4300003051758</v>
       </c>
       <c r="G156" t="n">
-        <v>84.18888854980469</v>
+        <v>84.18887329101562</v>
       </c>
       <c r="H156" t="n">
         <v>39.9687614440918</v>
@@ -7445,7 +7445,7 @@
         <v>124.1999969482422</v>
       </c>
       <c r="G161" t="n">
-        <v>84.00250244140625</v>
+        <v>84.00251007080078</v>
       </c>
       <c r="H161" t="n">
         <v>39.66244125366211</v>
@@ -7527,7 +7527,7 @@
         <v>127.25</v>
       </c>
       <c r="G163" t="n">
-        <v>85.03244018554688</v>
+        <v>85.03242492675781</v>
       </c>
       <c r="H163" t="n">
         <v>40.47532272338867</v>
@@ -7855,7 +7855,7 @@
         <v>128.4700012207031</v>
       </c>
       <c r="G171" t="n">
-        <v>85.4312744140625</v>
+        <v>85.43128204345703</v>
       </c>
       <c r="H171" t="n">
         <v>42.64629745483398</v>
@@ -8019,7 +8019,7 @@
         <v>116.0400009155273</v>
       </c>
       <c r="G175" t="n">
-        <v>85.74641418457031</v>
+        <v>85.74640655517578</v>
       </c>
       <c r="H175" t="n">
         <v>44.09361267089844</v>
@@ -8101,7 +8101,7 @@
         <v>128.25</v>
       </c>
       <c r="G177" t="n">
-        <v>85.25401306152344</v>
+        <v>85.25400543212891</v>
       </c>
       <c r="H177" t="n">
         <v>43.39969253540039</v>
@@ -8183,7 +8183,7 @@
         <v>134.7200012207031</v>
       </c>
       <c r="G179" t="n">
-        <v>85.23432159423828</v>
+        <v>85.23431396484375</v>
       </c>
       <c r="H179" t="n">
         <v>43.57813262939453</v>
@@ -8224,7 +8224,7 @@
         <v>132.3999938964844</v>
       </c>
       <c r="G180" t="n">
-        <v>85.39187622070312</v>
+        <v>85.39188385009766</v>
       </c>
       <c r="H180" t="n">
         <v>43.44926452636719</v>
@@ -8306,7 +8306,7 @@
         <v>139.6000061035156</v>
       </c>
       <c r="G182" t="n">
-        <v>85.05705261230469</v>
+        <v>85.05706024169922</v>
       </c>
       <c r="H182" t="n">
         <v>43.528564453125</v>
@@ -8388,7 +8388,7 @@
         <v>147.0899963378906</v>
       </c>
       <c r="G184" t="n">
-        <v>84.31845092773438</v>
+        <v>84.31845855712891</v>
       </c>
       <c r="H184" t="n">
         <v>44.01431274414062</v>
@@ -8429,7 +8429,7 @@
         <v>142.8000030517578</v>
       </c>
       <c r="G185" t="n">
-        <v>84.61993408203125</v>
+        <v>84.61992645263672</v>
       </c>
       <c r="H185" t="n">
         <v>43.93500518798828</v>
@@ -8552,7 +8552,7 @@
         <v>133.9499969482422</v>
       </c>
       <c r="G188" t="n">
-        <v>85.08448791503906</v>
+        <v>85.08449554443359</v>
       </c>
       <c r="H188" t="n">
         <v>44.35135650634766</v>
@@ -8634,7 +8634,7 @@
         <v>133.5899963378906</v>
       </c>
       <c r="G190" t="n">
-        <v>85.08448791503906</v>
+        <v>85.08449554443359</v>
       </c>
       <c r="H190" t="n">
         <v>44.02422332763672</v>
@@ -8716,7 +8716,7 @@
         <v>144.3000030517578</v>
       </c>
       <c r="G192" t="n">
-        <v>84.00709533691406</v>
+        <v>84.00708770751953</v>
       </c>
       <c r="H192" t="n">
         <v>44.1927490234375</v>
@@ -8839,7 +8839,7 @@
         <v>148.2299957275391</v>
       </c>
       <c r="G195" t="n">
-        <v>82.69247436523438</v>
+        <v>82.69248199462891</v>
       </c>
       <c r="H195" t="n">
         <v>42.85447311401367</v>
@@ -8962,7 +8962,7 @@
         <v>144.2700042724609</v>
       </c>
       <c r="G198" t="n">
-        <v>82.93959045410156</v>
+        <v>82.93958282470703</v>
       </c>
       <c r="H198" t="n">
         <v>44.04404830932617</v>
@@ -9126,7 +9126,7 @@
         <v>131.0299987792969</v>
       </c>
       <c r="G202" t="n">
-        <v>84.31351470947266</v>
+        <v>84.31350708007812</v>
       </c>
       <c r="H202" t="n">
         <v>44.24231338500977</v>
@@ -9249,7 +9249,7 @@
         <v>135.5</v>
       </c>
       <c r="G205" t="n">
-        <v>84.81383514404297</v>
+        <v>84.8138427734375</v>
       </c>
       <c r="H205" t="n">
         <v>42.89412689208984</v>
@@ -9290,7 +9290,7 @@
         <v>137.2700042724609</v>
       </c>
       <c r="G206" t="n">
-        <v>84.99246215820312</v>
+        <v>84.99245452880859</v>
       </c>
       <c r="H206" t="n">
         <v>43.11221694946289</v>
@@ -9577,7 +9577,7 @@
         <v>128.8300018310547</v>
       </c>
       <c r="G213" t="n">
-        <v>85.31992340087891</v>
+        <v>85.31993103027344</v>
       </c>
       <c r="H213" t="n">
         <v>44.52978897094727</v>
@@ -9823,7 +9823,7 @@
         <v>112.6900024414062</v>
       </c>
       <c r="G219" t="n">
-        <v>85.42906951904297</v>
+        <v>85.4290771484375</v>
       </c>
       <c r="H219" t="n">
         <v>44.02000045776367</v>
@@ -10028,7 +10028,7 @@
         <v>107.0800018310547</v>
       </c>
       <c r="G224" t="n">
-        <v>86.77863311767578</v>
+        <v>86.77864074707031</v>
       </c>
       <c r="H224" t="n">
         <v>44.91999816894531</v>
@@ -11283,13 +11283,13 @@
         <v>45880</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.008006624204152102</v>
+        <v>-0.008006531573486519</v>
       </c>
       <c r="C2" t="n">
         <v>-0.02006882859815462</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.006624553158330659</v>
+        <v>-0.006624642141811021</v>
       </c>
       <c r="E2" t="n">
         <v>-0.01437470108759764</v>
@@ -11298,19 +11298,19 @@
         <v>0.006821282117095429</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001145756286897726</v>
+        <v>0.001145664987046491</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.005818114956392617</v>
+        <v>-0.005818305731641993</v>
       </c>
       <c r="I2" t="n">
         <v>0.001373670393670201</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.004854367767266776</v>
+        <v>-0.004854447748282475</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.002958912426759719</v>
+        <v>-0.002959018853778028</v>
       </c>
       <c r="L2" t="n">
         <v>-0.006769128041570927</v>
@@ -11324,13 +11324,13 @@
         <v>45881</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004866410654465136</v>
+        <v>0.004866410200047966</v>
       </c>
       <c r="C3" t="n">
         <v>0.006729067881298345</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005651495387596572</v>
+        <v>0.005651585470735077</v>
       </c>
       <c r="E3" t="n">
         <v>-0.0009074665058316222</v>
@@ -11339,16 +11339,16 @@
         <v>-0.01151769740333874</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.005035101640139872</v>
+        <v>-0.005035102559549309</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001706949185569018</v>
+        <v>0.001707045575614963</v>
       </c>
       <c r="I3" t="n">
         <v>-0.004115177739006048</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005284564966545835</v>
+        <v>0.005284565391272533</v>
       </c>
       <c r="K3" t="n">
         <v>0.01256880322403719</v>
@@ -11357,7 +11357,7 @@
         <v>0.01548533416745057</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01064598076961532</v>
+        <v>0.0106460778123918</v>
       </c>
     </row>
     <row r="4">
@@ -11365,13 +11365,13 @@
         <v>45882</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01157571060584095</v>
+        <v>0.01157561660407014</v>
       </c>
       <c r="C4" t="n">
         <v>0.01714618294693948</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009329022770301343</v>
+        <v>0.009328933696812536</v>
       </c>
       <c r="E4" t="n">
         <v>0.003049283014586734</v>
@@ -11380,7 +11380,7 @@
         <v>-0.006716900401204762</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00828078582769054</v>
+        <v>0.008280970871434423</v>
       </c>
       <c r="H4" t="n">
         <v>0.006572453084371821</v>
@@ -11389,16 +11389,16 @@
         <v>-0.001377454481859552</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009300429124502019</v>
+        <v>0.009300429868059013</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005000006872497575</v>
+        <v>0.0005001064179936954</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003729916953587598</v>
+        <v>0.0003731060749034842</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003423228406564061</v>
+        <v>0.003423132057329248</v>
       </c>
     </row>
     <row r="5">
@@ -11412,7 +11412,7 @@
         <v>-0.01428571428571423</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.007126997951448111</v>
+        <v>-0.007126910330198744</v>
       </c>
       <c r="E5" t="n">
         <v>-0.006338706734070332</v>
@@ -11430,13 +11430,13 @@
         <v>0.004137882148359306</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.006810803403421439</v>
+        <v>-0.006810803942918553</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0007752531091496095</v>
+        <v>-0.000775464383009683</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.002161539056969808</v>
+        <v>-0.002161767483596089</v>
       </c>
       <c r="M5" t="n">
         <v>9.291786892906551e-05</v>
@@ -11471,13 +11471,13 @@
         <v>-0.003205110555777324</v>
       </c>
       <c r="J6" t="n">
-        <v>0.004033776950167267</v>
+        <v>0.004033857027052612</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.004397496451755467</v>
+        <v>-0.004397285397021111</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.007582405217356647</v>
+        <v>-0.007582291501593286</v>
       </c>
       <c r="M6" t="n">
         <v>-0.002341197926334693</v>
@@ -11488,13 +11488,13 @@
         <v>45887</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.00596075210647351</v>
+        <v>-0.005960660157870223</v>
       </c>
       <c r="C7" t="n">
         <v>0.001449253248131832</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.008475376168337045</v>
+        <v>-0.008475464546486622</v>
       </c>
       <c r="E7" t="n">
         <v>-0.001561267541180356</v>
@@ -11506,7 +11506,7 @@
         <v>-0.002893573135259508</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.00943626731364422</v>
+        <v>-0.009436171832891471</v>
       </c>
       <c r="I7" t="n">
         <v>0.0009187550646996279</v>
@@ -11515,7 +11515,7 @@
         <v>-0.007633599307329098</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0003984575835475068</v>
+        <v>-0.0003985637682377696</v>
       </c>
       <c r="L7" t="n">
         <v>0.002145247578081211</v>
@@ -11529,13 +11529,13 @@
         <v>45888</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0003527023959528641</v>
+        <v>0.0003526098633637176</v>
       </c>
       <c r="C8" t="n">
         <v>-0.0196816301068502</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01720830921155536</v>
+        <v>0.01720839987899225</v>
       </c>
       <c r="E8" t="n">
         <v>-0.005473279447945512</v>
@@ -11544,16 +11544,16 @@
         <v>-0.01189005246629538</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005803940396529095</v>
+        <v>0.005803847782429372</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01783085928305272</v>
+        <v>0.01783085756433067</v>
       </c>
       <c r="I8" t="n">
         <v>-0.007801752057791655</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01417002412019475</v>
+        <v>0.01416994407441496</v>
       </c>
       <c r="K8" t="n">
         <v>-0.01356751702355641</v>
@@ -11562,7 +11562,7 @@
         <v>-0.01746339254699392</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.00542510102815319</v>
+        <v>-0.005425196957653422</v>
       </c>
     </row>
     <row r="9">
@@ -11576,7 +11576,7 @@
         <v>0.01653384679513037</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002874736345221507</v>
+        <v>0.002874823970921536</v>
       </c>
       <c r="E9" t="n">
         <v>0.01012217528448978</v>
@@ -11585,25 +11585,25 @@
         <v>0.0168740461938186</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002192509134303799</v>
+        <v>0.002192509336189197</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003839870023804259</v>
+        <v>0.003839774958466213</v>
       </c>
       <c r="I9" t="n">
         <v>0.01110082277694935</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003992067798616716</v>
+        <v>0.003992147041083527</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.005937271677580847</v>
+        <v>-0.005937379408595511</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.006765587751421442</v>
+        <v>-0.006765705012071965</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.002657177257710863</v>
+        <v>-0.002656984608451873</v>
       </c>
     </row>
     <row r="10">
@@ -11617,7 +11617,7 @@
         <v>0.005228007655542211</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.002976762571271441</v>
+        <v>-0.00297676231117816</v>
       </c>
       <c r="E10" t="n">
         <v>-0.003469895114376564</v>
@@ -11626,7 +11626,7 @@
         <v>0.008297070704628373</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.00495150161645963</v>
+        <v>-0.004951502071394942</v>
       </c>
       <c r="H10" t="n">
         <v>-0.003585936968603542</v>
@@ -11635,16 +11635,16 @@
         <v>0.005946914824861871</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.003976194560351365</v>
+        <v>-0.003976273173897704</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.004629865444433889</v>
+        <v>-0.00462964919724318</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.003617457820035641</v>
+        <v>-0.003617222128299402</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.004011616774111215</v>
+        <v>-0.004011809805612443</v>
       </c>
     </row>
     <row r="11">
@@ -11652,13 +11652,13 @@
         <v>45891</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02037519384335207</v>
+        <v>0.02037510276760091</v>
       </c>
       <c r="C11" t="n">
         <v>0.02109215629479055</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01935199762683371</v>
+        <v>0.01935190829553024</v>
       </c>
       <c r="E11" t="n">
         <v>0.01070642694476942</v>
@@ -11667,7 +11667,7 @@
         <v>0.006879834818919406</v>
       </c>
       <c r="G11" t="n">
-        <v>0.007406409500798627</v>
+        <v>0.007406594855549509</v>
       </c>
       <c r="H11" t="n">
         <v>0.01583496244274762</v>
@@ -11676,16 +11676,16 @@
         <v>0.004092721126542465</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01516968399451457</v>
+        <v>0.01516976411920123</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01542743815834102</v>
+        <v>0.01542732760007959</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0135568064730478</v>
+        <v>0.01355668637872576</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01535673445069352</v>
+        <v>0.01535683304109692</v>
       </c>
     </row>
     <row r="12">
@@ -11693,7 +11693,7 @@
         <v>45894</v>
       </c>
       <c r="B12" t="n">
-        <v>0.002609431906992699</v>
+        <v>0.002609521397031189</v>
       </c>
       <c r="C12" t="n">
         <v>-0.009054886628255598</v>
@@ -11708,7 +11708,7 @@
         <v>0.01487139093553513</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.002871784079819695</v>
+        <v>-0.002871783816601803</v>
       </c>
       <c r="H12" t="n">
         <v>-0.004959896104641759</v>
@@ -11717,16 +11717,16 @@
         <v>0.004981984227124592</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.006291754058618704</v>
+        <v>-0.00629167631065386</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.002884764158413655</v>
+        <v>-0.002884656934054597</v>
       </c>
       <c r="L12" t="n">
         <v>-0.002248398923228145</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.004401020035203596</v>
+        <v>-0.004401115665894628</v>
       </c>
     </row>
     <row r="13">
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.002618535579459236</v>
+        <v>-0.002618622048289221</v>
       </c>
       <c r="E13" t="n">
         <v>0.007262047243691283</v>
@@ -11749,7 +11749,7 @@
         <v>-0.02244220393719054</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0005761580680651024</v>
+        <v>-0.0005762499356556372</v>
       </c>
       <c r="H13" t="n">
         <v>-0.00284834050375038</v>
@@ -11758,16 +11758,16 @@
         <v>-0.00766111649531398</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.001187217298477372</v>
+        <v>-0.001187295445816305</v>
       </c>
       <c r="K13" t="n">
-        <v>0.004015340881901697</v>
+        <v>0.004015232915554501</v>
       </c>
       <c r="L13" t="n">
         <v>0.004583206695744302</v>
       </c>
       <c r="M13" t="n">
-        <v>0.004186968758527643</v>
+        <v>0.004187065214133812</v>
       </c>
     </row>
     <row r="14">
@@ -11781,7 +11781,7 @@
         <v>-0.0008566184724371206</v>
       </c>
       <c r="D14" t="n">
-        <v>0.006235512040405844</v>
+        <v>0.006235599276852577</v>
       </c>
       <c r="E14" t="n">
         <v>0.00201872888336152</v>
@@ -11790,7 +11790,7 @@
         <v>0.008507727582099278</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.001152520567355375</v>
+        <v>-0.001152612540906373</v>
       </c>
       <c r="H14" t="n">
         <v>0.004284668115523749</v>
@@ -11799,7 +11799,7 @@
         <v>0.0009082345555133653</v>
       </c>
       <c r="J14" t="n">
-        <v>0.009904845490050329</v>
+        <v>0.009905002156513909</v>
       </c>
       <c r="K14" t="n">
         <v>0.001536842612600342</v>
@@ -11808,7 +11808,7 @@
         <v>0.005398781964622845</v>
       </c>
       <c r="M14" t="n">
-        <v>0.002278452752666471</v>
+        <v>0.002278548405594716</v>
       </c>
     </row>
     <row r="15">
@@ -11816,7 +11816,7 @@
         <v>45897</v>
       </c>
       <c r="B15" t="n">
-        <v>0.007621638837520983</v>
+        <v>0.007621550660848797</v>
       </c>
       <c r="C15" t="n">
         <v>0.01514714929616723</v>
@@ -11831,16 +11831,16 @@
         <v>0.007498628231191073</v>
       </c>
       <c r="G15" t="n">
-        <v>0.006577987801284602</v>
+        <v>0.006578264646033283</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.002607179986989339</v>
+        <v>-0.002607086452513285</v>
       </c>
       <c r="I15" t="n">
         <v>0.006352051803974579</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.001176970745365935</v>
+        <v>-0.001177048127733338</v>
       </c>
       <c r="K15" t="n">
         <v>0.006259849188709143</v>
@@ -11849,7 +11849,7 @@
         <v>0.007903125891794538</v>
       </c>
       <c r="M15" t="n">
-        <v>0.003541515341778823</v>
+        <v>0.003541324132844581</v>
       </c>
     </row>
     <row r="16">
@@ -11857,13 +11857,13 @@
         <v>45898</v>
       </c>
       <c r="B16" t="n">
-        <v>0.005450454455399045</v>
+        <v>0.005450542442079209</v>
       </c>
       <c r="C16" t="n">
         <v>0.0188625608195585</v>
       </c>
       <c r="D16" t="n">
-        <v>0.005450052858368748</v>
+        <v>0.005450139242367369</v>
       </c>
       <c r="E16" t="n">
         <v>0.009649901776661141</v>
@@ -11872,25 +11872,25 @@
         <v>-0.005316341536893088</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.007108567292723356</v>
+        <v>-0.007108565992169469</v>
       </c>
       <c r="H16" t="n">
-        <v>0.005465813765646921</v>
+        <v>0.005465719474102571</v>
       </c>
       <c r="I16" t="n">
         <v>0.001352524316504455</v>
       </c>
       <c r="J16" t="n">
-        <v>0.004713508207695005</v>
+        <v>0.004713352528949111</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0115754615518685</v>
+        <v>-0.01157535527697362</v>
       </c>
       <c r="L16" t="n">
         <v>-0.01534473544974457</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.005963829023207134</v>
+        <v>-0.005963639392962183</v>
       </c>
     </row>
     <row r="17">
@@ -11904,7 +11904,7 @@
         <v>0.02652674594083626</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.01658715306896652</v>
+        <v>-0.01658723755961478</v>
       </c>
       <c r="E17" t="n">
         <v>0.02364255931244252</v>
@@ -11913,7 +11913,7 @@
         <v>0.02565480882269577</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.00744138737355915</v>
+        <v>-0.007441662400915705</v>
       </c>
       <c r="H17" t="n">
         <v>-0.01701742874584189</v>
@@ -11922,16 +11922,16 @@
         <v>0.01620899096170714</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0179828445667789</v>
+        <v>-0.01798276866465842</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.008380068468406443</v>
+        <v>-0.008380282606327838</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.01009729206063403</v>
+        <v>-0.01009740895043942</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.007410252681608887</v>
+        <v>-0.007410347641911175</v>
       </c>
     </row>
     <row r="18">
@@ -11939,7 +11939,7 @@
         <v>45903</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.02242599411512769</v>
+        <v>-0.02242590720479687</v>
       </c>
       <c r="C18" t="n">
         <v>0.005114363900540653</v>
@@ -11954,7 +11954,7 @@
         <v>-0.0251433070800402</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0109775049423928</v>
+        <v>0.01097750596136438</v>
       </c>
       <c r="H18" t="n">
         <v>-0.002644887657507256</v>
@@ -11963,13 +11963,13 @@
         <v>-0.008861283607721648</v>
       </c>
       <c r="J18" t="n">
-        <v>0.002786636517523755</v>
+        <v>0.002786557810094958</v>
       </c>
       <c r="K18" t="n">
-        <v>0.007867435783447396</v>
+        <v>0.007867545064627945</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005966098860944458</v>
+        <v>0.005966335729691963</v>
       </c>
       <c r="M18" t="n">
         <v>0.005419642546478309</v>
@@ -11980,7 +11980,7 @@
         <v>45904</v>
       </c>
       <c r="B19" t="n">
-        <v>0.006667451393465029</v>
+        <v>0.006667361896615764</v>
       </c>
       <c r="C19" t="n">
         <v>-0.01098017797902162</v>
@@ -11995,7 +11995,7 @@
         <v>-0.008686375918397382</v>
       </c>
       <c r="G19" t="n">
-        <v>0.007623732667951133</v>
+        <v>0.007623916999337954</v>
       </c>
       <c r="H19" t="n">
         <v>0.006750338325567817</v>
@@ -12004,16 +12004,16 @@
         <v>-0.007152547400961717</v>
       </c>
       <c r="J19" t="n">
-        <v>0.006351698801775774</v>
+        <v>0.006351699300312319</v>
       </c>
       <c r="K19" t="n">
         <v>0.009051496036850626</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00493602222178402</v>
+        <v>0.004935904260594981</v>
       </c>
       <c r="M19" t="n">
-        <v>0.00835741674721624</v>
+        <v>0.008357320883294106</v>
       </c>
     </row>
     <row r="20">
@@ -12021,7 +12021,7 @@
         <v>45905</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.01930854100371349</v>
+        <v>-0.01930845268845771</v>
       </c>
       <c r="C20" t="n">
         <v>0.007581878607719084</v>
@@ -12036,25 +12036,25 @@
         <v>-0.02089516103236877</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01524718807386316</v>
+        <v>0.01524700444251348</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01005756793432044</v>
+        <v>0.01005747343672625</v>
       </c>
       <c r="I20" t="n">
         <v>-0.008104362328500869</v>
       </c>
       <c r="J20" t="n">
-        <v>0.009861943245665472</v>
+        <v>0.009862022008156446</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001442843594922749</v>
+        <v>0.001442950211607563</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0008374936443342751</v>
+        <v>0.0008373768390841363</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.002896288899897903</v>
+        <v>-0.002896194105849514</v>
       </c>
     </row>
     <row r="21">
@@ -12062,7 +12062,7 @@
         <v>45908</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.002289174420321949</v>
+        <v>-0.002289264268232838</v>
       </c>
       <c r="C21" t="n">
         <v>0.008062328525714202</v>
@@ -12077,10 +12077,10 @@
         <v>0.005645100889633881</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01332430303114074</v>
+        <v>0.01332421447448318</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.006638311519666762</v>
+        <v>-0.006638218584074318</v>
       </c>
       <c r="I21" t="n">
         <v>0.006808846219968023</v>
@@ -12089,13 +12089,13 @@
         <v>-0.001171990515642651</v>
       </c>
       <c r="K21" t="n">
-        <v>0.004878031642529423</v>
+        <v>0.004877924660135369</v>
       </c>
       <c r="L21" t="n">
-        <v>0.007494606070727716</v>
+        <v>0.007494723652926805</v>
       </c>
       <c r="M21" t="n">
-        <v>0.002456673081514316</v>
+        <v>0.002456577735978405</v>
       </c>
     </row>
     <row r="22">
@@ -12103,7 +12103,7 @@
         <v>45909</v>
       </c>
       <c r="B22" t="n">
-        <v>0.004818566985166584</v>
+        <v>0.004818657245857505</v>
       </c>
       <c r="C22" t="n">
         <v>-0.008797601469578864</v>
@@ -12118,7 +12118,7 @@
         <v>0.004791873901067945</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.005683069266608332</v>
+        <v>-0.005682893128553967</v>
       </c>
       <c r="H22" t="n">
         <v>-0.0004773136171791759</v>
@@ -12130,13 +12130,13 @@
         <v>-0.002346422089059552</v>
       </c>
       <c r="K22" t="n">
-        <v>0.00283321504432732</v>
+        <v>0.002833109098061337</v>
       </c>
       <c r="L22" t="n">
         <v>0.001925713159093956</v>
       </c>
       <c r="M22" t="n">
-        <v>0.00231188440026342</v>
+        <v>0.002311884620151083</v>
       </c>
     </row>
     <row r="23">
@@ -12144,7 +12144,7 @@
         <v>45910</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0174697201548093</v>
+        <v>0.01746962875770075</v>
       </c>
       <c r="C23" t="n">
         <v>0.006186109207866552</v>
@@ -12159,7 +12159,7 @@
         <v>0.01798609764003345</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005715551139631625</v>
+        <v>0.005715372982402878</v>
       </c>
       <c r="H23" t="n">
         <v>-0.0004775415542658257</v>
@@ -12171,13 +12171,13 @@
         <v>0.0007840319143461727</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0003271885900453242</v>
+        <v>0.0003272942715684124</v>
       </c>
       <c r="L23" t="n">
         <v>0.01812765701614127</v>
       </c>
       <c r="M23" t="n">
-        <v>0.00289080502144512</v>
+        <v>0.002890900188266654</v>
       </c>
     </row>
     <row r="24">
@@ -12200,7 +12200,7 @@
         <v>-0.0228884902346097</v>
       </c>
       <c r="G24" t="n">
-        <v>0.006685885690973503</v>
+        <v>0.006685975447733528</v>
       </c>
       <c r="H24" t="n">
         <v>0.01624464147050508</v>
@@ -12209,16 +12209,16 @@
         <v>-0.007592684071539124</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01488447144707372</v>
+        <v>0.01488439400364849</v>
       </c>
       <c r="K24" t="n">
-        <v>0.005820510052926497</v>
+        <v>0.005820615665316886</v>
       </c>
       <c r="L24" t="n">
         <v>0.003368475417101946</v>
       </c>
       <c r="M24" t="n">
-        <v>0.008310100433307488</v>
+        <v>0.008310195052279257</v>
       </c>
     </row>
     <row r="25">
@@ -12232,7 +12232,7 @@
         <v>0.01455409430367482</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.004611706061810938</v>
+        <v>-0.004611791056117198</v>
       </c>
       <c r="E25" t="n">
         <v>0.001971572597848414</v>
@@ -12241,25 +12241,25 @@
         <v>0.004246541898544454</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.004317028966220882</v>
+        <v>-0.004316853377789975</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.004466352218352232</v>
+        <v>-0.004466444983264317</v>
       </c>
       <c r="I25" t="n">
         <v>0.005850654499770735</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.001929743568220954</v>
+        <v>-0.001929667407842728</v>
       </c>
       <c r="K25" t="n">
-        <v>0.004417086724085584</v>
+        <v>0.004417191261504527</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0006640089708551677</v>
+        <v>-0.000664122147771895</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0003345366015885531</v>
+        <v>-0.000334630409346115</v>
       </c>
     </row>
     <row r="26">
@@ -12267,13 +12267,13 @@
         <v>45915</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.003386059334265612</v>
+        <v>-0.003385970540555672</v>
       </c>
       <c r="C26" t="n">
         <v>0.0109545687864836</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.001616140398514765</v>
+        <v>-0.001616055148415563</v>
       </c>
       <c r="E26" t="n">
         <v>0.01040483601055886</v>
@@ -12282,10 +12282,10 @@
         <v>0.01254952706286105</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00233470750677256</v>
+        <v>0.002334530569281235</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.001180697611423809</v>
+        <v>-0.00118051135924202</v>
       </c>
       <c r="I26" t="n">
         <v>0.008948508958212198</v>
@@ -12294,10 +12294,10 @@
         <v>-0.0003867102267423039</v>
       </c>
       <c r="K26" t="n">
-        <v>0.008556973749616503</v>
+        <v>0.008556867421086078</v>
       </c>
       <c r="L26" t="n">
-        <v>0.009007620395211413</v>
+        <v>0.009007961171733747</v>
       </c>
       <c r="M26" t="n">
         <v>0.005323962798345239</v>
@@ -12308,7 +12308,7 @@
         <v>45916</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01676107065932819</v>
+        <v>0.01676089097522571</v>
       </c>
       <c r="C27" t="n">
         <v>-0.004127963218285791</v>
@@ -12323,22 +12323,22 @@
         <v>0.01939909399016915</v>
       </c>
       <c r="G27" t="n">
-        <v>0.002107371197250352</v>
+        <v>0.002107195063475453</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.005910186657113625</v>
+        <v>-0.005910279396976637</v>
       </c>
       <c r="I27" t="n">
         <v>0.01019965036814519</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.004058662879958042</v>
+        <v>-0.004058739364700914</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.0008449753249998304</v>
+        <v>-0.0008450788899231343</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.003475769898128811</v>
+        <v>-0.003475881358947497</v>
       </c>
       <c r="M27" t="n">
         <v>-0.001376884824695557</v>
@@ -12349,7 +12349,7 @@
         <v>45917</v>
       </c>
       <c r="B28" t="n">
-        <v>0.00233901884411658</v>
+        <v>0.002339106675759872</v>
       </c>
       <c r="C28" t="n">
         <v>-0.02098439353920711</v>
@@ -12364,22 +12364,22 @@
         <v>-0.009250653696057043</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.002545714565724166</v>
+        <v>-0.00254553928879564</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0004756109554937549</v>
+        <v>-0.0004757048013808163</v>
       </c>
       <c r="I28" t="n">
         <v>-0.01053554808442769</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.003918614825797251</v>
+        <v>-0.00391853833029332</v>
       </c>
       <c r="K28" t="n">
         <v>-0.001995857239824539</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.003451174791567757</v>
+        <v>-0.003451287035417416</v>
       </c>
       <c r="M28" t="n">
         <v>-0.001242457061691904</v>
@@ -12405,25 +12405,25 @@
         <v>-0.003734810920872023</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.01031953670172603</v>
+        <v>-0.01031944941298335</v>
       </c>
       <c r="H29" t="n">
-        <v>0.000713849793910315</v>
+        <v>0.0007139437514851465</v>
       </c>
       <c r="I29" t="n">
         <v>-0.004436582377840947</v>
       </c>
       <c r="J29" t="n">
-        <v>0.001573581471429053</v>
+        <v>0.001573504372875734</v>
       </c>
       <c r="K29" t="n">
-        <v>0.00901673016481519</v>
+        <v>0.009016938060095958</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01727901390008912</v>
+        <v>0.01727890087745121</v>
       </c>
       <c r="M29" t="n">
-        <v>0.004672593154858351</v>
+        <v>0.004672499536354291</v>
       </c>
     </row>
     <row r="30">
@@ -12446,7 +12446,7 @@
         <v>-0.01566482474354858</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.001906246195751082</v>
+        <v>-0.001905978840043399</v>
       </c>
       <c r="H30" t="n">
         <v>-0.004993008736944304</v>
@@ -12455,16 +12455,16 @@
         <v>-0.008021383326866971</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.005106066421355027</v>
+        <v>-0.005105989836977964</v>
       </c>
       <c r="K30" t="n">
-        <v>0.006769464954618609</v>
+        <v>0.00676925752240165</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01014047182730704</v>
+        <v>0.0101405840568447</v>
       </c>
       <c r="M30" t="n">
-        <v>0.00495277480627232</v>
+        <v>0.004952868450893266</v>
       </c>
     </row>
     <row r="31">
@@ -12472,7 +12472,7 @@
         <v>45922</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.001150740111282689</v>
+        <v>-0.001150651237316724</v>
       </c>
       <c r="C31" t="n">
         <v>0.02561475349766895</v>
@@ -12487,7 +12487,7 @@
         <v>-0.0009521177641514944</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.00359440895116403</v>
+        <v>-0.003594765143349998</v>
       </c>
       <c r="H31" t="n">
         <v>0.003298605970757817</v>
@@ -12502,10 +12502,10 @@
         <v>0.005920073936714676</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01471127659595539</v>
+        <v>0.01471116660839167</v>
       </c>
       <c r="M31" t="n">
-        <v>0.004731049353107419</v>
+        <v>0.004730956629250382</v>
       </c>
     </row>
     <row r="32">
@@ -12513,7 +12513,7 @@
         <v>45923</v>
       </c>
       <c r="B32" t="n">
-        <v>0.01722377579880519</v>
+        <v>0.01722368528994989</v>
       </c>
       <c r="C32" t="n">
         <v>-0.001998047682952531</v>
@@ -12528,7 +12528,7 @@
         <v>0.02178361021094521</v>
       </c>
       <c r="G32" t="n">
-        <v>0.006989648151865424</v>
+        <v>0.006989648778213953</v>
       </c>
       <c r="H32" t="n">
         <v>0.007919498258845747</v>
@@ -12543,10 +12543,10 @@
         <v>-0.006642261760471446</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.008632415718237252</v>
+        <v>-0.008632308260953958</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.005443562937222368</v>
+        <v>-0.005443378865093829</v>
       </c>
     </row>
     <row r="33">
@@ -12554,7 +12554,7 @@
         <v>45924</v>
       </c>
       <c r="B33" t="n">
-        <v>0.01300745819949722</v>
+        <v>0.01300737072970271</v>
       </c>
       <c r="C33" t="n">
         <v>-0.003503488309709146</v>
@@ -12569,7 +12569,7 @@
         <v>0.01785471396938521</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.003806499035360567</v>
+        <v>-0.00380623240745448</v>
       </c>
       <c r="H33" t="n">
         <v>-0.0102381201924745</v>
@@ -12578,7 +12578,7 @@
         <v>0.006669669419053337</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.01019219311734065</v>
+        <v>-0.01019211629079919</v>
       </c>
       <c r="K33" t="n">
         <v>-0.003510615202493739</v>
@@ -12587,7 +12587,7 @@
         <v>-0.006173702727002017</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.003181664526101469</v>
+        <v>-0.003181757023221321</v>
       </c>
     </row>
     <row r="34">
@@ -12595,7 +12595,7 @@
         <v>45925</v>
       </c>
       <c r="B34" t="n">
-        <v>0.008966062833071442</v>
+        <v>0.008966149953912428</v>
       </c>
       <c r="C34" t="n">
         <v>0.03038671757272593</v>
@@ -12619,7 +12619,7 @@
         <v>0.007067073805264057</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.003564279432801354</v>
+        <v>-0.003564356773779753</v>
       </c>
       <c r="K34" t="n">
         <v>-0.004311291858417277</v>
@@ -12651,7 +12651,7 @@
         <v>0.0003896451503992981</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0008990060819583645</v>
+        <v>-0.0008994525657802788</v>
       </c>
       <c r="H35" t="n">
         <v>0.009886673917586686</v>
@@ -12666,7 +12666,7 @@
         <v>0.004110948441042206</v>
       </c>
       <c r="L35" t="n">
-        <v>0.003021735711531193</v>
+        <v>0.003021625501606673</v>
       </c>
       <c r="M35" t="n">
         <v>0.005729034082609274</v>
@@ -12677,7 +12677,7 @@
         <v>45929</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.01837154339501335</v>
+        <v>-0.01837162819288363</v>
       </c>
       <c r="C36" t="n">
         <v>0.01528904396361064</v>
@@ -12692,7 +12692,7 @@
         <v>-0.03155025202658901</v>
       </c>
       <c r="G36" t="n">
-        <v>0.008211259114270453</v>
+        <v>0.00821170836329288</v>
       </c>
       <c r="H36" t="n">
         <v>0.00191009820650323</v>
@@ -12707,7 +12707,7 @@
         <v>0.004631078168035652</v>
       </c>
       <c r="L36" t="n">
-        <v>0.005343472280167516</v>
+        <v>0.005343582745211739</v>
       </c>
       <c r="M36" t="n">
         <v>0.002810446783301224</v>
@@ -12718,7 +12718,7 @@
         <v>45930</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.01063130253389355</v>
+        <v>-0.01063121706737602</v>
       </c>
       <c r="C37" t="n">
         <v>-0.003058848661534941</v>
@@ -12733,7 +12733,7 @@
         <v>-0.0112615146686087</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002900581393286528</v>
+        <v>-0.002900758241000112</v>
       </c>
       <c r="H37" t="n">
         <v>0.004051570465396281</v>
@@ -12745,7 +12745,7 @@
         <v>0.006299204943254422</v>
       </c>
       <c r="K37" t="n">
-        <v>0.002739134291552814</v>
+        <v>0.00273923660495079</v>
       </c>
       <c r="L37" t="n">
         <v>0.005457809168927019</v>
@@ -12774,7 +12774,7 @@
         <v>-0.008271194716631403</v>
       </c>
       <c r="G38" t="n">
-        <v>0.002582523898818634</v>
+        <v>0.002582346020670201</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -12786,13 +12786,13 @@
         <v>0.003129925012149259</v>
       </c>
       <c r="K38" t="n">
-        <v>0.004797022405524931</v>
+        <v>0.004796919882163131</v>
       </c>
       <c r="L38" t="n">
-        <v>0.009792078528811032</v>
+        <v>0.00979218722943731</v>
       </c>
       <c r="M38" t="n">
-        <v>0.003407479845975114</v>
+        <v>0.003407572224651378</v>
       </c>
     </row>
     <row r="39">
@@ -12815,7 +12815,7 @@
         <v>-0.02187583384568015</v>
       </c>
       <c r="G39" t="n">
-        <v>0.002911993757656273</v>
+        <v>0.00291199427430211</v>
       </c>
       <c r="H39" t="n">
         <v>-0.005222018519871585</v>
@@ -12827,13 +12827,13 @@
         <v>-0.004290104172956832</v>
       </c>
       <c r="K39" t="n">
-        <v>0.004111121841221976</v>
+        <v>0.004111020294430778</v>
       </c>
       <c r="L39" t="n">
-        <v>0.005410745837684861</v>
+        <v>0.005410637608705526</v>
       </c>
       <c r="M39" t="n">
-        <v>0.001151824796685963</v>
+        <v>0.001151732625685131</v>
       </c>
     </row>
     <row r="40">
@@ -12856,7 +12856,7 @@
         <v>0.002376267357698802</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.001898542437031803</v>
+        <v>-0.001898365868050367</v>
       </c>
       <c r="H40" t="n">
         <v>0.004056404098548239</v>
@@ -12868,10 +12868,10 @@
         <v>0.00587538978116986</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.004209781352692232</v>
+        <v>-0.004209680647392355</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.00503215978370708</v>
+        <v>-0.005032052716477664</v>
       </c>
       <c r="M40" t="n">
         <v>-1.480540638265637e-05</v>
@@ -12882,7 +12882,7 @@
         <v>45936</v>
       </c>
       <c r="B41" t="n">
-        <v>0.004948891923559628</v>
+        <v>0.004948804188138034</v>
       </c>
       <c r="C41" t="n">
         <v>0.0124081091417132</v>
@@ -12897,7 +12897,7 @@
         <v>0.01617631678872167</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.007943689726322534</v>
+        <v>-0.00794360110566672</v>
       </c>
       <c r="H41" t="n">
         <v>-0.009981052157614689</v>
@@ -12912,7 +12912,7 @@
         <v>0.007510154587375251</v>
       </c>
       <c r="L41" t="n">
-        <v>0.01011522097561102</v>
+        <v>0.01011511227840267</v>
       </c>
       <c r="M41" t="n">
         <v>0.003586271966467658</v>
@@ -12923,7 +12923,7 @@
         <v>45937</v>
       </c>
       <c r="B42" t="n">
-        <v>0.001566833520860955</v>
+        <v>0.001566920961025176</v>
       </c>
       <c r="C42" t="n">
         <v>-0.0152065810885047</v>
@@ -12938,7 +12938,7 @@
         <v>0.004528532856074685</v>
       </c>
       <c r="G42" t="n">
-        <v>0.005751797280322046</v>
+        <v>0.005751618105993117</v>
       </c>
       <c r="H42" t="n">
         <v>-0.0031205596419841</v>
@@ -12950,7 +12950,7 @@
         <v>-0.005488027159718967</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.005265569704058781</v>
+        <v>-0.005265670505592235</v>
       </c>
       <c r="L42" t="n">
         <v>-0.006675987431881358</v>
@@ -12964,7 +12964,7 @@
         <v>45938</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.005810799773610431</v>
+        <v>-0.005810712606819646</v>
       </c>
       <c r="C43" t="n">
         <v>0.02696478451487838</v>
@@ -12979,7 +12979,7 @@
         <v>0.004508221923670508</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0007848081882957381</v>
+        <v>0.0007849858968107526</v>
       </c>
       <c r="H43" t="n">
         <v>-0.005056524133560614</v>
@@ -12988,10 +12988,10 @@
         <v>0.001319883938338595</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.0055184663057678</v>
+        <v>-0.005518389055273576</v>
       </c>
       <c r="K43" t="n">
-        <v>0.01146373818977175</v>
+        <v>0.01146384068658191</v>
       </c>
       <c r="L43" t="n">
         <v>0.0175371576443768</v>
@@ -13005,7 +13005,7 @@
         <v>45939</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.01359999074138696</v>
+        <v>-0.01360007722524303</v>
       </c>
       <c r="C44" t="n">
         <v>0.003366196287227785</v>
@@ -13020,7 +13020,7 @@
         <v>-0.0138718436012486</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.0007841927474063759</v>
+        <v>-0.000784370177283833</v>
       </c>
       <c r="H44" t="n">
         <v>-0.004598178755739313</v>
@@ -13029,7 +13029,7 @@
         <v>-0.009226749118025013</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.006341571597079709</v>
+        <v>-0.006341726462787856</v>
       </c>
       <c r="K44" t="n">
         <v>-0.001210254219509266</v>
@@ -13061,7 +13061,7 @@
         <v>-0.04302858439750457</v>
       </c>
       <c r="G45" t="n">
-        <v>0.01614692220362346</v>
+        <v>0.01614719009599686</v>
       </c>
       <c r="H45" t="n">
         <v>-0.01094096133328448</v>
@@ -13070,13 +13070,13 @@
         <v>-0.02128601398265129</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.01076984546460802</v>
+        <v>-0.01076976813161779</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.0347142937102668</v>
+        <v>-0.03471419340226101</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.04069601649614796</v>
+        <v>-0.04069591091944957</v>
       </c>
       <c r="M45" t="n">
         <v>-0.02702786217884567</v>
@@ -13102,7 +13102,7 @@
         <v>0.01282604694447098</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0005516320520686513</v>
+        <v>-0.0005519815876773304</v>
       </c>
       <c r="H46" t="n">
         <v>0.005653933883178919</v>
@@ -13114,10 +13114,10 @@
         <v>0.008467716411356019</v>
       </c>
       <c r="K46" t="n">
-        <v>0.02122138573826193</v>
+        <v>0.02122127961769138</v>
       </c>
       <c r="L46" t="n">
-        <v>0.02435429601170913</v>
+        <v>0.02435418327587713</v>
       </c>
       <c r="M46" t="n">
         <v>0.01534411813516834</v>
@@ -13128,7 +13128,7 @@
         <v>45944</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.0001156808717840407</v>
+        <v>-0.0001155905666538892</v>
       </c>
       <c r="C47" t="n">
         <v>-0.009733370732327495</v>
@@ -13143,7 +13143,7 @@
         <v>-0.01821284578157878</v>
       </c>
       <c r="G47" t="n">
-        <v>0.003201948945478428</v>
+        <v>0.00320212441810952</v>
       </c>
       <c r="H47" t="n">
         <v>0.009533017869981064</v>
@@ -13169,7 +13169,7 @@
         <v>45945</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.0005789228548718217</v>
+        <v>-0.0005789228025860904</v>
       </c>
       <c r="C48" t="n">
         <v>0.03269236365248784</v>
@@ -13199,7 +13199,7 @@
         <v>0.007056768737883523</v>
       </c>
       <c r="L48" t="n">
-        <v>0.009910693723528485</v>
+        <v>0.009910802559294885</v>
       </c>
       <c r="M48" t="n">
         <v>0.004439529909605389</v>
@@ -13210,7 +13210,7 @@
         <v>45946</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.01204820910263149</v>
+        <v>-0.01204820801386031</v>
       </c>
       <c r="C49" t="n">
         <v>0.01738043256913113</v>
@@ -13234,13 +13234,13 @@
         <v>-0.001803454643635738</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.0003922765649736482</v>
+        <v>-0.0003923534517954463</v>
       </c>
       <c r="K49" t="n">
         <v>-0.003702930251393011</v>
       </c>
       <c r="L49" t="n">
-        <v>0.0007388554443763518</v>
+        <v>0.0007386398293476315</v>
       </c>
       <c r="M49" t="n">
         <v>-0.006810134562330372</v>
@@ -13251,7 +13251,7 @@
         <v>45947</v>
       </c>
       <c r="B50" t="n">
-        <v>0.008208238277006341</v>
+        <v>0.008208146056264631</v>
       </c>
       <c r="C50" t="n">
         <v>-0.04433590749766092</v>
@@ -13266,7 +13266,7 @@
         <v>0.002507090465427853</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.001532671777133565</v>
+        <v>-0.001532758496143205</v>
       </c>
       <c r="H50" t="n">
         <v>0.006463862712322799</v>
@@ -13275,13 +13275,13 @@
         <v>-0.0009032229109263712</v>
       </c>
       <c r="J50" t="n">
-        <v>0.005494488589671498</v>
+        <v>0.005494565929291539</v>
       </c>
       <c r="K50" t="n">
         <v>0.006566773461732511</v>
       </c>
       <c r="L50" t="n">
-        <v>0.001757362880950852</v>
+        <v>0.001757470758357194</v>
       </c>
       <c r="M50" t="n">
         <v>0.005676205164253156</v>
@@ -13292,7 +13292,7 @@
         <v>45950</v>
       </c>
       <c r="B51" t="n">
-        <v>0.01058382604703745</v>
+        <v>0.01058391677228587</v>
       </c>
       <c r="C51" t="n">
         <v>0.01553520996299196</v>
@@ -13307,7 +13307,7 @@
         <v>-0.002206553669780065</v>
       </c>
       <c r="G51" t="n">
-        <v>0.003837648016649098</v>
+        <v>0.003837648349957146</v>
       </c>
       <c r="H51" t="n">
         <v>0.01046620979277657</v>
@@ -13319,7 +13319,7 @@
         <v>0.008586982314425562</v>
       </c>
       <c r="K51" t="n">
-        <v>0.01260064888366497</v>
+        <v>0.0126007503161143</v>
       </c>
       <c r="L51" t="n">
         <v>0.01115745283578673</v>
@@ -13333,7 +13333,7 @@
         <v>45951</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.002301653621149868</v>
+        <v>-0.002301653414518712</v>
       </c>
       <c r="C52" t="n">
         <v>-0.08235541082657738</v>
@@ -13348,7 +13348,7 @@
         <v>0.00648672858814936</v>
       </c>
       <c r="G52" t="n">
-        <v>0.004915379456790436</v>
+        <v>0.004915379882069582</v>
       </c>
       <c r="H52" t="n">
         <v>-0.003060322792836079</v>
@@ -13357,13 +13357,13 @@
         <v>-0.01029544012432893</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.005417864549973173</v>
+        <v>-0.005417940395374465</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.0002614443246297116</v>
+        <v>-0.0002615444686701052</v>
       </c>
       <c r="L52" t="n">
-        <v>0.000520402377882645</v>
+        <v>0.000520508690932342</v>
       </c>
       <c r="M52" t="n">
         <v>-1.494287878323064e-05</v>
@@ -13374,7 +13374,7 @@
         <v>45952</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0128041960496017</v>
+        <v>0.01280419489745221</v>
       </c>
       <c r="C53" t="n">
         <v>0.002055267200416377</v>
@@ -13389,7 +13389,7 @@
         <v>0.03456863521892739</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0006520117701340755</v>
+        <v>0.000652184020070834</v>
       </c>
       <c r="H53" t="n">
         <v>0.004486530974596947</v>
@@ -13398,13 +13398,13 @@
         <v>0.0158298534852428</v>
       </c>
       <c r="J53" t="n">
-        <v>0.005836525135355153</v>
+        <v>0.005836601839005917</v>
       </c>
       <c r="K53" t="n">
         <v>-0.009633987432361102</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.009884202426119537</v>
+        <v>-0.009884201375846446</v>
       </c>
       <c r="M53" t="n">
         <v>-0.005198916065879078</v>
@@ -13415,7 +13415,7 @@
         <v>45953</v>
       </c>
       <c r="B54" t="n">
-        <v>0.01332571401968807</v>
+        <v>0.01332571283577044</v>
       </c>
       <c r="C54" t="n">
         <v>0.00683681015856985</v>
@@ -13430,7 +13430,7 @@
         <v>0.03766110385882326</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.0068430824148622</v>
+        <v>-0.006843253907649838</v>
       </c>
       <c r="H54" t="n">
         <v>-0.0009403237792362518</v>
@@ -13442,10 +13442,10 @@
         <v>0.001160440576208011</v>
       </c>
       <c r="K54" t="n">
-        <v>0.008406510401807177</v>
+        <v>0.008406409230690803</v>
       </c>
       <c r="L54" t="n">
-        <v>0.01261003232755509</v>
+        <v>0.01260981633726677</v>
       </c>
       <c r="M54" t="n">
         <v>0.005929962705964353</v>
@@ -13456,7 +13456,7 @@
         <v>45954</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.01011573617020978</v>
+        <v>-0.0101157352832999</v>
       </c>
       <c r="C55" t="n">
         <v>-0.004300557387880488</v>
@@ -13471,7 +13471,7 @@
         <v>-0.001500895196854257</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0004374132201714342</v>
+        <v>0.0004374132580660106</v>
       </c>
       <c r="H55" t="n">
         <v>0.003529487001568965</v>
@@ -13483,10 +13483,10 @@
         <v>0.001932053042440263</v>
       </c>
       <c r="K55" t="n">
-        <v>0.01067827953226419</v>
+        <v>0.01067828060359166</v>
       </c>
       <c r="L55" t="n">
-        <v>0.01553146088445434</v>
+        <v>0.01553156851259541</v>
       </c>
       <c r="M55" t="n">
         <v>0.008172554694480416</v>
@@ -13497,7 +13497,7 @@
         <v>45957</v>
       </c>
       <c r="B56" t="n">
-        <v>0.002384453093031036</v>
+        <v>0.002384364309609088</v>
       </c>
       <c r="C56" t="n">
         <v>-0.0361445804028282</v>
@@ -13512,7 +13512,7 @@
         <v>-0.0008198627814095527</v>
       </c>
       <c r="G56" t="n">
-        <v>0.003389098113857791</v>
+        <v>0.003389098407339475</v>
       </c>
       <c r="H56" t="n">
         <v>0.002110225756783324</v>
@@ -13524,10 +13524,10 @@
         <v>0.003470883525864998</v>
       </c>
       <c r="K56" t="n">
-        <v>0.01780922137392449</v>
+        <v>0.01780922314180522</v>
       </c>
       <c r="L56" t="n">
-        <v>0.01846180787396845</v>
+        <v>0.01846170351277676</v>
       </c>
       <c r="M56" t="n">
         <v>0.01179766449278463</v>
@@ -13553,7 +13553,7 @@
         <v>-0.02365978243914202</v>
       </c>
       <c r="G57" t="n">
-        <v>0.002614816354848726</v>
+        <v>0.002614902883789405</v>
       </c>
       <c r="H57" t="n">
         <v>-0.02222749612055397</v>
@@ -13565,13 +13565,13 @@
         <v>-0.0153727332511383</v>
       </c>
       <c r="K57" t="n">
-        <v>0.007689812405443863</v>
+        <v>0.007690008216966859</v>
       </c>
       <c r="L57" t="n">
-        <v>0.009899673214770033</v>
+        <v>0.009899674229183919</v>
       </c>
       <c r="M57" t="n">
-        <v>0.002655926209922388</v>
+        <v>0.002656016019079832</v>
       </c>
     </row>
     <row r="58">
@@ -13594,7 +13594,7 @@
         <v>0.00574315262102143</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01010635390444203</v>
+        <v>-0.01010652606081686</v>
       </c>
       <c r="H58" t="n">
         <v>-0.02727925320808078</v>
@@ -13606,13 +13606,13 @@
         <v>-0.019906349699085</v>
       </c>
       <c r="K58" t="n">
-        <v>0.00450308802121091</v>
+        <v>0.004502990798896933</v>
       </c>
       <c r="L58" t="n">
-        <v>0.007186458081784863</v>
+        <v>0.007186458810958474</v>
       </c>
       <c r="M58" t="n">
-        <v>0.0004804602529762114</v>
+        <v>0.0004803706386860007</v>
       </c>
     </row>
     <row r="59">
@@ -13635,7 +13635,7 @@
         <v>-0.001253537095538548</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.005818554120649022</v>
+        <v>-0.005818381218535729</v>
       </c>
       <c r="H59" t="n">
         <v>0.005658010056436513</v>
@@ -13647,13 +13647,13 @@
         <v>0.002389434413365921</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.0152885562882743</v>
+        <v>-0.01528865264087542</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.01229735070363036</v>
+        <v>-0.01229735194247772</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.01099809761426018</v>
+        <v>-0.01099818714250811</v>
       </c>
     </row>
     <row r="60">
@@ -13676,7 +13676,7 @@
         <v>0.01185327687872118</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.002981451187494377</v>
+        <v>-0.002981363721563435</v>
       </c>
       <c r="H60" t="n">
         <v>0.0004893494172306667</v>
@@ -13688,13 +13688,13 @@
         <v>0.001589210993727219</v>
       </c>
       <c r="K60" t="n">
-        <v>0.004823836379978852</v>
+        <v>0.00482403254913244</v>
       </c>
       <c r="L60" t="n">
-        <v>0.0009651810650304071</v>
+        <v>0.0009653851539981329</v>
       </c>
       <c r="M60" t="n">
-        <v>0.003280131266806929</v>
+        <v>0.003280222087583162</v>
       </c>
     </row>
     <row r="61">
@@ -13717,7 +13717,7 @@
         <v>0.00248070991224103</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.002500847447516108</v>
+        <v>-0.002501022683080056</v>
       </c>
       <c r="H61" t="n">
         <v>-0.001711502235323015</v>
@@ -13726,13 +13726,13 @@
         <v>0.00743007810254892</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0007932669639525436</v>
+        <v>0.0007933447047370201</v>
       </c>
       <c r="K61" t="n">
-        <v>0.004784708564165685</v>
+        <v>0.004784708098236612</v>
       </c>
       <c r="L61" t="n">
-        <v>0.004090854946600331</v>
+        <v>0.004090752632862849</v>
       </c>
       <c r="M61" t="n">
         <v>0.001876739875461997</v>
@@ -13758,7 +13758,7 @@
         <v>-0.01113551804209212</v>
       </c>
       <c r="G62" t="n">
-        <v>0.002228675804580416</v>
+        <v>0.002228763948023849</v>
       </c>
       <c r="H62" t="n">
         <v>0.00269404598284817</v>
@@ -13767,13 +13767,13 @@
         <v>-0.006941454343098341</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.001981673154818897</v>
+        <v>-0.001981828359200244</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.02029790155517741</v>
+        <v>-0.0202980934182142</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.02639865199754654</v>
+        <v>-0.02639855051579121</v>
       </c>
       <c r="M62" t="n">
         <v>-0.01185354736001909</v>
@@ -13799,7 +13799,7 @@
         <v>-0.01251218576477808</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.01089623605952028</v>
+        <v>-0.01089641156323795</v>
       </c>
       <c r="H63" t="n">
         <v>-0.0002443161109926262</v>
@@ -13808,16 +13808,16 @@
         <v>-0.003058087118058883</v>
       </c>
       <c r="J63" t="n">
-        <v>0.001191395921872118</v>
+        <v>0.001191473848012992</v>
       </c>
       <c r="K63" t="n">
-        <v>0.006507949258017787</v>
+        <v>0.006508048824858337</v>
       </c>
       <c r="L63" t="n">
-        <v>0.003912295535809518</v>
+        <v>0.00391229512801794</v>
       </c>
       <c r="M63" t="n">
-        <v>0.003465385201129045</v>
+        <v>0.003465476340313245</v>
       </c>
     </row>
     <row r="64">
@@ -13840,7 +13840,7 @@
         <v>-0.002111805271811873</v>
       </c>
       <c r="G64" t="n">
-        <v>0.008992867826472573</v>
+        <v>0.008993046859287146</v>
       </c>
       <c r="H64" t="n">
         <v>-0.004886368116093998</v>
@@ -13849,16 +13849,16 @@
         <v>0.001314678383722345</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.001189978186713292</v>
+        <v>-0.001190055927497657</v>
       </c>
       <c r="K64" t="n">
         <v>-0.0186273619471754</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.0200954379378262</v>
+        <v>-0.02009564350569926</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.01072936386923751</v>
+        <v>-0.01072945371918343</v>
       </c>
     </row>
     <row r="65">
@@ -13881,7 +13881,7 @@
         <v>0.005361242911083419</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.002116686742056562</v>
+        <v>-0.002116774669890353</v>
       </c>
       <c r="H65" t="n">
         <v>0.01325801573223506</v>
@@ -13890,13 +13890,13 @@
         <v>0.00218810998634944</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01350285033710419</v>
+        <v>0.01350285138807705</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.003155392384014299</v>
+        <v>-0.003155292235082818</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.003458417352354748</v>
+        <v>-0.003458205805945913</v>
       </c>
       <c r="M65" t="n">
         <v>0.0009845650786590721</v>
@@ -13922,7 +13922,7 @@
         <v>0.005893883754625628</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.0002233698626032954</v>
+        <v>-0.0002234579966373662</v>
       </c>
       <c r="H66" t="n">
         <v>-0.0007268978391585801</v>
@@ -13931,13 +13931,13 @@
         <v>0.01091709354004733</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.001959307412898625</v>
+        <v>-0.001959230766926834</v>
       </c>
       <c r="K66" t="n">
-        <v>0.02212420765024037</v>
+        <v>0.02212420542751126</v>
       </c>
       <c r="L66" t="n">
-        <v>0.02557605614679459</v>
+        <v>0.02557605342744296</v>
       </c>
       <c r="M66" t="n">
         <v>0.01560437034633999</v>
@@ -13963,7 +13963,7 @@
         <v>0.01450894128208091</v>
       </c>
       <c r="G67" t="n">
-        <v>0.004578298493216559</v>
+        <v>0.004578563702363203</v>
       </c>
       <c r="H67" t="n">
         <v>0.01115422279690392</v>
@@ -13975,10 +13975,10 @@
         <v>0.008637630641912697</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.00266349827862411</v>
+        <v>-0.002663596308138949</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.008526966951562409</v>
+        <v>-0.008527069740130178</v>
       </c>
       <c r="M67" t="n">
         <v>0.002289177027853917</v>
@@ -14004,7 +14004,7 @@
         <v>-0.04029153267315433</v>
       </c>
       <c r="G68" t="n">
-        <v>0.001778773715593873</v>
+        <v>0.001778510362463681</v>
       </c>
       <c r="H68" t="n">
         <v>-0.00791370629361432</v>
@@ -14045,7 +14045,7 @@
         <v>0.0008596870297561399</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.008211268356818846</v>
+        <v>-0.008211182218446744</v>
       </c>
       <c r="H69" t="n">
         <v>-0.01305281808073222</v>
@@ -14063,7 +14063,7 @@
         <v>-0.02493880042580143</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.01659390636118807</v>
+        <v>-0.01659399641478621</v>
       </c>
     </row>
     <row r="70">
@@ -14086,7 +14086,7 @@
         <v>0.02190406317422799</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.005706141274171683</v>
+        <v>-0.00570605347637021</v>
       </c>
       <c r="H70" t="n">
         <v>0.002938924374780827</v>
@@ -14101,10 +14101,10 @@
         <v>0.0007559594991779495</v>
       </c>
       <c r="L70" t="n">
-        <v>0.005443362442926647</v>
+        <v>0.005443255536344394</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.0001637328001578009</v>
+        <v>-0.0001635496688257021</v>
       </c>
     </row>
     <row r="71">
@@ -14112,7 +14112,7 @@
         <v>45978</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.01825679513934275</v>
+        <v>-0.01825687990957392</v>
       </c>
       <c r="C71" t="n">
         <v>-0.01066139846671743</v>
@@ -14127,7 +14127,7 @@
         <v>-0.001120680929366791</v>
       </c>
       <c r="G71" t="n">
-        <v>0.002475623201907196</v>
+        <v>0.002475534393498569</v>
       </c>
       <c r="H71" t="n">
         <v>-0.00659339419214755</v>
@@ -14139,13 +14139,13 @@
         <v>-0.004761956980000037</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.008540578033146784</v>
+        <v>-0.008540477422004478</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.01565155869113877</v>
+        <v>-0.0156514540275221</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.009316529838549359</v>
+        <v>-0.009316620573407763</v>
       </c>
     </row>
     <row r="72">
@@ -14153,7 +14153,7 @@
         <v>45979</v>
       </c>
       <c r="B72" t="n">
-        <v>0.00796979525311059</v>
+        <v>0.007969882287927277</v>
       </c>
       <c r="C72" t="n">
         <v>0.01385522842544207</v>
@@ -14168,7 +14168,7 @@
         <v>0.01683025100813929</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0003368157411482997</v>
+        <v>-0.0003367271818831563</v>
       </c>
       <c r="H72" t="n">
         <v>0.003687394227613661</v>
@@ -14177,16 +14177,16 @@
         <v>0.008282454819535934</v>
       </c>
       <c r="J72" t="n">
-        <v>0.00159491390473443</v>
+        <v>0.001594992048482791</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.01217561345880047</v>
+        <v>-0.01217591665667961</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.01625310539566238</v>
+        <v>-0.01625299737720376</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.008397554120144202</v>
+        <v>-0.008397461670685558</v>
       </c>
     </row>
     <row r="73">
@@ -14209,7 +14209,7 @@
         <v>-0.02234486547009695</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.002021132250569324</v>
+        <v>-0.002021220869513174</v>
       </c>
       <c r="H73" t="n">
         <v>-0.007837451392406547</v>
@@ -14218,16 +14218,16 @@
         <v>-0.009943802090210063</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.006767473342165653</v>
+        <v>-0.00676755083348024</v>
       </c>
       <c r="K73" t="n">
-        <v>0.005969970168640204</v>
+        <v>0.005970176852466702</v>
       </c>
       <c r="L73" t="n">
-        <v>0.006952732290928632</v>
+        <v>0.006952621724409136</v>
       </c>
       <c r="M73" t="n">
-        <v>0.003863270235832328</v>
+        <v>0.003863176643276622</v>
       </c>
     </row>
     <row r="74">
@@ -14250,7 +14250,7 @@
         <v>-0.01029903718716441</v>
       </c>
       <c r="G74" t="n">
-        <v>0.003938032202213115</v>
+        <v>0.00393803255190428</v>
       </c>
       <c r="H74" t="n">
         <v>-0.003455958904367784</v>
@@ -14259,10 +14259,10 @@
         <v>-0.00960692178426148</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.004809593390664002</v>
+        <v>-0.004809671941569449</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.02367178721758623</v>
+        <v>-0.0236718893365444</v>
       </c>
       <c r="L74" t="n">
         <v>-0.03139131201890055</v>
@@ -14276,7 +14276,7 @@
         <v>45982</v>
       </c>
       <c r="B75" t="n">
-        <v>0.006302070097032875</v>
+        <v>0.006301982312242549</v>
       </c>
       <c r="C75" t="n">
         <v>-0.01048491819648978</v>
@@ -14291,7 +14291,7 @@
         <v>-0.01211687035826392</v>
       </c>
       <c r="G75" t="n">
-        <v>0.003025700944912391</v>
+        <v>0.003025878112747238</v>
       </c>
       <c r="H75" t="n">
         <v>0.01312867277026619</v>
@@ -14300,13 +14300,13 @@
         <v>-0.006613794328842793</v>
       </c>
       <c r="J75" t="n">
-        <v>0.01288761894929413</v>
+        <v>0.01288769889705632</v>
       </c>
       <c r="K75" t="n">
-        <v>0.00751273835218047</v>
+        <v>0.007512843732892183</v>
       </c>
       <c r="L75" t="n">
-        <v>0.003858305443777077</v>
+        <v>0.003858192864836907</v>
       </c>
       <c r="M75" t="n">
         <v>0.009961138168965045</v>
@@ -14317,7 +14317,7 @@
         <v>45985</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.002795708211040693</v>
+        <v>-0.002795708454924384</v>
       </c>
       <c r="C76" t="n">
         <v>0.02935986431466864</v>
@@ -14332,7 +14332,7 @@
         <v>0.01616154499085676</v>
       </c>
       <c r="G76" t="n">
-        <v>0.005698580019890542</v>
+        <v>0.0056983149675498</v>
       </c>
       <c r="H76" t="n">
         <v>0.001466851445838246</v>
@@ -14341,13 +14341,13 @@
         <v>0.004882389575904922</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.00119289496547359</v>
+        <v>-0.001192817039228133</v>
       </c>
       <c r="K76" t="n">
         <v>0.02557326108364966</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02382861003251335</v>
+        <v>0.02382861270480285</v>
       </c>
       <c r="M76" t="n">
         <v>0.01471860687623461</v>
@@ -14358,7 +14358,7 @@
         <v>45986</v>
       </c>
       <c r="B77" t="n">
-        <v>-0.006280247710724551</v>
+        <v>-0.00628007330090985</v>
       </c>
       <c r="C77" t="n">
         <v>0.0008577546625325727</v>
@@ -14373,7 +14373,7 @@
         <v>-0.01661457255563059</v>
       </c>
       <c r="G77" t="n">
-        <v>0.002555012696586756</v>
+        <v>0.002555276195526757</v>
       </c>
       <c r="H77" t="n">
         <v>0.008056678907742088</v>
@@ -14382,13 +14382,13 @@
         <v>-0.005300348895078466</v>
       </c>
       <c r="J77" t="n">
-        <v>0.01074833083528492</v>
+        <v>0.0107483299967075</v>
       </c>
       <c r="K77" t="n">
-        <v>0.006163668529668875</v>
+        <v>0.006163769755954451</v>
       </c>
       <c r="L77" t="n">
-        <v>0.002681335455997802</v>
+        <v>0.002681445285864781</v>
       </c>
       <c r="M77" t="n">
         <v>0.009405836039293458</v>
@@ -14399,7 +14399,7 @@
         <v>45987</v>
       </c>
       <c r="B78" t="n">
-        <v>0.007561196206223419</v>
+        <v>0.007561107508138321</v>
       </c>
       <c r="C78" t="n">
         <v>0.03706885418488737</v>
@@ -14414,7 +14414,7 @@
         <v>0.01140795545887863</v>
       </c>
       <c r="G78" t="n">
-        <v>0.004432742665395173</v>
+        <v>0.004432567357426809</v>
       </c>
       <c r="H78" t="n">
         <v>0.004359464097590804</v>
@@ -14423,10 +14423,10 @@
         <v>0.01065718458670584</v>
       </c>
       <c r="J78" t="n">
-        <v>0.006301763382215997</v>
+        <v>0.00630168570613665</v>
       </c>
       <c r="K78" t="n">
-        <v>0.008835737972002766</v>
+        <v>0.008835636476900666</v>
       </c>
       <c r="L78" t="n">
         <v>0.01183770606687751</v>
@@ -14455,7 +14455,7 @@
         <v>0.01470586473205682</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.004744062020493378</v>
+        <v>-0.004743975359400854</v>
       </c>
       <c r="H79" t="n">
         <v>0.004822645686783922</v>
@@ -14467,10 +14467,10 @@
         <v>0.004305292793967519</v>
       </c>
       <c r="K79" t="n">
-        <v>0.008107246699400328</v>
+        <v>0.008107146974362323</v>
       </c>
       <c r="L79" t="n">
-        <v>0.008598130518234992</v>
+        <v>0.008598238483408904</v>
       </c>
       <c r="M79" t="n">
         <v>0.0054584342293309</v>
@@ -14481,7 +14481,7 @@
         <v>45992</v>
       </c>
       <c r="B80" t="n">
-        <v>0.009618703260261929</v>
+        <v>0.009618617018615883</v>
       </c>
       <c r="C80" t="n">
         <v>0.02558096849660396</v>
@@ -14496,7 +14496,7 @@
         <v>-0.0001407364045787896</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.0124487542803009</v>
+        <v>-0.01244884176952554</v>
       </c>
       <c r="H80" t="n">
         <v>-0.0139188020226938</v>
@@ -14508,13 +14508,13 @@
         <v>-0.01013253701193573</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.003359030902372107</v>
+        <v>-0.003358932311603224</v>
       </c>
       <c r="L80" t="n">
-        <v>0.000454298083769844</v>
+        <v>0.0004541909903621466</v>
       </c>
       <c r="M80" t="n">
-        <v>-0.004565560353440801</v>
+        <v>-0.004565470301164498</v>
       </c>
     </row>
     <row r="81">
@@ -14522,7 +14522,7 @@
         <v>45993</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.01292165669046297</v>
+        <v>-0.01292157237420766</v>
       </c>
       <c r="C81" t="n">
         <v>0.01161463452084543</v>
@@ -14537,7 +14537,7 @@
         <v>-0.01210245764000251</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0004505793479445686</v>
+        <v>0.0004505793878621933</v>
       </c>
       <c r="H81" t="n">
         <v>-0.002433670470495919</v>
@@ -14546,16 +14546,16 @@
         <v>-0.004325284006119312</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.0003937437110379527</v>
+        <v>-0.0003936665517765281</v>
       </c>
       <c r="K81" t="n">
-        <v>0.007826172575998713</v>
+        <v>0.007826073319548543</v>
       </c>
       <c r="L81" t="n">
         <v>0.01030202025908489</v>
       </c>
       <c r="M81" t="n">
-        <v>0.001852367504067809</v>
+        <v>0.001852276871199932</v>
       </c>
     </row>
     <row r="82">
@@ -14578,7 +14578,7 @@
         <v>0.006552802476705866</v>
       </c>
       <c r="G82" t="n">
-        <v>0.002815073990664496</v>
+        <v>0.002815251344332914</v>
       </c>
       <c r="H82" t="n">
         <v>0.001951667028617265</v>
@@ -14587,10 +14587,10 @@
         <v>0.004778377919137267</v>
       </c>
       <c r="J82" t="n">
-        <v>0.001181619228992625</v>
+        <v>0.001181541948135578</v>
       </c>
       <c r="K82" t="n">
-        <v>0.00244372528009329</v>
+        <v>0.002443725520765216</v>
       </c>
       <c r="L82" t="n">
         <v>0.002385089741900659</v>
@@ -14619,7 +14619,7 @@
         <v>0.0103311023168049</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.00538961051575837</v>
+        <v>-0.00538978664703027</v>
       </c>
       <c r="H83" t="n">
         <v>-0.001704418022394516</v>
@@ -14631,7 +14631,7 @@
         <v>-0.004720744414286937</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.0009301893300760478</v>
+        <v>-0.0009300911758545194</v>
       </c>
       <c r="L83" t="n">
         <v>0.003724273589680971</v>
@@ -14645,7 +14645,7 @@
         <v>45996</v>
       </c>
       <c r="B84" t="n">
-        <v>-0.004120625594113636</v>
+        <v>-0.004120710180495535</v>
       </c>
       <c r="C84" t="n">
         <v>0.02299077434303509</v>
@@ -14660,7 +14660,7 @@
         <v>0.007423991929235374</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.004628566299502368</v>
+        <v>-0.004628477928322661</v>
       </c>
       <c r="H84" t="n">
         <v>-0.0002438630660646091</v>
@@ -14675,7 +14675,7 @@
         <v>0.004077349973276911</v>
       </c>
       <c r="L84" t="n">
-        <v>0.007317859034925878</v>
+        <v>0.007317964296056134</v>
       </c>
       <c r="M84" t="n">
         <v>0.001899394752821859</v>
@@ -14686,7 +14686,7 @@
         <v>45999</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.01088850325888124</v>
+        <v>-0.01088841924733119</v>
       </c>
       <c r="C85" t="n">
         <v>-0.004532609537463483</v>
@@ -14713,10 +14713,10 @@
         <v>-0.008709362116210539</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.001918404539296925</v>
+        <v>-0.001918502477041395</v>
       </c>
       <c r="L85" t="n">
-        <v>0.007025922640867543</v>
+        <v>0.007025817410254653</v>
       </c>
       <c r="M85" t="n">
         <v>-0.003004209105806011</v>
@@ -14742,7 +14742,7 @@
         <v>-0.008937399241173427</v>
       </c>
       <c r="G86" t="n">
-        <v>0.001024383953459829</v>
+        <v>0.001024115485576571</v>
       </c>
       <c r="H86" t="n">
         <v>-0.005890930547081452</v>
@@ -14754,13 +14754,13 @@
         <v>-0.003594327438588341</v>
       </c>
       <c r="K86" t="n">
-        <v>0.001233345566373334</v>
+        <v>0.001233345687396747</v>
       </c>
       <c r="L86" t="n">
         <v>0.002641709920368829</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.000863028073573191</v>
+        <v>-0.0008631180942337835</v>
       </c>
     </row>
     <row r="87">
@@ -14768,7 +14768,7 @@
         <v>46001</v>
       </c>
       <c r="B87" t="n">
-        <v>0.01050326897903364</v>
+        <v>0.01050318363378566</v>
       </c>
       <c r="C87" t="n">
         <v>0.01631324190229</v>
@@ -14783,7 +14783,7 @@
         <v>0.009733757504076346</v>
       </c>
       <c r="G87" t="n">
-        <v>0.003864752697307905</v>
+        <v>0.003864932529290099</v>
       </c>
       <c r="H87" t="n">
         <v>0.00197527975152112</v>
@@ -14792,16 +14792,16 @@
         <v>0.006089570455026561</v>
       </c>
       <c r="J87" t="n">
-        <v>0.004007981400402372</v>
+        <v>0.004007902849497036</v>
       </c>
       <c r="K87" t="n">
-        <v>0.004095633783892216</v>
+        <v>0.004095732190410706</v>
       </c>
       <c r="L87" t="n">
-        <v>0.004796635369398006</v>
+        <v>0.004796738863375394</v>
       </c>
       <c r="M87" t="n">
-        <v>0.00663214455678518</v>
+        <v>0.006632235252757246</v>
       </c>
     </row>
     <row r="88">
@@ -14809,7 +14809,7 @@
         <v>46002</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.004764031498840082</v>
+        <v>-0.004763947443033212</v>
       </c>
       <c r="C88" t="n">
         <v>0.02764400295161096</v>
@@ -14824,7 +14824,7 @@
         <v>-0.01828750919740052</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.001358868072424357</v>
+        <v>-0.001358690086326719</v>
       </c>
       <c r="H88" t="n">
         <v>0.005421286584202489</v>
@@ -14833,16 +14833,16 @@
         <v>-0.0008646487948147374</v>
       </c>
       <c r="J88" t="n">
-        <v>0.002794402776110871</v>
+        <v>0.002794559469413205</v>
       </c>
       <c r="K88" t="n">
         <v>-0.003234446415096626</v>
       </c>
       <c r="L88" t="n">
-        <v>-0.005109929244202061</v>
+        <v>-0.005110031717793451</v>
       </c>
       <c r="M88" t="n">
-        <v>0.002327035536273447</v>
+        <v>0.002326946031464106</v>
       </c>
     </row>
     <row r="89">
@@ -14865,7 +14865,7 @@
         <v>-0.006353825868682272</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.009638271651177033</v>
+        <v>-0.009638359966402499</v>
       </c>
       <c r="H89" t="n">
         <v>-0.001225484432066604</v>
@@ -14874,7 +14874,7 @@
         <v>-0.008221527997394951</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.0003980545415862569</v>
+        <v>-0.0003981325298384464</v>
       </c>
       <c r="K89" t="n">
         <v>-0.01911830760087863</v>
@@ -14883,7 +14883,7 @@
         <v>-0.02892474625572028</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.01075207461515448</v>
+        <v>-0.01075207557528268</v>
       </c>
     </row>
     <row r="90">
@@ -14924,7 +14924,7 @@
         <v>-0.009673609498594082</v>
       </c>
       <c r="M90" t="n">
-        <v>-0.001510898681416406</v>
+        <v>-0.00151080855021779</v>
       </c>
     </row>
     <row r="91">
@@ -14959,10 +14959,10 @@
         <v>-0.006031329756624793</v>
       </c>
       <c r="K91" t="n">
-        <v>0.00198190330543313</v>
+        <v>0.001981802971139146</v>
       </c>
       <c r="L91" t="n">
-        <v>0.001827105364295978</v>
+        <v>0.001826997710197231</v>
       </c>
       <c r="M91" t="n">
         <v>-0.002732285145230273</v>
@@ -14973,7 +14973,7 @@
         <v>46008</v>
       </c>
       <c r="B92" t="n">
-        <v>0.02214113434085929</v>
+        <v>0.02214104531373695</v>
       </c>
       <c r="C92" t="n">
         <v>0.04382468039768272</v>
@@ -14988,7 +14988,7 @@
         <v>0.02735386486436009</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.0009101061244594089</v>
+        <v>-0.0009101956137538281</v>
       </c>
       <c r="H92" t="n">
         <v>0.004439020498767432</v>
@@ -15000,10 +15000,10 @@
         <v>0.002831715083999597</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.01853714563805797</v>
+        <v>-0.01853694722260213</v>
       </c>
       <c r="L92" t="n">
-        <v>-0.02223623471440195</v>
+        <v>-0.02223612964608457</v>
       </c>
       <c r="M92" t="n">
         <v>-0.01100359398340023</v>
@@ -15014,7 +15014,7 @@
         <v>46009</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.0145154270451614</v>
+        <v>-0.01451534121076903</v>
       </c>
       <c r="C93" t="n">
         <v>-0.01559904833872339</v>
@@ -15029,7 +15029,7 @@
         <v>-0.01162107791285905</v>
       </c>
       <c r="G93" t="n">
-        <v>0.004783350147267829</v>
+        <v>0.004783440146537865</v>
       </c>
       <c r="H93" t="n">
         <v>-0.006138048593621881</v>
@@ -15041,7 +15041,7 @@
         <v>-0.001210220955261576</v>
       </c>
       <c r="K93" t="n">
-        <v>0.01449019850907751</v>
+        <v>0.0144900950035689</v>
       </c>
       <c r="L93" t="n">
         <v>0.01542424419598887</v>
@@ -15070,7 +15070,7 @@
         <v>0.01250180543784252</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.003732297927018235</v>
+        <v>-0.003732387071422649</v>
       </c>
       <c r="H94" t="n">
         <v>-0.003705419354788742</v>
@@ -15082,7 +15082,7 @@
         <v>-0.002019374991667822</v>
       </c>
       <c r="K94" t="n">
-        <v>0.01303536096228441</v>
+        <v>0.01303546153213331</v>
       </c>
       <c r="L94" t="n">
         <v>0.02161948213509146</v>
@@ -15111,7 +15111,7 @@
         <v>0.02498904318890083</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.002170208250155792</v>
+        <v>-0.002170297922714837</v>
       </c>
       <c r="H95" t="n">
         <v>0.007419465227514133</v>
@@ -15123,10 +15123,10 @@
         <v>0.00364226126115641</v>
       </c>
       <c r="K95" t="n">
-        <v>0.004793529762324944</v>
+        <v>0.004793430010699984</v>
       </c>
       <c r="L95" t="n">
-        <v>0.005395295698796598</v>
+        <v>0.005395401640550412</v>
       </c>
       <c r="M95" t="n">
         <v>0.006229803850433591</v>
@@ -15152,7 +15152,7 @@
         <v>0.008174382150915926</v>
       </c>
       <c r="G96" t="n">
-        <v>0.001602545708107916</v>
+        <v>0.001602725341497191</v>
       </c>
       <c r="H96" t="n">
         <v>-0.0002486910704578849</v>
@@ -15167,7 +15167,7 @@
         <v>0.004683320360612031</v>
       </c>
       <c r="L96" t="n">
-        <v>0.00544231679493401</v>
+        <v>0.005442105475013559</v>
       </c>
       <c r="M96" t="n">
         <v>0.004570492347330646</v>
@@ -15193,7 +15193,7 @@
         <v>-0.001422561865921934</v>
       </c>
       <c r="G97" t="n">
-        <v>0.006057118208393053</v>
+        <v>0.006057028678894572</v>
       </c>
       <c r="H97" t="n">
         <v>0.00647085439979822</v>
@@ -15205,10 +15205,10 @@
         <v>0.005227214549579751</v>
       </c>
       <c r="K97" t="n">
-        <v>0.002925563588204838</v>
+        <v>0.002925661929782386</v>
       </c>
       <c r="L97" t="n">
-        <v>0.002398099127578934</v>
+        <v>0.002398204181781383</v>
       </c>
       <c r="M97" t="n">
         <v>0.003517674396244841</v>
@@ -15234,7 +15234,7 @@
         <v>-0.02450133427465429</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.003294338301552791</v>
+        <v>-0.003294160613756647</v>
       </c>
       <c r="H98" t="n">
         <v>0.001978282858908553</v>
@@ -15246,7 +15246,7 @@
         <v>0.001600099204143168</v>
       </c>
       <c r="K98" t="n">
-        <v>-6.402972705099597e-05</v>
+        <v>-6.42258301777332e-05</v>
       </c>
       <c r="L98" t="n">
         <v>0.001572045936863553</v>
@@ -15275,7 +15275,7 @@
         <v>0.01650112730760478</v>
       </c>
       <c r="G99" t="n">
-        <v>0.003761114036173963</v>
+        <v>0.003761024415766201</v>
       </c>
       <c r="H99" t="n">
         <v>0.002714756400448159</v>
@@ -15287,7 +15287,7 @@
         <v>0.002396121739512536</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.004840682759455928</v>
+        <v>-0.004840585173137457</v>
       </c>
       <c r="L99" t="n">
         <v>-0.004504134914436242</v>
@@ -15398,7 +15398,7 @@
         <v>-0.002891911033057082</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.001491717404711879</v>
+        <v>-0.001491627525974537</v>
       </c>
       <c r="H102" t="n">
         <v>0.0007435947877894034</v>
@@ -15410,7 +15410,7 @@
         <v>0.002805611067397962</v>
       </c>
       <c r="K102" t="n">
-        <v>-0.00193712967993187</v>
+        <v>-0.001937030089695924</v>
       </c>
       <c r="L102" t="n">
         <v>0.002292112493914811</v>
@@ -15439,7 +15439,7 @@
         <v>0.01827149293733354</v>
       </c>
       <c r="G103" t="n">
-        <v>0.00494099422071459</v>
+        <v>0.004940903762957527</v>
       </c>
       <c r="H103" t="n">
         <v>0.001238179919649696</v>
@@ -15451,7 +15451,7 @@
         <v>0.00159866582653323</v>
       </c>
       <c r="K103" t="n">
-        <v>0.007942968524083938</v>
+        <v>0.007942867947986931</v>
       </c>
       <c r="L103" t="n">
         <v>0.002217545918676622</v>
@@ -15521,7 +15521,7 @@
         <v>-0.01050943217417244</v>
       </c>
       <c r="G105" t="n">
-        <v>0.005843151577011874</v>
+        <v>0.005843241332185833</v>
       </c>
       <c r="H105" t="n">
         <v>-0.01375932493975329</v>
@@ -15562,7 +15562,7 @@
         <v>0.04056645468152098</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.005011814550815008</v>
+        <v>-0.005011903337351575</v>
       </c>
       <c r="H106" t="n">
         <v>0.007473885554776238</v>
@@ -15603,7 +15603,7 @@
         <v>0.003402294593913169</v>
       </c>
       <c r="G107" t="n">
-        <v>0.006639967965145432</v>
+        <v>0.006640057648388709</v>
       </c>
       <c r="H107" t="n">
         <v>0.001483783991169219</v>
@@ -15644,7 +15644,7 @@
         <v>0.0122916468152936</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.002956952772412702</v>
+        <v>-0.002956952508972877</v>
       </c>
       <c r="H108" t="n">
         <v>0.002962788660020532</v>
@@ -15685,7 +15685,7 @@
         <v>0.02554084845893145</v>
       </c>
       <c r="G109" t="n">
-        <v>0.001711076101470033</v>
+        <v>0.001710897236794073</v>
       </c>
       <c r="H109" t="n">
         <v>0.007631721854014062</v>
@@ -15726,7 +15726,7 @@
         <v>-0.01183999328845886</v>
       </c>
       <c r="G110" t="n">
-        <v>0.005807310956872813</v>
+        <v>0.005807400678176755</v>
       </c>
       <c r="H110" t="n">
         <v>0.01123873497622174</v>
@@ -15767,7 +15767,7 @@
         <v>-0.02038291343469012</v>
       </c>
       <c r="G111" t="n">
-        <v>-0.0002265097263489668</v>
+        <v>-0.0002266871027987172</v>
       </c>
       <c r="H111" t="n">
         <v>0.007489838147912931</v>
@@ -15808,7 +15808,7 @@
         <v>0.007310618480811826</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.005775000221770799</v>
+        <v>-0.005774912538018206</v>
       </c>
       <c r="H112" t="n">
         <v>0.01223019337059172</v>
@@ -15849,7 +15849,7 @@
         <v>0.002930901325896018</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.013098022189727</v>
+        <v>-0.01309802335837962</v>
       </c>
       <c r="H113" t="n">
         <v>-0.01918978463611254</v>
@@ -15864,7 +15864,7 @@
         <v>-0.02124710947964625</v>
       </c>
       <c r="L113" t="n">
-        <v>-0.02595789204559718</v>
+        <v>-0.02595799708597002</v>
       </c>
       <c r="M113" t="n">
         <v>-0.02035680001149731</v>
@@ -15890,7 +15890,7 @@
         <v>0.02059554293026089</v>
       </c>
       <c r="G114" t="n">
-        <v>0.007616762283406686</v>
+        <v>0.007616853379776467</v>
       </c>
       <c r="H114" t="n">
         <v>0.00362320942618366</v>
@@ -15905,7 +15905,7 @@
         <v>0.01351837969000269</v>
       </c>
       <c r="L114" t="n">
-        <v>0.01388877805367961</v>
+        <v>0.01388899523079035</v>
       </c>
       <c r="M114" t="n">
         <v>0.0115411092816613</v>
@@ -15931,7 +15931,7 @@
         <v>-0.02072534386371538</v>
       </c>
       <c r="G115" t="n">
-        <v>0.004352348193597866</v>
+        <v>0.004352437917936047</v>
       </c>
       <c r="H115" t="n">
         <v>-0.009867717482777816</v>
@@ -15946,7 +15946,7 @@
         <v>0.00726938199084981</v>
       </c>
       <c r="L115" t="n">
-        <v>0.007440476665308449</v>
+        <v>0.007440369511513723</v>
       </c>
       <c r="M115" t="n">
         <v>0.005223257672714476</v>
@@ -15972,7 +15972,7 @@
         <v>0.0296574389093387</v>
       </c>
       <c r="G116" t="n">
-        <v>0.002736972290623418</v>
+        <v>0.002736972046114561</v>
       </c>
       <c r="H116" t="n">
         <v>0.002673843874449133</v>
@@ -16013,7 +16013,7 @@
         <v>-0.006355559306345127</v>
       </c>
       <c r="G117" t="n">
-        <v>0.004776561191326856</v>
+        <v>0.004776382582436067</v>
       </c>
       <c r="H117" t="n">
         <v>-0.0007272769619808273</v>
@@ -16054,7 +16054,7 @@
         <v>0.02966793965136749</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.006225213373249328</v>
+        <v>-0.006225213925227568</v>
       </c>
       <c r="H118" t="n">
         <v>0.0007278062787201556</v>
@@ -16069,7 +16069,7 @@
         <v>0.009065284269015539</v>
       </c>
       <c r="L118" t="n">
-        <v>0.0134857583953798</v>
+        <v>0.01348586310497679</v>
       </c>
       <c r="M118" t="n">
         <v>0.003984165378470905</v>
@@ -16095,7 +16095,7 @@
         <v>0.01268832987056046</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.002278056556867192</v>
+        <v>-0.002277967536531311</v>
       </c>
       <c r="H119" t="n">
         <v>-0.009696994854778485</v>
@@ -16107,10 +16107,10 @@
         <v>-0.007042199804775606</v>
       </c>
       <c r="K119" t="n">
-        <v>0.003311433854445545</v>
+        <v>0.003311530790538031</v>
       </c>
       <c r="L119" t="n">
-        <v>0.0079702325081632</v>
+        <v>0.007970128368420815</v>
       </c>
       <c r="M119" t="n">
         <v>-0.0001006645803248718</v>
@@ -16148,10 +16148,10 @@
         <v>0.01339633134589735</v>
       </c>
       <c r="K120" t="n">
-        <v>-0.005985274152202957</v>
+        <v>-0.005985273573928751</v>
       </c>
       <c r="L120" t="n">
-        <v>-0.01581452290804197</v>
+        <v>-0.01581442040868752</v>
       </c>
       <c r="M120" t="n">
         <v>-0.001984377154833794</v>
@@ -16177,7 +16177,7 @@
         <v>0.004801582718582553</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.005592490036273268</v>
+        <v>-0.005592400629388705</v>
       </c>
       <c r="H121" t="n">
         <v>0.001450428522078884</v>
@@ -16189,10 +16189,10 @@
         <v>-0.001944001761624903</v>
       </c>
       <c r="K121" t="n">
-        <v>-0.01201084301011435</v>
+        <v>-0.01201084184268564</v>
       </c>
       <c r="L121" t="n">
-        <v>-0.02035801359526845</v>
+        <v>-0.0203581156214242</v>
       </c>
       <c r="M121" t="n">
         <v>-0.002982484105574335</v>
@@ -16218,7 +16218,7 @@
         <v>-0.05269108386433841</v>
       </c>
       <c r="G122" t="n">
-        <v>-0.002856970744281484</v>
+        <v>-0.002857150306803335</v>
       </c>
       <c r="H122" t="n">
         <v>-0.01134453333622576</v>
@@ -16230,7 +16230,7 @@
         <v>-0.006622495142185048</v>
       </c>
       <c r="K122" t="n">
-        <v>0.0068664977949211</v>
+        <v>0.006866398739876489</v>
       </c>
       <c r="L122" t="n">
         <v>0.00959113454197924</v>
@@ -16259,7 +16259,7 @@
         <v>0.02840832785916936</v>
       </c>
       <c r="G123" t="n">
-        <v>0.002426221951880692</v>
+        <v>0.002426402505280922</v>
       </c>
       <c r="H123" t="n">
         <v>-0.003661941805220614</v>
@@ -16274,7 +16274,7 @@
         <v>-0.01536399586028137</v>
       </c>
       <c r="L123" t="n">
-        <v>-0.02189169970388394</v>
+        <v>-0.02189159440318356</v>
       </c>
       <c r="M123" t="n">
         <v>-0.008455385901172563</v>
@@ -16300,7 +16300,7 @@
         <v>0.005292319946488933</v>
       </c>
       <c r="G124" t="n">
-        <v>-0.00253575430662667</v>
+        <v>-0.002535844027602541</v>
       </c>
       <c r="H124" t="n">
         <v>0.01592730683901955</v>
@@ -16312,10 +16312,10 @@
         <v>0.0121046246958072</v>
       </c>
       <c r="K124" t="n">
-        <v>-0.01746911787310634</v>
+        <v>-0.0174690186398716</v>
       </c>
       <c r="L124" t="n">
-        <v>-0.02787166708509548</v>
+        <v>-0.0278716640845017</v>
       </c>
       <c r="M124" t="n">
         <v>-0.004843853725993386</v>
@@ -16353,10 +16353,10 @@
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>-0.01439528511008936</v>
+        <v>-0.01439528365620069</v>
       </c>
       <c r="L125" t="n">
-        <v>-0.01802770463743253</v>
+        <v>-0.01802781338508774</v>
       </c>
       <c r="M125" t="n">
         <v>-0.01248928406032423</v>
@@ -16382,7 +16382,7 @@
         <v>0.003911793099661054</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0006857476446884281</v>
+        <v>0.0006858368534361503</v>
       </c>
       <c r="H126" t="n">
         <v>0.01843325636405924</v>
@@ -16394,10 +16394,10 @@
         <v>0.01311731572809616</v>
       </c>
       <c r="K126" t="n">
-        <v>0.02113796544764113</v>
+        <v>0.0211378608088908</v>
       </c>
       <c r="L126" t="n">
-        <v>0.04055142659267119</v>
+        <v>0.04055153936991585</v>
       </c>
       <c r="M126" t="n">
         <v>0.01918478647681998</v>
@@ -16423,7 +16423,7 @@
         <v>0.01337834534194182</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.0002283961898309483</v>
+        <v>-0.0002285744646842724</v>
       </c>
       <c r="H127" t="n">
         <v>0.006191832497520977</v>
@@ -16438,7 +16438,7 @@
         <v>0.007660128835232483</v>
       </c>
       <c r="L127" t="n">
-        <v>0.01573026620400486</v>
+        <v>0.01573015611694384</v>
       </c>
       <c r="M127" t="n">
         <v>0.004821726716577324</v>
@@ -16464,7 +16464,7 @@
         <v>0.0001281996495876569</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01154029839886417</v>
+        <v>0.01154038859587803</v>
       </c>
       <c r="H128" t="n">
         <v>0.01396460998000282</v>
@@ -16587,7 +16587,7 @@
         <v>-0.002094737345747721</v>
       </c>
       <c r="G131" t="n">
-        <v>0.00549147325656274</v>
+        <v>0.005491385797401938</v>
       </c>
       <c r="H131" t="n">
         <v>0.01469558594744025</v>
@@ -16599,7 +16599,7 @@
         <v>0.01010860433224869</v>
       </c>
       <c r="K131" t="n">
-        <v>0.002130946298645853</v>
+        <v>0.002131048155454618</v>
       </c>
       <c r="L131" t="n">
         <v>0.002514095570572472</v>
@@ -16628,7 +16628,7 @@
         <v>-0.006428730725819509</v>
       </c>
       <c r="G132" t="n">
-        <v>0.001671697531908434</v>
+        <v>0.001671871640338995</v>
       </c>
       <c r="H132" t="n">
         <v>0.01011485265259182</v>
@@ -16640,10 +16640,10 @@
         <v>0.01000744305007784</v>
       </c>
       <c r="K132" t="n">
-        <v>-0.001030021979697371</v>
+        <v>-0.001030123515214476</v>
       </c>
       <c r="L132" t="n">
-        <v>-0.0005732155760755919</v>
+        <v>-0.0005733251775241754</v>
       </c>
       <c r="M132" t="n">
         <v>0.001613483019051953</v>
@@ -16669,7 +16669,7 @@
         <v>0.04846161371006064</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.003783198835420443</v>
+        <v>-0.003783285343234022</v>
       </c>
       <c r="H133" t="n">
         <v>-0.01342733298114174</v>
@@ -16681,10 +16681,10 @@
         <v>-0.01284410649566126</v>
       </c>
       <c r="K133" t="n">
-        <v>0.007467270408041182</v>
+        <v>0.00746716866302255</v>
       </c>
       <c r="L133" t="n">
-        <v>0.01025240666552829</v>
+        <v>0.01025251745417344</v>
       </c>
       <c r="M133" t="n">
         <v>0.005037707550576753</v>
@@ -16710,7 +16710,7 @@
         <v>0.02254409170186134</v>
       </c>
       <c r="G134" t="n">
-        <v>0.001005199545446089</v>
+        <v>0.001005373877660087</v>
       </c>
       <c r="H134" t="n">
         <v>-0.00346022771193788</v>
@@ -16722,7 +16722,7 @@
         <v>-0.001486937575244762</v>
       </c>
       <c r="K134" t="n">
-        <v>-0.003829877610147525</v>
+        <v>-0.003829676015125183</v>
       </c>
       <c r="L134" t="n">
         <v>-0.004967746123466843</v>
@@ -16751,7 +16751,7 @@
         <v>-0.004187756584076108</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.002343197391195484</v>
+        <v>-0.002343284061671502</v>
       </c>
       <c r="H135" t="n">
         <v>0.00833329223197854</v>
@@ -16763,10 +16763,10 @@
         <v>0.00744597485582088</v>
       </c>
       <c r="K135" t="n">
-        <v>0.008848880165775119</v>
+        <v>0.008848879268683163</v>
       </c>
       <c r="L135" t="n">
-        <v>0.004778615784367002</v>
+        <v>0.0047785066910222</v>
       </c>
       <c r="M135" t="n">
         <v>0.00723184928909637</v>
@@ -16792,7 +16792,7 @@
         <v>0.0006184669474522675</v>
       </c>
       <c r="G136" t="n">
-        <v>0.003690940328736181</v>
+        <v>0.003690765440400368</v>
       </c>
       <c r="H136" t="n">
         <v>0.001147967373821057</v>
@@ -16804,10 +16804,10 @@
         <v>0.001108698381537154</v>
       </c>
       <c r="K136" t="n">
-        <v>-0.01215486102492702</v>
+        <v>-0.01215496029341456</v>
       </c>
       <c r="L136" t="n">
-        <v>-0.01675185241684141</v>
+        <v>-0.01675185423566572</v>
       </c>
       <c r="M136" t="n">
         <v>-0.01021136603876627</v>
@@ -16833,7 +16833,7 @@
         <v>-0.001730523943236917</v>
       </c>
       <c r="G137" t="n">
-        <v>0.001783071413558046</v>
+        <v>0.001782984606484961</v>
       </c>
       <c r="H137" t="n">
         <v>0.002751500604505797</v>
@@ -16848,7 +16848,7 @@
         <v>0.01074149498554933</v>
       </c>
       <c r="L137" t="n">
-        <v>0.01299451323634249</v>
+        <v>0.01299462509558613</v>
       </c>
       <c r="M137" t="n">
         <v>0.00726847527019836</v>
@@ -16874,7 +16874,7 @@
         <v>-0.01275382308137407</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0001110265896964169</v>
+        <v>0.0001112870310417957</v>
       </c>
       <c r="H138" t="n">
         <v>-0.006631494536194937</v>
@@ -16915,7 +16915,7 @@
         <v>0.0005016089859393169</v>
       </c>
       <c r="G139" t="n">
-        <v>0.004004064910100968</v>
+        <v>0.004003890967163359</v>
       </c>
       <c r="H139" t="n">
         <v>0.004373844614320888</v>
@@ -16956,7 +16956,7 @@
         <v>0.0273285746134635</v>
       </c>
       <c r="G140" t="n">
-        <v>0.006092845676294534</v>
+        <v>0.006092846203030522</v>
       </c>
       <c r="H140" t="n">
         <v>0.004813229846997391</v>
@@ -16968,10 +16968,10 @@
         <v>-0.001465687796686654</v>
       </c>
       <c r="K140" t="n">
-        <v>-0.00320065505327527</v>
+        <v>-0.003200755472283601</v>
       </c>
       <c r="L140" t="n">
-        <v>-0.01595637071915179</v>
+        <v>-0.01595626224472846</v>
       </c>
       <c r="M140" t="n">
         <v>-0.004801940858611298</v>
@@ -16997,7 +16997,7 @@
         <v>0.06394149711162944</v>
       </c>
       <c r="G141" t="n">
-        <v>-0.01004214768445522</v>
+        <v>-0.01004206261934859</v>
       </c>
       <c r="H141" t="n">
         <v>0.001824769142402705</v>
@@ -17009,10 +17009,10 @@
         <v>-0.0003670837645906033</v>
       </c>
       <c r="K141" t="n">
-        <v>0.00131729516065282</v>
+        <v>0.001317396034816287</v>
       </c>
       <c r="L141" t="n">
-        <v>0.005621239320455551</v>
+        <v>0.005621128467472314</v>
       </c>
       <c r="M141" t="n">
         <v>0.0005685229860479257</v>
@@ -17038,7 +17038,7 @@
         <v>0.0345222436352004</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.00200871763663979</v>
+        <v>-0.002008630836983882</v>
       </c>
       <c r="H142" t="n">
         <v>-0.005009019021535388</v>
@@ -17050,7 +17050,7 @@
         <v>-0.01284868136150352</v>
       </c>
       <c r="K142" t="n">
-        <v>-0.01070569407223343</v>
+        <v>-0.01070559346331801</v>
       </c>
       <c r="L142" t="n">
         <v>-0.01461942181550357</v>
@@ -17079,7 +17079,7 @@
         <v>0.01507761259827922</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.003130903113082062</v>
+        <v>-0.003131076789484322</v>
       </c>
       <c r="H143" t="n">
         <v>0.001372828283347616</v>
@@ -17091,7 +17091,7 @@
         <v>0.001115707608225769</v>
       </c>
       <c r="K143" t="n">
-        <v>0.01524315706959412</v>
+        <v>0.01524315551940081</v>
       </c>
       <c r="L143" t="n">
         <v>0.01701813858289825</v>
@@ -17120,7 +17120,7 @@
         <v>0.05187855096828975</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.004038077263442963</v>
+        <v>-0.004037990368221278</v>
       </c>
       <c r="H144" t="n">
         <v>-0.009597774332657405</v>
@@ -17132,7 +17132,7 @@
         <v>-0.009286795262917646</v>
       </c>
       <c r="K144" t="n">
-        <v>-0.003012635036419575</v>
+        <v>-0.003012835076103726</v>
       </c>
       <c r="L144" t="n">
         <v>0.002431343105958828</v>
@@ -17161,7 +17161,7 @@
         <v>0.1293738905651218</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.00371683416028934</v>
+        <v>-0.003716658957755192</v>
       </c>
       <c r="H145" t="n">
         <v>-0.01038298955622796</v>
@@ -17173,10 +17173,10 @@
         <v>-0.01237344208293389</v>
       </c>
       <c r="K145" t="n">
-        <v>-0.01504328395399124</v>
+        <v>-0.01504318499200086</v>
       </c>
       <c r="L145" t="n">
-        <v>-0.02061629112335639</v>
+        <v>-0.02061640024005673</v>
       </c>
       <c r="M145" t="n">
         <v>-0.01310712991086205</v>
@@ -17202,7 +17202,7 @@
         <v>-0.04082003262886691</v>
       </c>
       <c r="G146" t="n">
-        <v>0.00870470417872049</v>
+        <v>0.008704438863747832</v>
       </c>
       <c r="H146" t="n">
         <v>0.002098403489968703</v>
@@ -17217,7 +17217,7 @@
         <v>0.01335559691185173</v>
       </c>
       <c r="L146" t="n">
-        <v>0.01799107398511657</v>
+        <v>0.01799118740321637</v>
       </c>
       <c r="M146" t="n">
         <v>0.00875996152231262</v>
@@ -17243,7 +17243,7 @@
         <v>0.01466499331395066</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.01064677091359267</v>
+        <v>-0.01064659750305263</v>
       </c>
       <c r="H147" t="n">
         <v>-0.001396006275538486</v>
@@ -17284,7 +17284,7 @@
         <v>0.0206877236801386</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.01291336667903109</v>
+        <v>-0.01291345364861785</v>
       </c>
       <c r="H148" t="n">
         <v>-0.01188255132359206</v>
@@ -17296,7 +17296,7 @@
         <v>-0.009084005902667669</v>
       </c>
       <c r="K148" t="n">
-        <v>-0.0001317664036337707</v>
+        <v>-0.0001316657417517186</v>
       </c>
       <c r="L148" t="n">
         <v>0.004793892815639911</v>
@@ -17325,7 +17325,7 @@
         <v>0.09569640023922621</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.00195095591216321</v>
+        <v>-0.001950866652158934</v>
       </c>
       <c r="H149" t="n">
         <v>-0.006366460038670474</v>
@@ -17337,7 +17337,7 @@
         <v>-0.007257511098913927</v>
       </c>
       <c r="K149" t="n">
-        <v>-0.01716330052598736</v>
+        <v>-0.01716329879806977</v>
       </c>
       <c r="L149" t="n">
         <v>-0.01844329344883755</v>
@@ -17366,7 +17366,7 @@
         <v>0.01266998908466221</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.004944206742483859</v>
+        <v>-0.00494429573478028</v>
       </c>
       <c r="H150" t="n">
         <v>0.002610300454830572</v>
@@ -17378,7 +17378,7 @@
         <v>-0.005001881322353463</v>
       </c>
       <c r="K150" t="n">
-        <v>-0.005927094575381431</v>
+        <v>-0.005927196401479651</v>
       </c>
       <c r="L150" t="n">
         <v>-0.007544898923255938</v>
@@ -17407,7 +17407,7 @@
         <v>-0.0405371643597755</v>
       </c>
       <c r="G151" t="n">
-        <v>0.007742165573769499</v>
+        <v>0.007742075694902928</v>
       </c>
       <c r="H151" t="n">
         <v>0.007810788653547007</v>
@@ -17422,7 +17422,7 @@
         <v>0.01121747197435274</v>
       </c>
       <c r="L151" t="n">
-        <v>0.01447370657306601</v>
+        <v>0.01447359476036758</v>
       </c>
       <c r="M151" t="n">
         <v>0.01017686501045656</v>
@@ -17448,7 +17448,7 @@
         <v>0.03312177344193334</v>
       </c>
       <c r="G152" t="n">
-        <v>0.002751906713261087</v>
+        <v>0.002751996147062785</v>
       </c>
       <c r="H152" t="n">
         <v>0.003287886896254033</v>
@@ -17463,7 +17463,7 @@
         <v>0.004880238904671153</v>
       </c>
       <c r="L152" t="n">
-        <v>0.005476153684558227</v>
+        <v>0.005476264505581474</v>
       </c>
       <c r="M152" t="n">
         <v>0.002630544991105488</v>
@@ -17504,7 +17504,7 @@
         <v>-0.01393967922837314</v>
       </c>
       <c r="L153" t="n">
-        <v>-0.0113229048679776</v>
+        <v>-0.01132279525081448</v>
       </c>
       <c r="M153" t="n">
         <v>-0.01395364451525716</v>
@@ -17530,7 +17530,7 @@
         <v>-0.0354236674895736</v>
       </c>
       <c r="G154" t="n">
-        <v>0.006094766917204453</v>
+        <v>0.006094856361978707</v>
       </c>
       <c r="H154" t="n">
         <v>-0.002379802371209938</v>
@@ -17545,7 +17545,7 @@
         <v>-0.003160260480330801</v>
       </c>
       <c r="L154" t="n">
-        <v>0.003406781232024869</v>
+        <v>0.003406669981755872</v>
       </c>
       <c r="M154" t="n">
         <v>-0.002464381043311259</v>
@@ -17571,7 +17571,7 @@
         <v>0.03467961548787879</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.01897339695345657</v>
+        <v>-0.01897366197543715</v>
       </c>
       <c r="H155" t="n">
         <v>-0.03172706929913138</v>
@@ -17612,7 +17612,7 @@
         <v>-0.08951661631609753</v>
       </c>
       <c r="G156" t="n">
-        <v>0.00652435575215371</v>
+        <v>0.006524538179382144</v>
       </c>
       <c r="H156" t="n">
         <v>0.007465375324108958</v>
@@ -17776,7 +17776,7 @@
         <v>0.05918467239962144</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.005458230988303225</v>
+        <v>-0.005458140660618782</v>
       </c>
       <c r="H160" t="n">
         <v>-0.006949737990369687</v>
@@ -17817,7 +17817,7 @@
         <v>0.04533015314934907</v>
       </c>
       <c r="G161" t="n">
-        <v>0.01331162532505692</v>
+        <v>0.01331153329263834</v>
       </c>
       <c r="H161" t="n">
         <v>0.004998811707418227</v>
@@ -17858,7 +17858,7 @@
         <v>-0.01987215431462441</v>
       </c>
       <c r="G162" t="n">
-        <v>-0.001037022510290031</v>
+        <v>-0.001037201770879514</v>
       </c>
       <c r="H162" t="n">
         <v>0.01541910444247407</v>
@@ -17899,7 +17899,7 @@
         <v>-0.02483303467276521</v>
       </c>
       <c r="G163" t="n">
-        <v>-0.0009845342084588982</v>
+        <v>-0.0009843549384184191</v>
       </c>
       <c r="H163" t="n">
         <v>0.002939013490867337</v>
@@ -18186,7 +18186,7 @@
         <v>0.02924212093256595</v>
       </c>
       <c r="G170" t="n">
-        <v>0.003006157153737643</v>
+        <v>0.003006246726669159</v>
       </c>
       <c r="H170" t="n">
         <v>0.004670681585384306</v>
@@ -18227,7 +18227,7 @@
         <v>-0.03596172415881871</v>
       </c>
       <c r="G171" t="n">
-        <v>0.005302631409738856</v>
+        <v>0.005302541631730051</v>
       </c>
       <c r="H171" t="n">
         <v>0.009530415169018314</v>
@@ -18350,7 +18350,7 @@
         <v>-0.07787663467542938</v>
       </c>
       <c r="G174" t="n">
-        <v>0.009156251590983322</v>
+        <v>0.009156161800042639</v>
       </c>
       <c r="H174" t="n">
         <v>0.01529324362046625</v>
@@ -18391,7 +18391,7 @@
         <v>0.04550154031057363</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.0002297366819011826</v>
+        <v>-0.0002296477260826935</v>
       </c>
       <c r="H175" t="n">
         <v>0.003597149065359018</v>
@@ -18432,7 +18432,7 @@
         <v>0.05712166438021704</v>
       </c>
       <c r="G176" t="n">
-        <v>-0.005514057384358617</v>
+        <v>-0.005514146381056073</v>
       </c>
       <c r="H176" t="n">
         <v>-0.01926527881880491</v>
@@ -18473,7 +18473,7 @@
         <v>0.008966814007675517</v>
       </c>
       <c r="G177" t="n">
-        <v>0.001963682390861754</v>
+        <v>0.001963772056751356</v>
       </c>
       <c r="H177" t="n">
         <v>-0.007309240273046358</v>
@@ -18514,7 +18514,7 @@
         <v>0.04111288697953563</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.002190355309320657</v>
+        <v>-0.002190444624086241</v>
       </c>
       <c r="H178" t="n">
         <v>0.0115048842675971</v>
@@ -18555,7 +18555,7 @@
         <v>-0.01722095682301861</v>
       </c>
       <c r="G179" t="n">
-        <v>0.00184848806816218</v>
+        <v>0.001848667255289982</v>
       </c>
       <c r="H179" t="n">
         <v>-0.002957173592620155</v>
@@ -18596,7 +18596,7 @@
         <v>0.01752271473692524</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.004958952811547457</v>
+        <v>-0.004959041714150181</v>
       </c>
       <c r="H180" t="n">
         <v>-0.007757267713927818</v>
@@ -18637,7 +18637,7 @@
         <v>0.03622331382567245</v>
       </c>
       <c r="G181" t="n">
-        <v>0.001043101357540266</v>
+        <v>0.001043191148480949</v>
       </c>
       <c r="H181" t="n">
         <v>0.00965729746976729</v>
@@ -18678,7 +18678,7 @@
         <v>0.07901144911926394</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.00775738796932135</v>
+        <v>-0.007757476970873256</v>
       </c>
       <c r="H182" t="n">
         <v>-0.006148937423230305</v>
@@ -18719,7 +18719,7 @@
         <v>-0.02350135052890645</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.0009334562995825246</v>
+        <v>-0.0009333659009480577</v>
       </c>
       <c r="H183" t="n">
         <v>0.01741532273282487</v>
@@ -18760,7 +18760,7 @@
         <v>-0.02916577192835035</v>
       </c>
       <c r="G184" t="n">
-        <v>0.00357553004093103</v>
+        <v>0.003575348751229335</v>
       </c>
       <c r="H184" t="n">
         <v>-0.0018018583321604</v>
@@ -18801,7 +18801,7 @@
         <v>0.03368345557282915</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.00759270505974774</v>
+        <v>-0.007592615583579265</v>
       </c>
       <c r="H185" t="n">
         <v>-0.005415159006912917</v>
@@ -18883,7 +18883,7 @@
         <v>-0.07088854373658826</v>
       </c>
       <c r="G187" t="n">
-        <v>0.007608522709151355</v>
+        <v>0.007608613059850278</v>
       </c>
       <c r="H187" t="n">
         <v>0.01290476643919147</v>
@@ -18924,7 +18924,7 @@
         <v>0.007614813704363677</v>
       </c>
       <c r="G188" t="n">
-        <v>-0.004995339930420895</v>
+        <v>-0.004995429150942976</v>
       </c>
       <c r="H188" t="n">
         <v>-0.007599401433387776</v>
@@ -18965,7 +18965,7 @@
         <v>-0.0102245304166213</v>
       </c>
       <c r="G189" t="n">
-        <v>0.00502041862806113</v>
+        <v>0.005020508746688801</v>
       </c>
       <c r="H189" t="n">
         <v>0.0002251672894157952</v>
@@ -19006,7 +19006,7 @@
         <v>0.03795199837714747</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.006040874109614625</v>
+        <v>-0.006040963236385255</v>
       </c>
       <c r="H190" t="n">
         <v>0.003602732107952589</v>
@@ -19047,7 +19047,7 @@
         <v>0.04067502697744141</v>
       </c>
       <c r="G191" t="n">
-        <v>-0.006661990604272083</v>
+        <v>-0.006662080817694482</v>
       </c>
       <c r="H191" t="n">
         <v>0.0002244811549796388</v>
@@ -19088,7 +19088,7 @@
         <v>-0.01566188300643612</v>
       </c>
       <c r="G192" t="n">
-        <v>-0.002235496247472324</v>
+        <v>-0.002235405632034282</v>
       </c>
       <c r="H192" t="n">
         <v>-0.008299795319133607</v>
@@ -19170,7 +19170,7 @@
         <v>0.03657339669607729</v>
       </c>
       <c r="G194" t="n">
-        <v>-0.01483751592564531</v>
+        <v>-0.01483742503232843</v>
       </c>
       <c r="H194" t="n">
         <v>-0.01548618355740272</v>
@@ -19211,7 +19211,7 @@
         <v>0.007151032781125721</v>
       </c>
       <c r="G195" t="n">
-        <v>-0.001195349834499981</v>
+        <v>-0.001195441986465262</v>
       </c>
       <c r="H195" t="n">
         <v>0.0120287059609796</v>
@@ -19293,7 +19293,7 @@
         <v>-0.05681225196114237</v>
       </c>
       <c r="G197" t="n">
-        <v>0.01072040337114499</v>
+        <v>0.01072031039763655</v>
       </c>
       <c r="H197" t="n">
         <v>0.01115159300464463</v>
@@ -19334,7 +19334,7 @@
         <v>-0.01199148080054757</v>
       </c>
       <c r="G198" t="n">
-        <v>0.00369430463897813</v>
+        <v>0.003694396966182678</v>
       </c>
       <c r="H198" t="n">
         <v>0.00157553995653692</v>
@@ -19457,7 +19457,7 @@
         <v>-0.04357665124600818</v>
       </c>
       <c r="G201" t="n">
-        <v>0.002350245967680076</v>
+        <v>0.002350155266616305</v>
       </c>
       <c r="H201" t="n">
         <v>-0.001789279060572135</v>
@@ -19498,7 +19498,7 @@
         <v>-0.001907960026933164</v>
       </c>
       <c r="G202" t="n">
-        <v>0.005158200406636837</v>
+        <v>0.005158291361796241</v>
       </c>
       <c r="H202" t="n">
         <v>-0.00492944515525584</v>
@@ -19580,7 +19580,7 @@
         <v>0.04965530903983684</v>
       </c>
       <c r="G204" t="n">
-        <v>0.0005383981278650474</v>
+        <v>0.0005384881308954093</v>
       </c>
       <c r="H204" t="n">
         <v>-0.01636734571766429</v>
@@ -19621,7 +19621,7 @@
         <v>0.0130627621583832</v>
       </c>
       <c r="G205" t="n">
-        <v>0.002106107026722537</v>
+        <v>0.002105926928086754</v>
       </c>
       <c r="H205" t="n">
         <v>0.005084380384328568</v>
@@ -19662,7 +19662,7 @@
         <v>0.02615280998145098</v>
       </c>
       <c r="G206" t="n">
-        <v>-0.003969701615743837</v>
+        <v>-0.003969612206535134</v>
       </c>
       <c r="H206" t="n">
         <v>0.000459757544257533</v>
@@ -19908,7 +19908,7 @@
         <v>-0.0407297177692173</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0129595343469826</v>
+        <v>0.01295962492685665</v>
       </c>
       <c r="H212" t="n">
         <v>-0.001556014334970213</v>
@@ -19949,7 +19949,7 @@
         <v>-0.02639137993910456</v>
       </c>
       <c r="G213" t="n">
-        <v>-0.002442445725688636</v>
+        <v>-0.00244253492829416</v>
       </c>
       <c r="H213" t="n">
         <v>0.009795243247855412</v>
@@ -20154,7 +20154,7 @@
         <v>-0.0189779773052251</v>
       </c>
       <c r="G218" t="n">
-        <v>-0.007608211284667044</v>
+        <v>-0.007608122657358662</v>
       </c>
       <c r="H218" t="n">
         <v>0.01244279686910388</v>
@@ -20195,7 +20195,7 @@
         <v>-0.01268968208532351</v>
       </c>
       <c r="G219" t="n">
-        <v>0.001277801310112459</v>
+        <v>0.001277711889231092</v>
       </c>
       <c r="H219" t="n">
         <v>0.01408448263147211</v>
@@ -20359,7 +20359,7 @@
         <v>0.0151687374213183</v>
       </c>
       <c r="G223" t="n">
-        <v>0.001030139025204324</v>
+        <v>0.001030227033664399</v>
       </c>
       <c r="H223" t="n">
         <v>-0.007073463696925519</v>
@@ -20400,7 +20400,7 @@
         <v>-0.005976833943822646</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.01177818421242582</v>
+        <v>-0.01177827109479745</v>
       </c>
       <c r="H224" t="n">
         <v>-0.01981298811057663</v>
@@ -21616,40 +21616,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04512657403632034</v>
+        <v>0.04512653222567484</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.002219973807048315</v>
+        <v>-0.002219974464853936</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008267523140241132</v>
+        <v>0.000826751833005113</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.002099568842302273</v>
+        <v>-0.002099559161053157</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06188890457309214</v>
+        <v>0.06188888549484568</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.006342707483633704</v>
+        <v>-0.006342709977714722</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001625385197713193</v>
+        <v>0.001625385002878533</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02607056571816186</v>
+        <v>0.02607055764394305</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0007154102514151401</v>
+        <v>-0.0007154079001255552</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.008323317851482465</v>
+        <v>-0.008323311842682203</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.009061329234759764</v>
+        <v>-0.009061325526543929</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.004178074744588331</v>
+        <v>-0.004178064141005728</v>
       </c>
     </row>
     <row r="3">
@@ -21659,13 +21659,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.002219973807048315</v>
+        <v>-0.002219974464853936</v>
       </c>
       <c r="C3" t="n">
         <v>0.3819278821475615</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009108393984833946</v>
+        <v>0.009108390206961216</v>
       </c>
       <c r="E3" t="n">
         <v>0.1463271892197654</v>
@@ -21674,25 +21674,25 @@
         <v>-0.03354875982114938</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004650347378176214</v>
+        <v>0.004650269931158654</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01027429611010906</v>
+        <v>0.01027430274981883</v>
       </c>
       <c r="I3" t="n">
         <v>0.03031242005299443</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01433006855841461</v>
+        <v>0.01433008898658614</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0441950854198947</v>
+        <v>0.04419506394259978</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05719193217322984</v>
+        <v>0.05719197929808896</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02854245310854265</v>
+        <v>0.02854245564723594</v>
       </c>
     </row>
     <row r="4">
@@ -21702,40 +21702,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0008267523140241132</v>
+        <v>0.000826751833005113</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009108393984833946</v>
+        <v>0.009108390206961216</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01898879069701121</v>
+        <v>0.01898879751755305</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004417537130918383</v>
+        <v>0.004417536160876454</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01435951503876371</v>
+        <v>-0.01435951443421579</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00408675468363549</v>
+        <v>0.004086760359527351</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01919213376707795</v>
+        <v>0.01919213678559028</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.005452377458879203</v>
+        <v>-0.005452377901683395</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0162067824327217</v>
+        <v>0.0162067878663924</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001381138829323023</v>
+        <v>0.001381148897328537</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.001531945664912215</v>
+        <v>-0.001531933019895025</v>
       </c>
       <c r="M4" t="n">
-        <v>0.004926962411675848</v>
+        <v>0.004926975469924388</v>
       </c>
     </row>
     <row r="5">
@@ -21745,13 +21745,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.002099568842302273</v>
+        <v>-0.002099559161053157</v>
       </c>
       <c r="C5" t="n">
         <v>0.1463271892197654</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004417537130918383</v>
+        <v>0.004417536160876454</v>
       </c>
       <c r="E5" t="n">
         <v>0.08139802010083402</v>
@@ -21760,25 +21760,25 @@
         <v>-0.01085179812269732</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002747614334217231</v>
+        <v>0.00274759393634287</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004345041299906146</v>
+        <v>0.004345044498331544</v>
       </c>
       <c r="I5" t="n">
         <v>0.01490292493040275</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007079368513654913</v>
+        <v>0.007079385566352529</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01772405945033695</v>
+        <v>0.01772405730034252</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02224438369749981</v>
+        <v>0.02224439214223633</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01160524493554574</v>
+        <v>0.01160524815831546</v>
       </c>
     </row>
     <row r="6">
@@ -21788,13 +21788,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06188890457309214</v>
+        <v>0.06188888549484568</v>
       </c>
       <c r="C6" t="n">
         <v>-0.03354875982114938</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01435951503876371</v>
+        <v>-0.01435951443421579</v>
       </c>
       <c r="E6" t="n">
         <v>-0.01085179812269732</v>
@@ -21803,25 +21803,25 @@
         <v>0.2269510540040444</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.01814612809230342</v>
+        <v>-0.01814613214915497</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.01244737812306685</v>
+        <v>-0.01244737702811816</v>
       </c>
       <c r="I6" t="n">
         <v>0.082701060840049</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.01763674717650212</v>
+        <v>-0.01763673682716238</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.02471868098639284</v>
+        <v>-0.02471869011511584</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.02603008643053918</v>
+        <v>-0.0260300784333639</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.02055364935468743</v>
+        <v>-0.02055364543990696</v>
       </c>
     </row>
     <row r="7">
@@ -21831,40 +21831,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.006342707483633704</v>
+        <v>-0.006342709977714722</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004650347378176214</v>
+        <v>0.004650269931158654</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00408675468363549</v>
+        <v>0.004086760359527351</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002747614334217231</v>
+        <v>0.00274759393634287</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01814612809230342</v>
+        <v>-0.01814613214915497</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008600251329274722</v>
+        <v>0.008600287710779673</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003907685969563633</v>
+        <v>0.003907691252304876</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.007144191796723083</v>
+        <v>-0.007144198225304535</v>
       </c>
       <c r="J7" t="n">
-        <v>0.004297668136840069</v>
+        <v>0.004297674932584857</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003549227084278832</v>
+        <v>0.003549201762895467</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003633359750584607</v>
+        <v>0.003633338518558332</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002831979346335646</v>
+        <v>0.002831966145768192</v>
       </c>
     </row>
     <row r="8">
@@ -21874,40 +21874,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001625385197713193</v>
+        <v>0.001625385002878533</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01027429611010906</v>
+        <v>0.01027430274981883</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01919213376707795</v>
+        <v>0.01919213678559028</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004345041299906146</v>
+        <v>0.004345044498331544</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01244737812306685</v>
+        <v>-0.01244737702811816</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003907685969563633</v>
+        <v>0.003907691252304876</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01989483903464305</v>
+        <v>0.01989483611222575</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.004766584629818585</v>
+        <v>-0.004766583484499149</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01617295853197569</v>
+        <v>0.01617296009892257</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003919650146105826</v>
+        <v>0.0003919802861434608</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.002654657547392096</v>
+        <v>-0.002654632786260042</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004330090240569258</v>
+        <v>0.004330108085652617</v>
       </c>
     </row>
     <row r="9">
@@ -21917,13 +21917,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02607056571816186</v>
+        <v>0.02607055764394305</v>
       </c>
       <c r="C9" t="n">
         <v>0.03031242005299443</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.005452377458879203</v>
+        <v>-0.005452377901683395</v>
       </c>
       <c r="E9" t="n">
         <v>0.01490292493040275</v>
@@ -21932,25 +21932,25 @@
         <v>0.082701060840049</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.007144191796723083</v>
+        <v>-0.007144198225304535</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.004766584629818585</v>
+        <v>-0.004766583484499149</v>
       </c>
       <c r="I9" t="n">
         <v>0.03916281266472498</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.005581067610308504</v>
+        <v>-0.005581061061150057</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.003928589643664975</v>
+        <v>-0.003928595697608418</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.002866362639659018</v>
+        <v>-0.002866351023793645</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.004329044971378347</v>
+        <v>-0.004329044064305648</v>
       </c>
     </row>
     <row r="10">
@@ -21960,40 +21960,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0007154102514151401</v>
+        <v>-0.0007154079001255552</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01433006855841461</v>
+        <v>0.01433008898658614</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0162067824327217</v>
+        <v>0.0162067878663924</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007079368513654913</v>
+        <v>0.007079385566352529</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.01763674717650212</v>
+        <v>-0.01763673682716238</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004297668136840069</v>
+        <v>0.004297674932584857</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01617295853197569</v>
+        <v>0.01617296009892257</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.005581067610308504</v>
+        <v>-0.005581061061150057</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01534592962749776</v>
+        <v>0.01534593324272815</v>
       </c>
       <c r="K10" t="n">
-        <v>0.003906910914699712</v>
+        <v>0.003906933491378633</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002184964627809752</v>
+        <v>0.002184986018331844</v>
       </c>
       <c r="M10" t="n">
-        <v>0.005872913806755712</v>
+        <v>0.005872932542855916</v>
       </c>
     </row>
     <row r="11">
@@ -22003,40 +22003,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.008323317851482465</v>
+        <v>-0.008323311842682203</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0441950854198947</v>
+        <v>0.04419506394259978</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001381138829323023</v>
+        <v>0.001381148897328537</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01772405945033695</v>
+        <v>0.01772405730034252</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.02471868098639284</v>
+        <v>-0.02471869011511584</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003549227084278832</v>
+        <v>0.003549201762895467</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0003919650146105826</v>
+        <v>0.0003919802861434608</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.003928589643664975</v>
+        <v>-0.003928595697608418</v>
       </c>
       <c r="J11" t="n">
-        <v>0.003906910914699712</v>
+        <v>0.003906933491378633</v>
       </c>
       <c r="K11" t="n">
-        <v>0.03844645097024302</v>
+        <v>0.03844644359104041</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04881216633541425</v>
+        <v>0.048812163750218</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0235356787261177</v>
+        <v>0.02353568165640694</v>
       </c>
     </row>
     <row r="12">
@@ -22046,40 +22046,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.009061329234759764</v>
+        <v>-0.009061325526543929</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05719193217322984</v>
+        <v>0.05719197929808896</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.001531945664912215</v>
+        <v>-0.001531933019895025</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02224438369749981</v>
+        <v>0.02224439214223633</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.02603008643053918</v>
+        <v>-0.0260300784333639</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003633359750584607</v>
+        <v>0.003633338518558332</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.002654657547392096</v>
+        <v>-0.002654632786260042</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.002866362639659018</v>
+        <v>-0.002866351023793645</v>
       </c>
       <c r="J12" t="n">
-        <v>0.002184964627809752</v>
+        <v>0.002184986018331844</v>
       </c>
       <c r="K12" t="n">
-        <v>0.04881216633541425</v>
+        <v>0.048812163750218</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06755220592186868</v>
+        <v>0.06755219989988981</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02879245993656182</v>
+        <v>0.02879246854511774</v>
       </c>
     </row>
     <row r="13">
@@ -22089,40 +22089,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.004178074744588331</v>
+        <v>-0.004178064141005728</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02854245310854265</v>
+        <v>0.02854245564723594</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004926962411675848</v>
+        <v>0.004926975469924388</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01160524493554574</v>
+        <v>0.01160524815831546</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.02055364935468743</v>
+        <v>-0.02055364543990696</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002831979346335646</v>
+        <v>0.002831966145768192</v>
       </c>
       <c r="H13" t="n">
-        <v>0.004330090240569258</v>
+        <v>0.004330108085652617</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.004329044971378347</v>
+        <v>-0.004329044064305648</v>
       </c>
       <c r="J13" t="n">
-        <v>0.005872913806755712</v>
+        <v>0.005872932542855916</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0235356787261177</v>
+        <v>0.02353568165640694</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02879245993656182</v>
+        <v>0.02879246854511774</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01662005601373192</v>
+        <v>0.01662006714956381</v>
       </c>
     </row>
   </sheetData>
